--- a/accumulated_news.xlsx
+++ b/accumulated_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2463,6 +2463,598 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>IT조선</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>삼성전자, 7년 폴더블 혁신 담은 '폴더블 헤리티지' 전시 - IT조선</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5fMXVkZzUtZDVWendtM1JXYUtDWjE2Q3VJUUQ4QUFLUW5GMFFfdUJ2eGRITjFmQ2MwNktXUUQya3FhaUZJMVRKU00zLTB3OW53Nlc1dl84V09qTU1vdU80V29ENnA5eTJfMVlaeUd0TFc?oc=5</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 00:50:46 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>sedaily.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>삼성전자, 7년 폴더블 기술 한눈에…‘폴더블 헤리티지’ 전시 - sedaily.com</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE1jN2xWMnlOa2VuMmkyakQ3Q2Y2cHF6aGdHWlMwYnJITGxTQ2kySHZ3NUozem9BU2t6RWRYU2lZV09IZm9Udms4WlhzUXB1Z0J2bkdLdDUtd0RaN3Z0Y2R3ck0zbF9hUdIBU0FVX3lxTFBlalVQbjB4Y2NxQlNHdWthZjhGQW82YUdWSWRFWm9JUERSWXJrOG1Rdjc2bEo1eE5XSGFxU3pqRXdveEtoQWw3UTFPYzlSSU55VFVR?oc=5</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:50:01 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>뉴스1</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>정부가 길 닦는다…삼성전자·SK하이닉스 반도체 투자 속도 붙나 - 뉴스1</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE9GZm92VnVLbHN1aFdUdVM1M1A0YXNENVNLeFU2ZW1jVEJpUk8yRkNteWdxaHg0UVM1cm9OVGpwZ1VsNFlRY2lmbzcxZ05OVFpRcDBsc3B6OXNESnRCS1F2dE1lNF8?oc=5</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 21:15:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 日키옥시아 최대주주 지위 확보.. 실질 지배력 확대 - 한국경제</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBrSDNTTDN3bE51MzFyOTlaQnotWl9ZZ3d0MHNWWWhZUHdBVVBZNjRUUEhJWTB4NGY3NzR3ZHdPM2VBMlczcnFBNlZGbVlLOV9QeW9nc2hYUmstUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:50:10 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>지디넷코리아</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 日키오시아 최대주주 등극 - 지디넷코리아</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFA5YVF4dUJXNkU3Ukp3b2ZnRHIxUG1qWEFTUW9fRGxFMWxuRmduV2F6aUlUMUtKNms1VmNXd2NZQWpiclVGSE5nNEM0WWljSjI5QkpLQVhn?oc=5</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:59:34 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 日 낸드 기업 키옥시아 최대주주로 등극 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9haGVWdGNlMmZSODA3cklZVllqUG1rMHFXNUExRnVsOUlZZUFFNXlWS2dkS2JYRm1EbnE5OHQtVGxZdzQ4MnBPYkNXdmFYZnc?oc=5</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 02:21:02 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>미래에셋 “SK하이닉스, 주주환원 40조 전망...솔리다임 상장은 투자재원 확충” - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9nRWdQRERJQTBoMUpOb1Q5dHFwU2dCRVZZTHhJYm9LRjNTakNWQk5LamtRWTB4bTNqZ1JNVV9XQ3RsSmdjTi1MdWlzX2d2S2M?oc=5</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:52:45 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DB하이텍</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DB하이텍, 모아팹에 MEMS 장비 기증 - 디일렉</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE95OFg5cjJXb1JfS2gxQ2lJYUpsd2kwMXNvdjJONTRPSDY2c1VqeFBleW5EX2hwNWJ2ZlZ0SHRnNG9aWVFMYTMxUmV4Wlpfdm8zeE1mOWh0UEpSdnBsYjdaQTN3WHItdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 07:28:39 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DB하이텍</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>etnews.com</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DB하이텍, 반도체 장비 공공나노팹에 무상 이전…“상생 협력으로 생태계 고도화” - etnews.com</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE9Pc0hmMzQ2aW45Uk1wTzdUUDYyRTNLZGowR3h1VUhDbmpORzZldlBFczQwYjJHbjhNS0FpSGxjdTVPeWt3cV93RzFCM25hUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 03:54:16 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>반도체</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>중앙일보</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>“하닉 290층 사람 있어요”…이 뉴스 2개 뜨면, 반도체 팔아라 - 중앙일보</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE42SFFScnFTd1h2SzJNamdDbXVMdkJkNlRRdGhDVXRTQ3lzb0M4MURDN0JiZjdxY3Q2R08xSkwxR0owYkk5akZ5cXdJOVNhSlpjMlNJUE9R?oc=5</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 20:00:03 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>반도체</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>비즈니스포스트</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>대신증권 "코스피 9700선까지 회복 가능, 반도체 마지막 조정 국면에 코스닥 상승 기대" - 비즈니스포스트</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5iVEFEaHJfUkZBM0t1NjNxYWNtN1lsdTJ4WTRlaWZWQnZEUC1YZ3JFZDk5dFhnRXlpUmxmVmRNZFFGM0VwMmw3NXZYa2kwMEhiaVJxeG1lelpmZU1oa1ZNVHJZNE50ZDEzNzVPeWRBVktJbGc?oc=5</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 00:09:35 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>반도체</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>반도체가 끌어올린 8월 수출…초순부터 역대 최대 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5CNkw2aEFTNUpTb2JYYWVScV8yQ25LVk9vc3pBcEd2Z0VjSWFzWHJNOHdIY3BtSERxQ050NXV6YmpONGtEZ0E0VHVfU3JtUmM?oc=5</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 02:12:03 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SK Hynix</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>barchart.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Micron vs. SK hynix: One Stock Rules AI Memory. The Other Has More Room to Run. - barchart.com</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPUC1OYTBBSXZ4cEdaUkxXckdTcldkQm5MNWl0QTBOVnJIempXY0ZXSnhtNGNuYkFIYkg5WHprWnlsVnVqazFReVRHQS11VWEtS2lUc215d0xrVWtlVVNxT1hKQUQ5WFRqXy1Hal8xY2tld1J6RHpXQVREQ1hJRjdsUllpdjJyS1VDVzRadGxPVEhvRzAwNkhrSFF5ZUNZOFA3MEZUejhXd2JmSXJYR1ZtREJvYXg0UDRrYWFJ?oc=5</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 19:52:57 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Hyundai EV</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>motor1.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Shocker: Hyundai Ioniq 5 EV Defies The Odds As Sales Increase - motor1.com</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNRFNib0h0QmJtY1hYeURUbTgzZ0dPTHlPUDl1SzJ3QmtiLWU4aW1ZUGxnZmxTVHBDcUhmNzFwbFh5Y1l4OXdveXpyVHZNSDNhM2puTkFQRHBsTm9TWlZfME8xWjlWX3l4cjhrRmRxNERPVXlpYUk0SkJkeHVWUkpOanFXR2U0WWM?oc=5</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 21:38:55 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HBM memory</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Micron Says AI Memory Crunch Could Last Beyond 2027 as DRAM Demand Soars - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQQkg0Q3NTZ2NNTl9QWld3N3dsYmR3NjAtdWRmTFhIcjU0aWs5ek1KUVpremF2QS1rcUJ2ZktpSXJFaGJ6Mnd2ZXdfWms5Z1ZPTDJhWmo0eDl2b2pGS2k2VlczY2k0MUhtNXozQjIyc3NHRzRsc2lDVVg0akZkazdTcUdCMlJORFpHUkFpbGlabUNzbGVza1d3?oc=5</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 01:04:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:37</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HBM memory</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Tom's Hardware</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Nvidia reportedly testing lower memory configs of Rubin Ultra as memory shortage bites back — designs tested include as little as 192 GB and step back to HBM4 - Tom's Hardware</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAJBVV95cUxNNFZrdGxyV2c1Wk1DdF9sQ1lMYUJpdnB1bUZIRS14MmhKSXZWZGt3a0k3TkIzcUxTam5ENHdISng5OGUxVkdoeGRhYkJJX0Rpa290ZkE3LU9Ncks3SHhBVkNjclpkRTE2NFRNOFg1YmRlWWR4dzJ0UzMwSmR5Z3RIZmZsbWlOREd5N1BzVHZfV1A1d1BuOFlZa21ER3RMVE0tTzJtUXNJOGhOb3RyVWQzOEduSFBHVDhSMUh6T211WGw2OV92eGJYVDVfQk1kOU5FbGJ4bTlGUjdsN0dBM0lXWi1Odm1nenNvd3dBd2k4VnRSTHBIWUVHLVB2NWNyLUczSnJ0dWRCcUZpbDdGQk5ibTBCZ05sRTR0RW9zX0NacTY1c2hCYXJQMTJUaU0?oc=5</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 16:47:00 GMT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/accumulated_news.xlsx
+++ b/accumulated_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:J248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,21 @@
           <t>발행일시</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>면접활용도</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>분류태그</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>검색키워드</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -501,6 +516,17 @@
           <t>Mon, 10 Aug 2026 23:58:00 GMT</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,6 +564,17 @@
           <t>Mon, 10 Aug 2026 23:54:50 GMT</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -575,6 +612,17 @@
           <t>Tue, 11 Aug 2026 01:25:23 GMT</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -612,6 +660,17 @@
           <t>Tue, 11 Aug 2026 00:19:09 GMT</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -649,6 +708,17 @@
           <t>Tue, 11 Aug 2026 01:10:58 GMT</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -686,6 +756,17 @@
           <t>Mon, 10 Aug 2026 08:11:00 GMT</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -723,6 +804,17 @@
           <t>Mon, 10 Aug 2026 23:48:08 GMT</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -760,6 +852,17 @@
           <t>Tue, 11 Aug 2026 00:41:00 GMT</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -797,6 +900,17 @@
           <t>Tue, 11 Aug 2026 01:20:42 GMT</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -834,6 +948,17 @@
           <t>Tue, 11 Aug 2026 01:35:49 GMT</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -871,6 +996,17 @@
           <t>Mon, 10 Aug 2026 06:43:11 GMT</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -908,6 +1044,17 @@
           <t>Sun, 09 Aug 2026 01:00:00 GMT</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -945,6 +1092,17 @@
           <t>Thu, 06 Aug 2026 07:28:39 GMT</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -982,6 +1140,17 @@
           <t>Thu, 06 Aug 2026 03:54:16 GMT</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1019,6 +1188,17 @@
           <t>Thu, 06 Aug 2026 01:39:55 GMT</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1056,6 +1236,17 @@
           <t>Mon, 10 Aug 2026 23:30:00 GMT</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1093,6 +1284,17 @@
           <t>Tue, 11 Aug 2026 00:43:00 GMT</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1130,6 +1332,17 @@
           <t>Tue, 11 Aug 2026 01:04:17 GMT</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1167,6 +1380,17 @@
           <t>Tue, 11 Aug 2026 00:16:50 GMT</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1204,6 +1428,17 @@
           <t>Tue, 11 Aug 2026 00:03:00 GMT</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1241,6 +1476,17 @@
           <t>Tue, 11 Aug 2026 00:01:27 GMT</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1278,6 +1524,17 @@
           <t>Mon, 10 Aug 2026 22:31:00 GMT</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1315,6 +1572,17 @@
           <t>Mon, 10 Aug 2026 08:57:00 GMT</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1352,6 +1620,17 @@
           <t>Mon, 10 Aug 2026 05:23:38 GMT</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1389,6 +1668,17 @@
           <t>Mon, 10 Aug 2026 07:12:45 GMT</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1426,6 +1716,17 @@
           <t>Mon, 10 Aug 2026 20:00:02 GMT</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1463,6 +1764,17 @@
           <t>Tue, 11 Aug 2026 01:03:00 GMT</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1500,6 +1812,17 @@
           <t>Tue, 11 Aug 2026 00:20:00 GMT</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1537,6 +1860,17 @@
           <t>Tue, 11 Aug 2026 00:21:00 GMT</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1574,6 +1908,17 @@
           <t>Mon, 10 Aug 2026 05:25:00 GMT</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1611,6 +1956,17 @@
           <t>Mon, 10 Aug 2026 23:00:00 GMT</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1648,6 +2004,17 @@
           <t>Tue, 11 Aug 2026 00:46:15 GMT</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1685,6 +2052,17 @@
           <t>Tue, 11 Aug 2026 01:32:57 GMT</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1722,6 +2100,17 @@
           <t>Mon, 10 Aug 2026 21:49:15 GMT</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1759,6 +2148,17 @@
           <t>Sat, 08 Aug 2026 07:00:00 GMT</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1796,6 +2196,17 @@
           <t>Mon, 10 Aug 2026 00:30:00 GMT</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1833,6 +2244,17 @@
           <t>Mon, 10 Aug 2026 04:24:27 GMT</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1870,6 +2292,17 @@
           <t>Tue, 11 Aug 2026 00:23:00 GMT</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1907,6 +2340,17 @@
           <t>Mon, 10 Aug 2026 19:52:57 GMT</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1944,6 +2388,17 @@
           <t>Mon, 10 Aug 2026 02:37:32 GMT</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1981,6 +2436,17 @@
           <t>Mon, 10 Aug 2026 10:29:27 GMT</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2018,6 +2484,17 @@
           <t>Mon, 10 Aug 2026 02:02:00 GMT</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2055,6 +2532,17 @@
           <t>Mon, 10 Aug 2026 13:38:13 GMT</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2092,6 +2580,17 @@
           <t>Mon, 10 Aug 2026 07:35:25 GMT</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2129,6 +2628,17 @@
           <t>Sun, 09 Aug 2026 20:30:00 GMT</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2166,6 +2676,17 @@
           <t>Mon, 10 Aug 2026 02:01:20 GMT</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2203,6 +2724,17 @@
           <t>Sun, 09 Aug 2026 21:38:55 GMT</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2240,6 +2772,17 @@
           <t>Mon, 10 Aug 2026 10:54:51 GMT</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2277,6 +2820,17 @@
           <t>Sun, 09 Aug 2026 03:00:00 GMT</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2314,6 +2868,17 @@
           <t>Mon, 10 Aug 2026 08:14:29 GMT</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2351,6 +2916,17 @@
           <t>Mon, 10 Aug 2026 03:27:21 GMT</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2388,6 +2964,17 @@
           <t>Mon, 10 Aug 2026 20:27:00 GMT</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2425,6 +3012,17 @@
           <t>Mon, 10 Aug 2026 22:42:00 GMT</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2462,6 +3060,17 @@
           <t>Mon, 10 Aug 2026 16:47:00 GMT</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2499,6 +3108,17 @@
           <t>Tue, 11 Aug 2026 00:50:46 GMT</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2536,6 +3156,17 @@
           <t>Tue, 11 Aug 2026 01:50:01 GMT</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2573,6 +3204,17 @@
           <t>Mon, 10 Aug 2026 21:15:00 GMT</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2610,6 +3252,17 @@
           <t>Tue, 11 Aug 2026 01:50:10 GMT</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2647,6 +3300,17 @@
           <t>Tue, 11 Aug 2026 01:59:34 GMT</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2684,6 +3348,17 @@
           <t>Tue, 11 Aug 2026 02:21:02 GMT</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2721,6 +3396,17 @@
           <t>Tue, 11 Aug 2026 01:52:45 GMT</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2758,6 +3444,17 @@
           <t>Thu, 06 Aug 2026 07:28:39 GMT</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2795,6 +3492,17 @@
           <t>Thu, 06 Aug 2026 03:54:16 GMT</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2832,6 +3540,17 @@
           <t>Sun, 09 Aug 2026 20:00:03 GMT</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2869,6 +3588,17 @@
           <t>Tue, 11 Aug 2026 00:09:35 GMT</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2906,6 +3636,17 @@
           <t>Tue, 11 Aug 2026 02:12:03 GMT</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2943,6 +3684,17 @@
           <t>Mon, 10 Aug 2026 19:52:57 GMT</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2980,6 +3732,17 @@
           <t>Sun, 09 Aug 2026 21:38:55 GMT</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3017,6 +3780,17 @@
           <t>Tue, 11 Aug 2026 01:04:00 GMT</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3052,6 +3826,8513 @@
       <c r="G71" t="inlineStr">
         <is>
           <t>Mon, 10 Aug 2026 16:47:00 GMT</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>jabon.co.kr</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>삼성 18나노 D램 유출 6년 4개월…SK하이닉스 4000장 출력 5년 - jabon.co.kr</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1oU2d5bzJod01vN21RZURHMGRMYngwdTN5amhjbGxPX2Vrcjd2TGlGMVh6bEtHVDg0azJHM2FfWVNoRnZ5UUQ4OUNiLTBwU1NyQlFtakUwcnpCckxwRjZaclFWZVJpZ3c?oc=5</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>잡플래닛</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>삼성전자 반도체 엔지니어 이직, 협력사 경력 도움될까? - 잡플래닛</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wJBVV95cUxNUHhlY3dNVE5ja3BJb1FLRFN2a0xiNWhVVDhrOGk5U0duUlNKM05XOVJWN3AxV3dwNDhXMS11dWFycWxYVmdUOGY2M25ibkZLQ01XaVBWTkZmWVdwMER3aTBLUnRoNmVNZ0VtMnUtOVpPVWU0MGlVQVNQOU5CNVZNeHAzbWxVS3RiOUIwUm0xVWZvUjhUYWE1MFdfdmEtMUdBSXdydU8wdW5LWTFhLUdleDg2NmhyVDZ4WU9DQ0FuYmxySlFQM3J5clRRODlNaklSQzdHUjVLX2cydWFOMVdfamJHVWhiYThaZHhTYThfcXBsX1owck9LU1luNXQyUy1yckNVT1Nld09xS0MtZW1wRnFkRE82M3N0S1Z0bS1JX1FoX1hpVW1qZEJ2QTRyYy0yUHZBYUFXekdXcGlac1pLNGFSWEdUcWU4M1RqSUI4a2RIY0E2eVBKOEdsTDNFWUxGdWtlRm1DelYzb0U?oc=5</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>삼성 ‘HBM4 성공’ 숨은 주역 최정민 “4나노 초저전력 공정 기술로 HBM4 양산화” - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9MOWNpNHJXdFpwNFJMSTctNkk2WE5FRWNtbEJ5NkhuMnRrdGIwSGhCQlZpcUpna1JwU2Nmc1FHZlNldk8xb18zOUltRGFJNGc?oc=5</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>문화일보</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>“AI시대 견인 핵심엔 반도체 공정 기술” - 문화일보</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9fMUpERmRteE1wb1VNNVBfelFyaDFjemJGRjlNQjBNbHBaNDdLRVRmZEdndXNLMzYtNEg2cE1udU50THVjSWRwdnBUSFF3eTRj?oc=5</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>dt.co.kr</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>‘4나노 파운드리’로 HBM 양산 큰 몫… 삼성전자, 개발 스토리 소개 - dt.co.kr</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE51cEpBdDdTelpkSnYxaVNwM2h4YU9FQnRYSlpfR05BRzNlNEU4Tmx6LVJ1Qm5RRDIwZ1ZGM3JTVld1UXAyUGRWS0xrOXhaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>학력 제한 없앤 SK하이닉스, 반나절 심층면접...AI 활용능력 본다 - 조선일보</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNSDQyWFBwZ0xkVWNfRGdKX3JGdWVEV3RaSFo3YTNGREVuRUVIYlJDRWdCTDZOV3hrdnNIWTQzaTRCWEl6WmZGSWVXd3ZVSDQ5M0VLVW4yVXBSeU1JVXJ1bnpwV05ra2FiMElBcm9faVFXT2hheGFZdGQxQ0tBUUxydEtrMA?oc=5</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>SK하이닉스 양산기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>SK하닉 '억대 성과급' 그냥 주는 거 아니었네…취준생 '발칵' - 한국경제</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBKTGJycGExaUdoV2lpUjI1ZzZEdmRGeDF1enRrc2lEZjJITXBZdHRfdFFQd2JHbFJLUW1xdktaOGJ6Sk00SzBXMWZKWFhMZDFUWTdmaVEtZTFzZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>SK하이닉스 양산기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>뉴시스</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 반도체 인재 대규모 채용 돌입…"세 자릿수 규모" - 뉴시스</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1LLVM2VlJjMmR4VE82RER0TVlJSDB5dm10WFhHcGVLbnY2WFM0UXFXd2VJWEE0dzRodlJCTUU3X2gyVjdySFhyYUVJdkwycG9QUU5DZnNnOFA3YzlweDZaZdIBeEFVX3lxTFB6MTVYTV82LU5MeS1fMVdkZ1lvaXptcm1jYWxPelpGaVNBbklKejQxWnU2YnF1b0tIZ192cWFkN1hKOEhtUHgzR255UVJCRmZGSXZLQU51QlJyc0xyWHhoMzRKVmRRRzNONUdWek9PclZoRWQwekx2ag?oc=5</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>SK하이닉스 양산기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>삼성전자·SK하이닉스, HBM4 수율 격차 1.5배…엔비디아 물량 배분 좌우 - 글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOMnZtX2ZuS2JkLWw1NE84UDI1MnV2TVQzMDZoeENPeGpQOGhXMmh0RmlIZzgxVVAyTmhQeFRTNjgwRVktYnV3dEt1cDZ5eFVoRnZlMUtEM2RnaHJtZzJpaDhCMzNFNTYxMVVWNndEc3dJY2pxVHhubTJsWXo2cjhUeWZSc1RMd1dr?oc=5</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>SK하이닉스 양산기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>현대차·기아, 딥엑스와 AI칩 공동개발…"품질 검증 완료" [CES 2026] - 한국경제</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5tbTFpeVVYcmxpeXMwdU1mWHRwRWVkbzdGQ3htYy1Kbm1vdV9kSE5PZzdjRDJ4OVExSHo4VWZDWG5KeG5YaWFiak9IWDB1eENGdjZHLUFkVzlPdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>현대차 개발품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>정조대왕, 즉위 직후 "내 아버지는 사도세자"… 정몽구 회장은? - 조선일보</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPdjlUU2FaMGVCNzZCOUFhN3FZY2g0cXlFUzY2bzhrTVFfeDVueEg3dFNkazhyME9fZGllOWdla0U0dVo2V3NZd012OGs3a2NvLVNoZEJEbjRaY2pvN1hFUV82Y3E3X25reVViWUxaalp6M2JxRDJNa1ZWcGlZSWlodlhveFhJVmVzZFNHTG5ZTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>현대차 개발품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>비즈니스포스트</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>[현장] 현대차그룹 남양기술연구소를 가다, 정의선 '세계적 품질' 자신감의 비밀 - 비즈니스포스트</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBDUUZxUDg5UlNtb2VmRXdGQVpWVm5OaDF2OWhtVTM3c2VLRF90VV9fa09hOXRJMEFpR0RKdnBDSjlzZE9tVWlqWjJQUmNxZV9URF9DREJ6N3QyemJJRm5TZ2wwSFhTVmpCY1FucE1OMy1ELVk?oc=5</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>현대차 개발품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>월요신문</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>현대차·기아, 딥엑스와 AI 칩 공동 개발...품질 검증 완료 - 월요신문</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1wV2taeHY0NnlnODJGdVZpS2tzOV8zdlcxelFyN0oyNlZyeDJLVTVQa0YxczRxRnIyck43bkxEaTlBRzJOOGQ1eEo2YkFBSl9YQjBUbkxZdERDUWdjZ0FQTFQ3VWFXazdaNEE?oc=5</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>현대차 개발품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>서울파이낸스</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>[진격의 오토에버 ①] 취임 후 시총 2배 '껑충'···류석문 대표에 거는 기대 - 서울파이낸스</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5kUFg4bWh3Rm9lNGxhWGo0SmJwVGUzZ2lLRG5qTk8zWHBWd0doelNkakxTVmxldVdOSmJ3b0xXazJOLVVLTU9EYVJoRHl5ME1ZS25ONlFXaXB2X1g0WkJZNERQcW1RQ2tqckE?oc=5</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>현대차 개발품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>매일경제</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>현대모비스, 생성형 AI ‘MoAI’ R&amp;D·품질·영업 업무에 도입 - 매일경제</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE16cmVMNFhKblNrS2N6YVFVUjE5Qk0tNEdZdVFvVG1FdVpvMW1QanUxN0NzVFNIaVJDSGZIN3FrWXZELVJFMzRrMmdFNENuX0JOTXRyb2RR?oc=5</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tue, 21 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>현대모비스 품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>뉴스퀘스트</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>로봇 부품 시장 진출하는 현대모비스, 아틀라스 양산 맞춰 원가·품질 두 마리 토끼 잡는다 - 뉴스퀘스트</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1fWk1wMWRzcTgtVFlDUm5oR1dqUkZMZENEZ0UyU0pWZE5pNW5CYVM5d29naFZMekxoNmtxdTFER0oyS2U4STROV0ZBNVJ4cjNEdldLMGluSi1QOW5XUHhKb2tWMC05bVRpQ05oNVFtY9IBc0FVX3lxTE1CbGhxVTFCVkY1YktFeEVwckVpUndjREZvN0MyUDdITzNFRmtTbHBlb0l6OHRPUTRiT3dfTEJXVERkZ3U4U210TDRxU0hXeHo3RUt2NFNWbFVZd2t1UDZib3BsRVFDMG01UUk1NzJrZTF5ZUU?oc=5</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>현대모비스 품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>데일리e뉴스</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>[ESG 포커스] 현대모비스 "품질보증 체제 확립...최고 경쟁력 유지 총력" - 데일리e뉴스</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5xdUgwRUZvbVI3bXZ1WGpoUUo5SWxCOTRoemFSRWxvSVF4UFB1MHdlbmRrX2pZVVcyam1hUzUwbmlINXUzV1lOVm9neWlxNzdVYUlqY1BkQnp0OFFwWU0tUTd6ZkxxbTF1YUYwODZrZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Wed, 01 May 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>현대모비스 품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>뉴스1</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>현대모비스, 車 반도체 설계부터 품질 검증 등 전 과정 인증 완료 - 뉴스1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFB2NUVnemtiN0pKd1VwOVlyLUFqLWs4QS1YMEFwUGlCeVo4dVp3Zy15UW5vcVhOVDVIaTZyb3QzbDVVY0NzVXktanlfLS1jUDktVXF6OHhPMloxazhhcWJMcg?oc=5</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Thu, 21 Aug 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>현대모비스 품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>아주경제</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 中 충칭 털고 용인·청주 54조 폭풍 투자…AI 메모리 선택과 집중 - 아주경제</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1ZZ1JyelV3UzMwWXgzV0ltZ3BwaEk3WHc1T19BMzdyT3RDY1otUGczT203TElfX1NJcU9kY01NRWVvN3FMYXMybEhxNE9tSzZFWkIxclNuRDFuQdIBWEFVX3lxTFBRWHpTQVhhM3dTM2VrUUdobjY3UU1aVF91N0x2UDB6d2VBdXhaLUxVdTJaY0pYaDVjSW5icTlrTVQzOVNkZXJGSWdVS1ZHNDhqNlJIQWhSM00?oc=5</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>라인/투자/Fab</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ccdn.co.kr</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>하이닉스, 청주 M17 건설 확정 - ccdn.co.kr</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE90X0JRcjdMcWQtTWtDeE80Tm1JMEd6LVZ0ZGlNRzlGMmhZOXUyT2h6SzdHaVlOWlNtd1RleTdCbHNEOHRhUHpVNUIwcnRheGxHRDJ6bHprcDMxVmMxSm5oUUh5eE1pUVZpU2c?oc=5</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 04:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>낸드, 2027년 물량 완판 초읽기…SK하이닉스, 청주 M17 건설 19조 투자 - 글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPOEJ3a3ZsbVFmN0Exd1dBUm1LeWtTVVZzdldpWmJnQUp4MlRlWTVNalg4cjFiM1htaHRGZWdOS0lyc0c4a3VBRmU3c0VUc1o2OW1HSFlJdEl1T2dqMXJONTJxUUI3T3FFNmJsc0lqR3pPVUF0WllTN0dBdDdoNzg3dHhjb0ctNlow?oc=5</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Sat, 08 Aug 2026 19:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>라인/투자/Fab</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>"용인과 청주에 54조 투자" SK하이닉스, 中 충칭 공장 지분 매각 검토 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE11N0swb3hTLVEzYmFjRmFGV2RuYmozNUlVb05VR3gwTXFYX2FmcmIzVGZMWlNRTXo2cXFOa052dmJMT05HOENuY0FNQU1ic0k?oc=5</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Sat, 08 Aug 2026 11:21:28 GMT</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>라인/투자/Fab</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>오늘경제</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>[이슈] SK하이닉스, 용인·청주에 54조 원 투자 확정…"공급력이 곧 경쟁력" - 오늘경제</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE0wWEluOFMxOHFJQThIYUdBRzAxal9oMXFEaDlYSmUzSnI3LXl1a05MbkF1LXF1WWk1aFBMRFMtbkJPOHZXSlp1ODdBdng2OXlYVU5yRjd1MU1QaHRBWndLV0FvOUpxUGZSZllDZl90N2MxcUk?oc=5</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>라인/투자/Fab</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>연합인포맥스</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>SK하이닉스 54조 시설투자…최태원 "공급 늘려 가격 낮춰야" - 연합인포맥스</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE84VE53WVpROHRRZ2NsODZ6dEVMZE1UWUQ4cEVKWnNIck9ZWnRXa0ZsaldReS1RZjFKSDRrYWp0eXRQX253V1RPSXBuM042WURXWGRKV3c5WGdfN3c1dzR2RXBaVmFjZkZMbjRuVFFWRk4?oc=5</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:26:00 GMT</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>라인/투자/Fab</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>경향신문</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>청주 SK하이닉스 공장서 불···유독 가스 누출돼 직원 3600명 대피 소동 - 경향신문</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE4xTFg0MmhKMVNBMnFNd1JMR09sRHZ2N1lwR1ltSzdabWpURHR6b2R5eTJtaTZKWF9ybElxaTRWV05ZRUZhZzJ2eUlYelpmQjYzYnJMQlBNVE1fd9IBX0FVX3lxTE5hRHRDanZmS3FrUWVnYjltMUdqcTJXa216MnM1VzRhODN3N19TbHhzSk40Qk5tdkFjYmIyd05zSVd3eFZ3M0V3emZySEJCczlyN1NydGR1YU5TWUtCMU80?oc=5</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 이달부터 M15X 신공장서 HBM4용 D램 생산 본격화 - 조선비즈 - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPRElnN2tWX3ppM3gxcnhOZzlqVHpXUUxUV0NxRmJJSHd0cFVfeWwtb05CencweUxBR3Y2SXZTeldOcEpCQUpWclptaDlJczNjQnFyV3ZFLTE2elFXZzl2em9oQldwU3czX25rSldrbjhub2ZseWtMbVlvd0xDcDUwQURB0gGWAUFVX3lxTE1aa1V1SFBCYmtxeG5ubm40Z1I5eEZ4LTBMTlNWUVFBVHZ1dDRhaDVKYVd3dXFDb1YtcVlNWThRZnBER0lkcHdXYTUzMVd1YUxZU2paUC1NcnBBc3RfNUhQaW8ycXZjY1oxLUIwcGhpQlZ0VnptTHpLRDhPQjNYMkpISXU2QmRheEoxR1BYalhHRW95Y3BZQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>에너지경제신문</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주공장서 불…3600여명 대피 소동 - 에너지경제신문</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFAzZjBNSG90RDNrc1NpajlsOHlpU2thalQ0QWQyR2FWTXNFLWF3dVJ1bGJxVHlxY1NEbEhtMjdUd0VtX1ZnejltMEc1RjhKTy12Wl9nbmJSRmhxZHc?oc=5</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>충청타임즈</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주사업장 반도체특별법 포함 유력(?) - 충청타임즈</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1VaXBPRVdvV2hySUZRLXVMTDkyMEh6c1pBUWlmeFZKMkZrZHRGdlZHVm44RldVWXNBMzlaalZMZDFTTEMtaHhpck45elltMnNJbWNBd1pKTDl5QmdodXc2cHJxR3hvV2NL?oc=5</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:32:00 GMT</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>HBM 12단서 8단 후퇴 검토…삼성·SK하이닉스 수율이 판 가른다 - 글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQU25KdjJ5UjdodEJ1NU5nUjhIMmg4SnZMMS1mNzVLZkJoWV8tMThtNjc3WGNnZWdLZHR3REc1VVI3bS1yTHdvZkJPUkU1T0xBcm1CbEdpejc4cTEtYTE3N08yUlktZnE2Qmt0dWdwcC1oSlcxRVo0UWg2U3FXZFhqa3ROVzAyZkJW?oc=5</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:35:00 GMT</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>블록체인투데이</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>드디어 승부 뒤집나?… 삼성 HBM4 수율 80% 육박, SK하이닉스 맹추격 - 블록체인투데이</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBGcnp5M2dnNVBSd1pBTGJsb25LUWduek5ERGs0aEdnbzcwX1QtbHhPRVBCcjFQQ2l6YW56eG1GMTl4V2xSYVhncTRqWXYweDZIeGs1WTB0am01amg5VXpqbjJKSVRuZk8ydmlqdFNvc1Y?oc=5</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:49:03 GMT</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>etnews.com</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>[반도체 라이징 스타]퓨리언스, HBM 공정 수율 높이는 포스트 CMP 세정 솔루션 고도화 - etnews.com</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE5LTWE2OHJCOFhrTHBlR003R0ZzQU1RblJ2OTVWMHlhdlprMEdRek0zeEI3b3o4TUxmbXRLRUtDVWNrTWFTN3FZd1diOGxaQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 05:14:00 GMT</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>서울경제</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>삼성 HBM4 ‘황금 수율’ 달성…공급 늘린다 - 서울경제</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9kU0ZBOTF2WWpnUm5XeXZIUVZndGwxdUs4V0thTUxBOWczek1sMFRadF9zd2t6UTNYbWlYSTVfMENzLWYtZXRvVmozZnBKcHByMWfSAVNBVV95cUxQVUkwSlQ4ejBQa2dXdklEMlpoWGRxMzZEVG5UQl9jaVpCeVNIUFN5cW11NUN0RXphQndEWG5ZWmhoYnZpMDN2X2VuMXl5eTBoQTRUSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 09:12:48 GMT</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>프라임경제</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>한미반도체, 'AI 병목 해결책' HBF 상용화 임박 '수혜'…"핵심 TC 본더 수율 검증 완료" - 프라임경제</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1vYkZxUmJKN3dzNnRTcTFsVFRWZmNnQTllcHlaX2Y1TzAyVnZ1R1Q5aHFucVgyWFY3MFkzUy1wTzBJZ01kcWRsUVM5ZlE5U3NLU291SmZlbGlsSk02a0lKb2swbm0tRWVPN1Z6ZA?oc=5</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 23:14:49 GMT</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>파이낸셜포스트</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>[인사이드] 'HBM 성공 주역' 구자흠 부사장이 밝힌 '삼성 파운드리' 공정 경쟁력 - 파이낸셜포스트</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE94UmdlUmxpcjdOdnFsTHRXSU1RTklsRHI5Nl9yR1FERXVrZEYtS3NpVlR0QlhnMG9sckF0SVZPVU5jZ051SWpaTGFfWUE2WmpWYmJ6cDlRdlhDTkM5cGpmNVR0R01NOTBUbTBUZWdCZHhpLXBZ?oc=5</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 02:43:35 GMT</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>뉴스투데이</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>[취준생을 위하여] (55)반도체 후공정 담당하는 삼성전자 DS부문 ‘TSP총괄’은 어떤 일을 할까 - 뉴스투데이</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE9NX3dGTlBDUVZkMEpVeWtKT2V0Wkd6VjVMNlRyb2xFSWNyUXh3WXpBN1F5dnhWM2pXNnlqTTBLalJKeC1uSUdETQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Thu, 05 Sep 2019 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>아시아투데이</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>파운드리는 패키지가 3할…삼성전자가 조용히 키우는 TSP총괄 - 아시아투데이</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5TeHpUMHlFcjJtVTdQLUZBYmw2aGxxRWpsOEM3QWZ6aXRfekhCZnI2RDZjU0k5UURqOEdOUkFScmdDWm5pX3BsTWo0RUxKS1dMRVo2UERuLW1DSWNvYU5XRDZOMWNiZ3YyZC1VTHRB?oc=5</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Wed, 05 May 2021 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>etnews.com</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>뉴로테크, G2셀 방식 TSP공정 장비 중국에 수출 - etnews.com</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE9XVU9iM0xmVjNvSzllNWZWTzhTd2p5Q3V3VUM1N0J5eEY2Qm12U2VJTU0zX1FwRW5ORmlDd3dNVjFUeXBVcDFzRzdXOA?oc=5</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Wed, 05 Dec 2012 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>녹색경제신문</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>삼성전자, “반도체 후공정 라인 무인화율 30% 달성” - 녹색경제신문</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE5Zal8tc1dsQ2c4cndLWVNacmxSUnlQWkVrUWwzTHAwbVRfcE8yUHlaWjNFeFYxdjJmSzh2amhiS3djUWxvRWpiZWdwNmJSVFBYVk5hTHNTa3RxeGFlY09XNzB6LVprbV9l?oc=5</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Thu, 29 Aug 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>라인/투자/Fab</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>지디넷코리아</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>SK하이닉스, EUV 공정 고도화…신소재 'PSM' 도입 시작 - 지디넷코리아</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5udkV1Sm5VbjNVcHBhMnNpWEQ0RWFEWGl5Y1ZfYm1pcHBFQmVUMjBTTDAtQ2FFVWpobmxHNTlnRGlhU2lyb1JERlAtX0tNeW9uUVNEZlBR?oc=5</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:50:33 GMT</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>시사저널e</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>SK하이닉스, ‘EUV 멀티’·‘하이NA 싱글’ 차세대 패터닝 전략 다각화 - 시사저널e</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9wZmJlM2pINExCSWIwMlktdXRmNnZVLXdPZmhhR01INzZEMm02YkplX2lUZ1ZtMDZYSWRZYk02Z1RadGlGVTQtVEtxbDRRakcxTnFpOWlnN2F5eGtCdGNtN09UT3VrVzJYNTdVcjdYMHBnOGpna3fSAXZBVV95cUxPcGZiZTNqSDRMQkliMDJZLXV0ZjZ2VS13T2ZoYUdNSDc2RDJtNmJKZV9pVGdWbTA2WElkWWJNNmdUWnRpRlU0LVRLcWw0UWpHMU5xaTlpZzdheXhrQnRjbTdPVE91a1cyWDU3VXI3WDBwZzhqZ2t3?oc=5</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:19:47 GMT</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>플래텀(Platum)</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>어썸레이, 75억 원 유치하며 EUV 펠리클 사업화 단계로 - 플래텀(Platum)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE9rX0R1SDlkQVU5LTQwREJJMVRWcnU1eVZ6U1MzLTFsWmFIc09XX2k0Y1I0LUJlWGlGb1BsbFpGc1gwU0ZIMXoyRA?oc=5</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:21:05 GMT</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>칸(KHARN)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>어썸레이, EUV 펠리클 멤브레인 사업화 본격화 - 칸(KHARN)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9PQ2pzZFhacU9yY2ZzeDd0U2lBandzQlZOcUR2MjN1NzlPSEpGeFFoOGdDNUF5Q1JoRkFLQjZETGt3SUZJZUxRTjQxTmRidTlXa2hBb0Zn?oc=5</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:33:08 GMT</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>점유율 1.6% 대만 난야, 15조원 들여 EUV 공장 건설 - 조선일보</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxNdXFKcDhYRHlmUkZZa2s3VGxfaTZXa3RkVGZtLXowWWl3RGxnOFIyU1JrcENLRW56NmpqMUJIazZUZ0JGNThIQjhEVTc1WldLWklCZXlWdEI0TzVDRUQ1a3VYcTdZYXY1c1N0Ync0QzhaSlFRTmJKUGVla1lvaTdaR0tUOA?oc=5</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:09:47 GMT</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>인텔, ‘하이NA’ EUV 실전 배치하며 차세대 파운드리 ‘속도전’… 삼성전자는 신중 - 조선비즈 - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQb3R5cERDWGFnYmh6T2wzTExKRVpZSzVkdFBEWXdXTTZ1R056Rm12cUpQdVBHZE5jVHhJQW11Mlp6WDRNTHdwZ1B0d054dGJqY25ZMHIzbDlyQzRKOXVIZDI5enZXZzRsNDVtNW5sLWhncm1VNHdjV3hVaW14RmRNLUVn0gGWAUFVX3lxTFAtOV9INlRKUHl0VmI3aXd4SHpMTXRKRGpGcXRiUWJnTjlJdWs5c1VZWjFHUEFZQnBQc2hDVE4zTzRKWnZlOTJHUEs5VlR6OXdSUlVoZ3BnQlFqdlF6dlE5ZW5wNEFYYlp2cW14M2kzTlFhcTRvQ3BrcENkVmFsVjZmOXoxY3hLa0FKN3Y3OEZNMzBRdHQyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>High-NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>수천억 하이-NA 도입하고도 속도 조절… 삼성, 2나노 수율 잡고도 양산 늦춘 속사정 - 글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPMDZhMW9DVWpJdFBaX0N4ajFaTDFIMTZPNklLeWpnZWVXTlBWc2dxdkE1TzgzOE1vNkZiamtveU5xWmhxMnV1T3U0eEgxMTVLOWJCemFsdHdqcDJIUHZUMHR6Z2FiWl80RU85YUI1UlVJemJCN2ZWREhMT1ItVHIydkJRQUQwSkJW?oc=5</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Sun, 19 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>High-NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ASML "하이-NA EUV 양산 장비, 인텔이 첫 승인" - 디일렉</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5yeGgycFJhNmtxdS15cGZWaFdjOTFrY2dVVzJYTnl1VXI3UWdRTEtuTDRJWEtZeVE4NnFCTHlGXzlidjlXd3N0T08xVEk1eEFaWGZ1QlN0NXZld3plT0M0b1ZHYjlOUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Thu, 29 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>High-NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Spherical Insights</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>반도체 Etch 장비 시장 크기, 공유 및 예측 - Spherical Insights</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQbm9iMmNjd3VSUEZNWWl3NmFBLVFxbFVsTERCUUZTVUpwdGlaVG92TGZ3eVR2MHp6OUdaZVlOMEFhQ0ctUlg3VkFjOVEydEVhcVVFQmFjOTMtMmZma1kzb1dYNkJvczRrcWFwUFk4ektKWlhNMTdBbjNGc2RydHBPcGo5c0NtVXN4cFlYcGp3?oc=5</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Sun, 26 Jul 2026 01:26:35 GMT</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Dry Etch</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>잡플래닛</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>식각 공정을 지원하는 쿠어스텍의 첨단 세라믹 솔루션 | 쿠어스텍코리아(유)의 비즈니스 뉴스 | 쿠어스텍코리아(유) - 잡플래닛</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wJBVV95cUxPMGtDX1ZWMXgySkh6R1RUd3RrbG9lOU9iM1pJcTdVNUg2WTJYQi1uVUdWWkxXY29GR2k3VmNrRDNJc2JzeTI3QW5nOUtWYTVSbXdqc09tOVh6bG1zcXc4MXUwTHYxQkk2NGhFWTJoenVsRnVzeXJ3djdRck1RT0IySnUxcmxzc3otSmFDMlZZaXZHVldCQTdxVHUzNnRFc3Y2QTExNTc4YTFXQjRhY0tzQ1JXRWpMc044Q3o1UVZIeUxnR2hzaTNQa1U0a1hVMmQzSldQTDhMQ3pMQlhiX0RUU3ZwTEZheFVWY2IyazhZLVN0Zll2cGNleVFhLU1IaUszMkwydWpBVWhhR2VhSWVvRGpUWENWVkV4a3RKazhfbU5OY2tPSWFfb2xrZUhaNXIwMzJRRmRxX2xfSVU0X0h5VnpVQkVDaVUxbUNtX1htYXhVSmxhV21mRWpKbEJvSW5rRjZmN1hIaHhkWWM?oc=5</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Dry Etch</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>elec4</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>[연재 기고] 반도체 및 디스플레이 공정에서의 친환경 건식 식각 기술 동향 - elec4</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBPaEVKc1Z2QVlsNERfb00zLVRac2ltanRBQ1pGWmpZMHNzNHNMQnUyRFVhSi1hOWhYUm53Yk1oTFRVTmtrNUg3Q2t1LTBqVzJpbDJKR3BDNjBadmR0d19OUi12X1VHTldwdXhJN2FR?oc=5</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 02:14:47 GMT</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Dry Etch</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ppss.kr</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>미세공정의 열쇠 '플라즈마', 반도체 식각의 한계를 깨다 - ppss.kr</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBubjJlUVBtTnhLRXZubVFQa1JFckJZMGxqaktMUS1WWWpaY2JSdE1zSnhmaEJsWXFGUjFhS2RYd0RYX0xWZVlVRy02WmhKQW5rUnJ3ZnVjT0w5VURjcEpwMURKVk0?oc=5</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Fri, 05 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Dry Etch</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>한경매거진&amp;북</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>반도체 '쌓는'시대, 칩메이커 뒤에서 조용히 폭등…식각이 뭐길래[반도체 8대공정] - 한경매거진&amp;북</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE43MlBUYTM4aHB5OVRhT1JOQ3F0cjJWa3NOeVNDbEhBNkNsck94RnJjS294V2hETHpWcnR1SHZpNV9kejkxTU1LRGNjYW8zb0FXVVpzR0dxTk04VERpd21waGJjdThoRFVWbzA1dg?oc=5</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Dry Etch</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>시사저널e</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>삼성전자·SK하이닉스 증착 공정 ALD 비중 늘자 주성엔지니어링 '방긋' - 시사저널e</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1zQlh2Q09LVjZtenJ6YV9lcWtWRDBaNlJXWUs4OE9MbGhjZGtjN256QjFtZkR5ZklVLXI1X2c3V2JkTmt0d2JIbUVTYkloR0dTdndUMnktVktvdk80X2l4MzFvZTRWeUxpS1ZTZHJVWUVpZ9IBdkFVX3lxTE1uQ0xXM3FYVEMyazJIV2swU2prcU90Sm5KNFc2MFJudHY1UDQ5U1BEdURCazF0bUY1UExVNlhTek80T1hUSFB1akNZRHRZZUlyVDhEWjd1NUlFbWpBMWVZUnA3aVNJbVRlWmNaX21lQTZyUmJtcUE?oc=5</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>ALD 증착</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>조세일보</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>“원자 단위의 한계 돌파”…3나노·300단 시대, ALD 장비가 뜬다 - 조세일보</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE92N3NYWnJGZVpwVWVsaXRuWHVFb1BvSE5tdDBGTDViN1Z6S2Y2M3FuLUM1cm5oNlM2OURrMjVwb1RQTmpVaFZRTnh2XzZnYS1PcWZPSzhjU1BYQmpqMnJn?oc=5</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>ALD 증착</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>어플라이드, 2나노 GAA 공정용 증착 시스템 2종 발표 - 디일렉</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5vakhtQ1ZRcndRNHMxMlRXNFZKa2RkM3NKenhtd1VQMmg2Ylk2SF94WTYtRUFneDJQbVBMXzUydl9JZTJoSU9td2Ftckd5NS0zUWN6cGsxYktfdEJ6R1d6RUFXcnFOZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Wed, 15 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>ALD 증착</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>대학지성 In&amp;Out</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>한양대 박진성 교수, 원자층증착 분야 세계적 학술상 ‘ALD Innovator Award’ 수상 - 대학지성 In&amp;Out</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9zTHh1ZmxiOVRuX0tBSHRydXdGMjFHMmpnWTAxQXFpOUJDdWVHR0gzQ3F2NWp4R1JrQmJBc2lObUYtUXlOZHBvNlo5U2hab1FTOXRScFBKWGFJOHp4Nm1RZ2dvNHUybVN1cGl0TQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>ALD 증착</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>녹색경제신문</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>[세미콘코리아2026] 원익IPS, "낸드·로직향 ALD 수요 증가 체감" - 녹색경제신문</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9kTWpGRjlUUkhKZ2dQY2ZsMXVHRkZscVhqNmVEeVpOaTlLcFdtc2ZQVEU5UllsM0swd1p6Y3dFRXlFdjVzdUpMXzhLR1k4NnRZT2tlQVVQUDRGQXFnMW9ZVjBoRmtFa1lO?oc=5</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>ALD 증착</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>케이씨텍, CMP 공정으로 패키징 영토 확장 - 디일렉</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFB6OGhXeThrSkdCWU1veENFQ2drcW13dzNsTlJZdTRJMm9Xc3VMZWhCMGxMNk5GOTVuWmduTFNvS2dsdkxHTlJ4QW1lRlRLb3l4UmhZNTZTMWR1S1hRUzlZRlItU3NDQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>CMP 슬러리</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>마켓인</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>와이씨켐, SK엔펄스 CMP 슬러리 사업부 인수…반도체 소재 사업 확대 - 마켓인</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE0yRWpKRmVIR0hDb25nUmR1RF9CMjFBbmR0eU1lcXA4SEZCc1RxWXdISmE3djFkLWs1bVY0S2s4UHZjQm1pTWNpVnlHTjB2dmo3c0ozVElTbEZUVHlJQ2xVZW5lZjhvbmZHR1BOSkVCVVR6SXc?oc=5</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Fri, 24 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>CMP 슬러리</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>연합인포맥스</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>SK엔펄스, CMP슬러리 사업 110억에 매각…사업 총정리 - 연합인포맥스</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5vRWxETU1fMnFoNVpYdlNHVDdVNEhGN2Q3cFMxZ0hvY0FxMU1QT1JOUXRBVHFHNm1jZ3laX0p3UGFnMFhMd04wVlkwbXAzOFoxcXFoUUprdTV1blo2NXRTejNQWWNfRkQ0bEVpVUtnXzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Wed, 22 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>CMP 슬러리</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>케이씨텍, CMP 기술로 日 독점 반도체 핵심소재 국산화 추진 - 디일렉</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBJWjBOTndxQy1NRmh2RHNGejRmeHkxNHJJNjN5Y0Q5SW1pUXEwcnlleEVMTVpBYUdLZzlFUFhMNk9MWDk4WTc1YXA1MzJScHA4cUZrY2w1a1VtalZ4eEtHenFYYmJnQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>CMP 슬러리</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>네이버 프리미엄콘텐츠</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>🍀(나노신소재 / 투자전략) “CNT 도전재·CMP 슬러리·TCO 타겟” - 네이버 프리미엄콘텐츠</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxQVmNHWDE4MHI3azBSRkgyUk5VMkpabXhLeFdTczBhdmlPd2xHNE4tRFJ5aGF2Y1dLSXFiMzZlbl9TX2ZTdGp1b1pJQjlSSktsVWxjWHNoSW5LOFBXeWRuZkczTG13RURGc29lNmptaDNiNUtwNlMzRFcyU01JNmlEUFhsRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>CMP 슬러리</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>교수신문</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>한국외대 임주원 교수 연구팀, 이종접합 반도체 광전극 개발로 차세대 광전화학 전지 성능 획기적 향상 - 교수신문</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9QVjBlQnkwdjBqbU96NzU1dU9HbVpWRUg5OWQ3TVlEanJDSUxUM1lGakhlZ1k0SXpkd0hWeW9zZmc3ZzdTdUNaWmwwVklNNW53ZEtKeEdPbzNoU1V4bzk2Y2tEWGRnX1k?oc=5</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Tue, 18 Nov 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>뉴스H</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>한양대 ERICA 이승현 교수팀, 차세대 그린수소 촉매 설계 전략 제시 - 뉴스H</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1BM1FLUk5rX3NEcDczZ25xdjBsN0lTVUtNZnBVQnphaEZ5MDVpNFJMMlZBN2doN21WMFhvTTBuLXZ3S1hJYzRvMTV6Z056M1NNZFJLUGNtVUxEZnpXN2ZFdTRKM1hvRnlWQW9F?oc=5</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Mon, 08 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>토픽트리</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>“주행 중 갑자기 멈춘다?”... 현대차·기아 차주들 10명 중 1명은 겪는다는 '이 결함' - 토픽트리</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQQnBDcVVxU2Fxa3c3ekx3NTJoTEtQNWlCZFJHdWlFRHZ6R2NXRHFzVDRVQk5nLTVoUWZwS1pGSHBzZmZnQ2RSQk5UUk5nVWkzdTU1Q0ZrVGg2WXVMbkF3WUl0RjV2VEpIVV9GUEpEYUNpVnAwOUNNdXhqT2g0ajRVMtIBiAFBVV95cUxQQnJ4MXJYNEZ1cVo2ZnZjZ29IRXBsT1l3WVNMSVhLOHg1QlJFcVI1dGZUbDd4LXdzNGpjOHNmcEtHNGt4dTVKRVkta2tKaE5hQk54OUJGZGJPUzhkSHJ2b2F2bWhyb3Q1c25sODlPRVR4bUNyMmhlMTg3RGJYeURkdjNQZVZVdm51?oc=5</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Sun, 22 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Korean Car Blog</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>현대·기아, 독일에서 15년 ICCU 보증 발표 - Korean Car Blog</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNRTRpVG9MaXIwaEJwS2pIcjd1dnJIODJTZGxBbElCdWhuRTQtTGhoTzFlMDlpN3JFMUdnb2hrZ2FRUXdRYWNQQ3V1UHFXVTYzbVZ2blhSRUJ2UHZ0RnhFU20xdGVsdGtZS1NSbFNUNmtlWDRFRkE4VDRhU2VBbXRUYXNONThFeHItdmhuTk5SRkNHV3ZOQUVPa0JEVWNHMmM?oc=5</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>뉴스프리존</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>한양대 에리카, 차세대 그린수소 촉매 설계 전략 제시 - 뉴스프리존</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE44eEtsRzZtNmNEQkl1NWhnbkZORUEtM0dJM3B6UHFxemdBMWdaNUFvT05mY1ZYNXdhc1Q3MHdLRGkzamVSMzFMeHJvcjZibFJLVlNTaTloUEwtV0xpbGtaR3VtaFExdnBTZEJOVjVsUWdoZGPSAXdBVV95cUxOYVFVdFJHZm5sYl9tZEV2d05pSGhyTm5RdFVNTmFFQzBRRWQxbVNfb2tTWDJndWlpcXZWa1lhQzhxWVBZVlZtb1lucWx6dVpHcE9oOWpJNWRZamNKbi01Ym5SZXlnUFlrRjk5S3ZEdXRZZ2FhcE40SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Wed, 26 Nov 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>마켓잉크</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>티로보틱스, 진공로봇 하나로 여러 챔버 연결…평행링크로 팹 공간 줄인다 - 마켓잉크</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1FQm5jZEdzampnNVgtRlAxYVRacFl1WnJFZmRXaDRyTDd1T201YUE4cEVMWkVRR1VySWg5TVJlc25zOHRSQ0RGR0tackVuSzRobnduQ2RiQ29ySzNnWXJVOHc1WUVMRFZQemdOQU1R?oc=5</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>챔버 파티클</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>라온로보틱스, DD 모터 로봇 앞세워 신규 반도체 고객사 진입 - 디일렉</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBRVndaMmowV2l0SEhqSXYyQWFOTzZVVVNTRmJPT1RKZGdpaTJRMTZfdEcxeHdOQ2pQSFA2SzdzeFpSUGdMNzBPX2JsbHQzTXVHSnYzdkdLbGdwVUFZNG5fLVFrSHBWQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>챔버 파티클</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>칸(KHARN)</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>신성이엔지, 차세대 반도체 인프라 신기술 공개 - 칸(KHARN)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5TR2llQTlZMXZqRkhjUG5acHo3dG9uRzZZa1FvMjI3STBYMDctcXN0OW9qUUhIRVFnRW1kdzBJQVBQR0thcnRqem50NzNBUXJXdkNCV3VJMU56bDA?oc=5</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>챔버 파티클</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>etnews.com</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>신성이엔지, 습도·정전기 동시 제어 'EDM 이오나이저' 공개 - etnews.com</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTFBXZWFrYUI5THpVSmQxNEtEa3luMG9pbzlnU1N3Z01rUzFHaElYbE1YQlgyeERIUVRKNkU1RFZPM1h1WGtYUnpVdEM1Qk9NQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>챔버 파티클</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>헬로디디</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>ITER, 핵심 제어기술 첫 실증 무대로 KSTAR 선택세계 표준 검증 플랫폼 입증···韓 핵융합 기술 경쟁력 재확인 - 헬로디디</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9mbHRlQlU4amdZTXlxQ1VJLWRrSmY0anFHTnh6ejhxMXNJZmtKV2k4RU9ONGFiandSWDJPMDRfdExLa0ZZR2p4WDdFY2pfQTFaM0xBX1FnWXVmeXpHckZNVGx6MVhOU2Y3UWc?oc=5</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>플라즈마 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>시사프리즘</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>[심층] ‘태양을 지상에’… AI가 가속하는 핵융합 경쟁, 한국의 선도 기술은 어디까지 왔나 - 시사프리즘</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBiZExPYzNpdnVIeUxMTXI3Y3RUWUlwRWF0czE3Q05yNXFRLVBxeDhnRVg4cTJucWZPb1JfTFM1VVBJTG1rTjZlNG1GZElUcXowR2tPbFBDTmpOOVdrSG5MODNkYVVqRU93?oc=5</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Fri, 06 Mar 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>플라즈마 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AI로 ‘플라스마’ 통제 쉬워져… 핵융합 발전에 한발 더 가까이 - 조선일보</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPUFJCWXB6cWs5cFZDNXFkMElJcE9vNkNTRHJqV0lobmNHQW5Nems3SGR0T3M5bE9WZUtORnI3SWhyLUNXUFZGQWstNlFfS1lROUV2Si1oZzdaSnVTd2tiRWZSLUxSZ1pMbEw1YVgxU2p3TFJNMDl0SXRHa0tHMnVLVTFhZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Thu, 23 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>플라즈마 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>동아사이언스</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>태양의 원리를 지구에서... KSTAR, 텅스텐 환경 핵융합 실험 본격화 - 동아사이언스</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTFA1VkpKMzhvUkVUTkxOT09EcXNjdVVpLXZUZHV3TXE2czVnRUlFVkh0bFFjYjFoRUJ3Uk05TDF2cWJod0xjV1hIZmJILWJJSDFUeVN3Rg?oc=5</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Mon, 27 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>플라즈마 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>지티티코리아</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>스위치·오버레이 구조가 만든 SDN 병목, PON 기반 전환이 해답이다 - 지티티코리아</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE90MkU0QXN2SzhqUmh5YXhCNXJpZWRUVkowRE5TX1VZNDFZbjVibTZ1UE5NcS15SWRKUEJYYlZqRmFjUVQ0d0R1M0ZEdzExX2NoRmNiNF9GM2c4N0NMdEZhS3d5RHhEVmczeEE?oc=5</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>pinpointnews.co.kr</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>노광공정의 핵심 '오버레이 계측장비'… 오로스테크놀로지, 기술력 입증 부각 - pinpointnews.co.kr</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE8tOGJiMmNETUU5UUJSeDM1T3JoZzJ2anozeF9RQzhZUHJZT3F3ZGRUV0QtcFQxRVVQYWtPcXB2QUJMNHBySEtYaFVwLTJZTWY5QThyVnQ3SjMyMXpORG4ycE5mV1JtOHhieDduRzZNYjlDX0HSAXdBVV95cUxNVFBRR0RWSmUwdUJBalVrSkxDdWdvbmRIU2RJWnl4S3lBUG15TmJFX0Z6QlpSMFJJY0hxdE5aRy16cmdmSkN0MlhPUEZuNnNuRzJGV3huLUFDNXJRaG5uSkVmM3JsdFUyVXJGMGJJV2puMGpWQW1rQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Mon, 04 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>elec4</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>[연재 기고] 디스플레이 공정에 반도체 노광 기술을 어떻게 접목하는가 - elec4</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9ZYUNoUkhPOWFvUXdiUzl5TWNoUmNvT3FCSGNKbjJ3VklzaTRGaTRyTFFLaDBLTTAzbFcxQV9sX2RBSkVKdUcxZjZDZkJueGc4QzlHVF92N3JGX0xpRVUwcGpiYVpEbGt3ZU0xQVJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Tue, 14 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>보드나라</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>엔비디아, 초고성능 측정과 오버레이 커스텀 추가된 프레임뷰 1.7 배포 - 보드나라</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE1JMnA0aU9OXzNwQm1oZEJjTWxjSmdnRndWSGFIUVpQX2swWHBuOHhjalU3UjFpRkF3dGN1UnVZeWJCeld3UXlIM1pCVUkwc1p4UEN2dEJuWVlrZTBod0FxU3VPRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>비즈월드</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>프랙틸리아, EUV 패턴 제어와 수율 향상 위해 스토캐스틱 제어 솔루션에 '오버레이 분석 기능' 추가 - 비즈월드</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE51UUM1MjdmSGw5NEpvbmlOam1KTUhoVWRxTEwtcnhJQmZvYXVIaDNUMm1tZ3h4QzFIaUF2aU0xMk9VQjUtZGs1UGdZZEk3TmY0RlpNRnk1SjFOYjNUNEo4S1IyT0tNbm56ZWc?oc=5</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jun 2023 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>PRESS9</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>롯데에너지머티리얼즈, 판가 인상·수율 개선에 실적 반등 기대-NH투자증권 - PRESS9</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE84b0o3blZFUjV3b1o1TVBhZDYtUHo2QTlodXpzMTNTSlV0czNjc0RvZmhhRDZVY2cwZlp5cVl0MUFVRzNCV3JkR1JDcHMyVThId0hyZVZSYTVIS2U4ektQd1ljTm5LZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:50:13 GMT</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>마이크론, HBM4 램프업 순항…"내년 HBM4E 양산" - 디일렉</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFAzd2NNeXN2YTE4dUMwMTc0QWJrdWdSSmVkaktHd1lMY3QyaG9JNUo2blZ5ampqdHE0WDctdXVodE9oYXdrUHB3SG5YUUtqV0toeG01YkpORVhRMUp5R3M1dGdYRWlCQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Mon, 25 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>딜사이트</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>삼성전자, HBM4 연말 수율 목표치 85%로 상향 - 딜사이트</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1YOXJiM1lVZEc0RXlKeGhpOEJHQy1tVjlOS0xMbXI5cFE3R2FBLVNXV3Y0WTYzWnA4V2Q4OUJTcGp2NDdTZDhlSUg3dWlDa0E?oc=5</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>아시아투데이</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>[컨콜] SK하이닉스 “HBM4E 샘플 공급 완료…27년 본격 양산 목표” - 아시아투데이</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4yLU9UZncybXpsTDRfQ2VjUnRfdWVDdGthdnEyei13cVE5N1JOWVVVejE3WTlPRU1xNDAyMHliVEZqa093UVpFM3VmYV9KYU9DUG5vS1RybW1kdzQ1TXJOcDFWREJHQ24xc19yU3ZB?oc=5</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 00:49:39 GMT</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>IT조선</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>[단독] “손익분기점 넘겼다”… 삼성전자 ‘1c D램’ 수율 60%까지 개선 - IT조선</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5WXzhWU1d3OHg1ckluMzRkU3N6OGpnbm1ZbzFfWGJlNXI4enV2aXBFbGpWTUJDTTBlQ0xuemVOSTRWNHFiQW8xY1dOdk1OWFlhRlR5S3pmVmZmZmFVZGZFZy1sLWdwQmRGczFMRy0yWWvSAXRBVV95cUxPYXd3WW95MnRramRUelBZWGcycTM5cXU3SlJ0Vm1LbG9wd3M4cGFvUEJVQlRIdDdPR0I5SWpGOVJDbUtSMFBDbDhxdmlVMjdCU205U1JwUlBUbFNELUE4UEltZF8yUHZwZ2drYmlCWFRybHU1Sw?oc=5</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>daejonilbo.com</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>트라닉스, 글로벌 최고 수준 'IATF 16949 인증' 획득, “품질 경영 경쟁력 입증” - daejonilbo.com</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE9ZU25LTnB0V29Sc1BXdktLT3ZDdXlQb3pMUkxIUGxISmkzNHRXSnJyYWN3dUVsVlFaNkI5NXIwTlE4YVhYVUQta25VbEFPWVpyTTFWamFVTEdfSXl3eDNpd09tUFYxOGpxZVlPTjZUQdIBc0FVX3lxTE5rdi01QWFuQ19pMkhRR0lINmtLSkpCRUdhY3ZRdHhFa1NibTljc1JwM0daeGtkVG5ZLTFvMkFRZTdZUnVtbnhxb0ZkQjV2S1cyUkFTcXRwcVM1SWJxa2JDX054dFV1MkVZUnFERDRfV3RjN2s?oc=5</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Thu, 06 Nov 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>IATF16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>알엔투테크놀로지, 전력반도체용 세라믹 방열기판의 IATF16949 인증 획득 - 한국경제</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBPYm5SVjc2Vnk3bW5PWnZkdmQzQk00Q0VpUjNGY3ViNTkwV2wxY05nUHIxTnpoUENDYlAyQTlTR1hhOUtiT0NQbjdhQllYQXl4d1g0U2R6MG9tZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Wed, 27 Nov 2024 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>IATF16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>프라임경제</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>시노펙스, 베트남 사업장 '국제 공인 자동차 품질 인증' IATF16949 획득 - 프라임경제</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE9jLVlPS2UyX0pHSnBVajEtdUQwVmd5QzlNcVdwUUQtWXBIZFh6cWRROE15SWI0MXZGbjQxd1Vfd29iUGJxdXYtYk95OExyR3Rwa0RpZjRMT3dsSHRva1B3XzJSQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Wed, 24 Apr 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>IATF16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>에너지신문</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>시노펙스, 옌퐁사업장 자동차품질경영시스템 인증 획득 - 에너지신문</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBZOTVkY0NxTlJ0MmV4X1RnckppbEd4NW94Q3c4ajZZU2R1b2pSb3lzVnhoaEhTMXJqNlp5VnY4VGl5TmQyLVQ3Z2dQaHFJWmxjWWphUk1oX2xoLXBscW8xZUhpelBzNzVLSGxlazRXeVBtdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Wed, 24 Apr 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>IATF16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>센시리온, 전기차 배터리 열폭주 감지용 수소센서 공급 - 디일렉</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE0yYk1IeEZqQXdiYUtyNUFfV1JTM25LcHBYVjh3TVY0R3h0SmRHWUZIOXByeXMzWlRCdXMwY0IyMlJLRlE5ckhSTkxuSmRjQUZNMi1XNGZabm5IQXRJX1hZZk1pSGV4dw?oc=5</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>지티티코리아</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>전력 효율·AI 인지·기능 안전을 결합한 차세대 ADAS SoC 전략 - 지티티코리아</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFA3V0c2QXcxQjk4OWppeEthNUlNMzhIVlBoaF9DdzRNNDhibVpPOHFMTmQ4d1NlTlJTVXBkcXdjZU1tMEx3NXpNRm5tcFhkajFzNFpoOHBLbG8yNGg5Ny1CdlhNWS1OSFBYVmc?oc=5</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>elec4</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>전체 애플리케이션 영역을 지원하는 차량용 게이트 드라이버 - elec4</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9XdHV5a3JjaFVEYTRZVHNaREVEcWpfemFXVzdmN2djMV9DTWRpSENsR0sxZllGLVk3Q1BsUllCOGktZnB4dEZrZnJWNFljZnpJWGNYa3RHUnIyRFMzczhieDZLMS1KYl8wVHRGZQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 05:06:09 GMT</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>hellot.net</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>ST, 자동차 배터리 효율 높이는 선형 전압 레귤레이터 출시 - hellot.net</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5YRWlyOFNkSi10RnpGaVFvdkNpR0FGNWs4OGZHclNRZmVMTFhFbkZPVUtBOFBGQTJnUnhPQjBTR0pOS0ZQdnVpbkdteU9CZ0RhbkxCU3QtLXF4bTZX?oc=5</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Wed, 01 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>퀄리타스반도체, 자율주행 ADAS용 MIPI 서브시스템 IP 첫 공급 - 디일렉</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBMNy1NeXRPRTVRQXh0UXVjQVhMR1BVS2xHbXllQzhmTzN4bHkxck1Rb3JiSG1GWkdoeFhIU0QtUndsbUowcXJWQlRNaFpXQnRxRkJKLWp6aU4yekdaQy1oZk1UYjdMdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Tue, 16 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>머니투데이</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>'칩 설계 솔루션' 잇다반도체, ISO26262인증…"고객도 인증 효과" - 머니투데이 - 머니투데이</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBYTUREcWJHZFk2aTdhSkw2VW5wek1ndllIRnl2QmpKeERTSjFkZzFXSDQwTmo5SHp1WmNBNzV2OWN3MFV1X1RpZ2E5RG9IRW95RWFtR2V2WnZhNmR1YXZNSzJFZVhCV1NPS1HSAW9BVV95cUxOMnZJeUNSRThYSlZkYTRnTjhUaFl1Rjgzb1k0ZktKbS1ISWRhN29rX09sSTJ4ckJ6NDJuZ2FGcEhDQXRBY2RrWUxDTW9ORnlkV3VSRjhOTVlUTGlNN01pa0NIMkd4TzVrZm10Sl9xd3c?oc=5</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 차량용 D램 'ISO 26262' 최고 등급 획득 - 디일렉</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE0xSV9lUWFSeE0tdE15c1VEM05qQzVDc2hxUUsyZ3RqSHFfM3BrS01PTFBWdUxnZV96eHNwdWg4VzlMNTdqbE9VdDlyeDgxSUZhUmtWNENhb0g5UWM4LWxsMWdUbEdlUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>TÜV SÜD</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>TÜV SÜD Korea, 하우엔지니어링웍스와 자동차 ISO 26262 기능안전 및 A-SPICE 분야 업무협약 체결 - TÜV SÜD</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOWEJiLU91RTJFemEyZGNPNEpTdFR2d3VTdGZYU3VZM1hKdXI0OGVyU3Z6aVQ4bzhpRE91c3pMYWE5TVhucEFXY2xQYi1WaEh5MFhfcFhJck9yRzEwTl9DVUFndkFuSnJDeDVwRmZKZnByaGxsc25LaFhCS2RpalNWaGhTVnU2TUpEbUU0b3VKTmxSUVhaRWwzQk5ZQ0VZSUdaV0VXeS1fdjhJU2g4Z1lB?oc=5</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 06:53:16 GMT</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>IT비즈뉴스</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>현대오토에버, 전장SW 검증자동화 툴 ‘ISO26262’ 획득 - IT비즈뉴스</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1FOTFRMVdNWi1HQk9WLTdTUDhvR25wazhiZXdzcHRpNFh1ZnBKeGJtMXB3UzlIbmFCaUxWS3pwaXRGWUU0UGRhaEdvRHRUTGJWeTRUSXAxa29jUTZ6NUxGUXozS25WVFFQc0Vpeg?oc=5</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Mon, 26 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>KIPOST</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>TÜV SÜD Korea, 하우엔지니어링웍스와 자동차 ISO 26262 기능안전 및 A-SPICE 분야 업무협약 체결 - KIPOST</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9xMUFlQnNHUXE4X3g1ZTZPNXJ0ZERWc21kNmdZaWxtUV82WlBsYnM2Mm9hcVY1NWhVOW0zLWgyNjFkM0RLX2ljRzk1U1JBeDhMeEhJUGR2M1ZDT0llcEZGUUh1VEstSFpr0gFsQVVfeXFMTXFqUWtnS2NOb3VxLVFFZ1R2M25KNmxxMS1MZWxSczdMaWV2QU9zM2V3S215T3FHVGFrU1ZKZ3RWMjZFVTlWam16SnFibkNmQUFHMGh1UG5zdmhvSlRORTdKSzdCbmlDNm1OTHZf?oc=5</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>autoelectronics.co.kr</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>[구태완 테크 칼럼] Safety Analysis: 귀납적 vs. 연역적 안전분석 - autoelectronics.co.kr</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1KN1FSaWdHRGk0YUlSMjZkbjdLemtBemNuLUpUMnJIa3FJS05OMVdGeFhKRTdWZk5zcUh4SlYxR3hvcUNfbkQ0Z2JUVzV4VmYyV29CQkp6OFZmUThUNm1faFRLdHVoWkhzOEJfMExRcUNUTHhY?oc=5</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 01:10:17 GMT</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>한국식품의약신문</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>의료기관평가인증원, ‘2026년 환자안전 현장지원 활성화’ 사업 시행 - 한국식품의약신문</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBCZ3JBYnFsSWJLT1BzOHNFbGQ3amtDOXdrTW1hTmdIOGxyaDBNdXBpUVIxME9MXzB5ak5JOHJMZ3QxRzNkRXZuekdRYjhkTnlHRVByU193cHJEOElQX2ZZeDllVWxyWXM?oc=5</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>테크수다</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>이엠포커스 ‘스마트 FMEA’, ‘FMEA 360’으로 제품명 변경 - 테크수다</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQaWR3TmJPUjRLeDBaZEMxQ05meXZ4aXd0VnFzUnQwTmdKQnJlcTZRVjhfdmJCVXU4cU5lTWpaaXc1ZXBPMTlvcHV0LVdhZEI1d2x6cktOYlpxd25rOGhNSEtWcnlyYkw1Y2NiSEl5ellLUlcxY0JmY2Q4YVlob3VWVElWbmpFTHU4clFUV2JmUENpd9IBlwFBVV95cUxPREVZc0FjRVJodDBiZDVabVNkcGx6UW9nbUwtaVZXMmU5RnlmbWNXUGZad3E5OTFzVzlsTVZkRDhrWkpVOU5QNXVaSXB3Y1MwRTRuRnE5Z2RIM1pBXzQ4V05COTlrSHR1dGF3Q08zSVNINDB1bFhvcnI0YWp1Q2UxQmFxeUlqOEUwUy0ybDdKdEVobEZ2R1RJ?oc=5</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Wed, 14 Feb 2024 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>뉴스와이어</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>이엠포커스, LG마그나에 FMEA 솔루션 공급 계약 체결 - 뉴스와이어</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBXTE5xN3QxUmtBVnM5UmhxXzRmU3FudkJYUjFmbUNVRVhrMHR0ZHhVZDRzVVo5Z0oxYlVrWnc1X3M4bkFwc1h4TmhTVTB4bWtkWlQ4SldBWFozaVN4WVE?oc=5</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Tue, 11 Jul 2023 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AIAG-VDA에 최적화된 ‘스마트-FMEA’ 솔루션 - 동아일보</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBwb3hnTmVBTEszXzBFMGhKZTdTV3FfSDB2dWh2TjVtaVpHU0NPX09TZTN5M2g1Z1A5Qk5CY3g5N1ZFUGtSVHBDSEx3R2REZEROc2JZZEltZHMyT2YzMUlqYmJieTRIY2hjOGF3X3k4VVhLM1M1LXfSAWZBVV95cUxObUJjU1NjUldKNkFJNTJZenVmSUFMRUhIV1p2OGRYVjdaNE53VFdfdDl2WGE4RmtQVEZJako4R3hWb3lhRmw2em9aNkZDaExwY0h2Y2gtMUVvd0NLY0VnSFJrOTdDeEE?oc=5</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Mon, 31 Oct 2022 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>epnc.co.kr</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>세윤씨앤에스, APQP 프로세스 관리 솔루션 ‘와이저오토 포털’ 신버전 개발 완료 - epnc.co.kr</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBkRTFOV093MXF2Z3QyLUtRWGlFTmVGOE1lTUVCNkkwLVJwNGp5RWNqdi1jSWxPclNxakhlZ1NnaV9FZEk5WGtDZl9WSG5DMTVkWWtoQXlBLWRQUnNGcGQxSXJXTkFkM1k?oc=5</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2015 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>APQP</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>'PPAP' 피코타로, 15세 연하 모델과 결혼 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE5UT1F5ZmFwM2RNUnpkY29aMFdiZE56eHJQTllyaGJjQ2Fna21oS0Eta0h2Qkt3cW9CUk4xMXJtRUdrOUcwQXc?oc=5</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Fri, 04 Aug 2017 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>PPAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>연합뉴스</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>'의외의 조합?'…日 기시다 외무상 만난 PPAP 아저씨 - 연합뉴스</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9wY1hZdEs0U3E3N042OGJBTWVLX05JOWcxSnRta3FPTzlOazFRSkpnYTRBTEZNZUNvY2RDb243T0xDWkNMYnVLZ1o2eXFqbjl5NDlwU05qS3M1bjQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Thu, 13 Jul 2017 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>PPAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>중앙일보</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>'PPAP' 아저씨, 유튜브 스타로 만들어준 저스틴 비버와 만났다 - 중앙일보</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFA5MkNndW1lRzhEOHlHSTlzVDU1MVhxWXVnQXFjMlNiN2R2dXM3ekI0eThfdmw5VUNrdUdyVm51Zld4c0Y3cmstRS1SMlRIWFpZS1ZHWEtR?oc=5</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Tue, 07 Feb 2017 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>PPAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>문화일보</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>제2의 강남스타일 ‘PPAP’ 아시나요? - 문화일보</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1sS2hXYjBkaHZCX3BXaDc3cDZIODRLR0NiYTNWNFcwMFMxRXRidm55TmVIdVFNaUVKMFBMQkh2dzNKY1FfdEZVVnVfSlpGTkxl?oc=5</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Mon, 24 Oct 2016 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>PPAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>경향신문</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>트럼프와 피코 타로의 첫 만남은..."PPAP 부르려고 하자 트럼프가 '스톱'" - 경향신문</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5pMXNOc25OSFZRUG9vaS1JcVo1UUx2RkY5S05hb3NCMDRBb2YxY0JBMkppOGdQLW9fZWhJX3RGc052M2ozbGhSVjdLcm95ZXE4RUVVUGd3amZWQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Tue, 07 Nov 2017 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>PPAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>시흥타임즈</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>시흥도시공사, ‘ISO10002’ 및 ‘SQ인증’ 연속 획득 - 시흥타임즈</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBFd3JRUHlpMC1iYnBZdG9VZnBhY3dzNzhVY3o0VUFsSjJWbXE4QUNzTjB4QTZaQjd2ZjlLTHgtZWtXckV4aExlMks4QUhXMXZYV0IwYVk4UV8tRGVKRUNybw?oc=5</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>성동저널</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>‘고객중심 서비스 혁신’... 성동공단, ‘한국서비스품질 우수기업’ 인증 - 성동저널</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1DeUhnU09ka1JudDhqb2ZHZlgyb0RnOFNYTHA5NWVjYVRGRmJNeFVNeVRKa29TVEhmQk9OeU9tS1YySnpMNzY5aTN5Mk16Ml83dGFsU0U1eDNKNlVyQTVkUkFjMDdwbDdYUEFEMk4wTGY?oc=5</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>페스카로, JS오토모티브 인수 "SDV 수직계열화 완성" - 디일렉</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9sVm9KV09WRlZHaHc0TTI0U1Raa0FxSU9TeGxnUEtsWWZTVWVqQUhSQmZ1LWJERDVXZDFJUFhEUmlWcC1NOTJDVzNHOHRyMVlIZlRNNHVabERwYm9pSU00VUw0eDNTdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>localsegye.co.kr</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>강원랜드, ‘한국서비스품질 우수기업(SQ)’ 인증 획득 - localsegye.co.kr</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE94Sk5kRVJEUzdXRkRJcG93djQtUGlLOVBKdktfWmtRSEVXV0ZIS1N5UG5tdl81a3ROaFFJcUtybE1HYXFUWjhNYkg3UmpPQ09lMW91VDZqT0FqRnNOTFBSNNIBWEFVX3lxTE5Jb3V6c0RCNm5XajZST21WQ1otQ1RBRTJLWlZvekZmekdLcTVWU1dsLXEyQ3lCOXRTQXkwbVV1ejAxT3VZYjM0di1sWVZNMk5wUTk2SU10OGc?oc=5</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Fri, 17 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>내외경제TV</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>부산시설공단, 한국서비스품질 우수기업(SQ) 인증 취득 - 내외경제TV</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9Td3d0MzdVTndmM2FIUmQtajl3QjZxV0pHTXltaW9mVmctRjVLbEd1Ni1qekQtTXRULXFBY016eXBKTjlySTZRbFVCU1ozMThfYkRDNWRteUxJQmM1MnlCbEVNZlp3LWQwRzZv?oc=5</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>더스탁(The Stock)</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>디케이티, 휴머노이드 초단기 진입…'비결' 본업에 있다 - 더스탁(The Stock)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5NODRjZzdNX3FVaW15WjlBWm9hcUtFUldocmttendMZzhtMGR4bVJVdHFFZW5aQk9sX3liWktTOVEzVURMaWh4SFlIdlMwZVkxeXJVS0poWEdoMHA1ODk2QkJwX1h5b3NESUE?oc=5</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 01:01:11 GMT</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>파이낸스스코프</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>아모텍, 전장용 MLCC 성장세 지속… 고신뢰성 라인업으로 시장 공략 가속 - 파이낸스스코프</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9HcTJwLWYycVpqR01iOHh5aHZRREY1UUtmNUFWa1V2UzBla2FucTlDbWdxSy1hLUdYMnBiVHJKRFRWaU9HSnI0dXdyRWZpblM2ZDFWejJPSVZza2RwU1R0V2Z4RHlibHlyRnc?oc=5</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 23:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>데이터넷</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>아모텍, 전장용 MLCC 공급 확대 추진 ··· 고신뢰성 제품 경쟁력 강화 - 데이터넷</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5uQVlKWHQ5SmROZ3BnRzFYbll1NW9ac2wxN1dZeGxjUHJ6alVTUFVrZ3MxNnhsRXN5clE4eWJ1NExvMENrUTJzV2ZScmZFT20wS0dtVmtXbWVrODRtc3owQ3N2VFZiSlJyc1psMQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:41:19 GMT</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>etnews.com</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>FITI시험연구원, '소재부터 배터리 팩까지'…미래 모빌리티 신뢰성 혁신 이끈다 - etnews.com</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE90VmFscmVXVnU3WHF0MWV4WEEzU1VCQWJVSTFsTWFQNVNRZHdFR2c3bkVKNDd4eld6d2toWlFqa2VmWDJKN0pCTzJCM0UyUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Fri, 12 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>IT비즈뉴스</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>SK키파운드리, 전장반도체 신뢰성 극대화 ‘온칩 EMC 보호 기술’ 개발 - IT비즈뉴스</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9HU3ZXQjJQY2l1RzRtamVJN1QzSV9FdnQ0a0w3b0RSNDdfYmJ0dF9KeGJaYUlIUVR3VzRLZUNUcHI4ODlTQzFLTkxUMWV3SkhWUHZ4R3YwTUxJSEFwZFFfZWR5UkZXX3hHZHozbA?oc=5</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>edaily.co.kr</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>링크드, 글로벌 완성차 부품 공급처 확대…전동모터 본격 양산 - edaily.co.kr</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQcVdLbzVnZUdTWkI2RHItLUNBQVVVRnQycEYtdXhDM2lPQTlnX1QyMTh0Y1YydlBNNGIxU2U2OUk5RjNLVEo2bGp3b284MVpERHpXOUkxdElOTl83aHN1Q1JUZnlZeEVobnNqODZ3QUcySUk4ak5pOHVaY0F0WGQwNw?oc=5</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>DV PV 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>더구루</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>리펑강 베이징현대 총경리, 中 자동차 제조사 '속성 개발·품질 관리 부실' 힐난 - 더구루</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE1wcXIyRldnMnJwaGdBZTFjNW9XNnRPY0xiYWVPZlpDZlkxWFdQcEg0aHRXMWUyS3Mxdll2RC1nRUxqbTBaOWZia1pORG8xRHA4a0tuS2d5blBfNW5mdEFjUHVLRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>DV PV 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>carmgz.kr</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>링크드, 글로벌 완성차 부품 공급처 확대…“추가 8개 사와 단계별 공급 협의 중” - carmgz.kr</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE1OQVNRX2RnR1hLTkJsUjQtd2wzZ04xRXM1S2ZEQjBTWlJlZnBlRnJFNVBWSDgyYzdSSlRmSHozcDRQUjFtTGR5WExDNkRBVG1aSnNPZENfNGRsYmJBMGROaUswV1dRdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>DV PV 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>dailycar.co.kr</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>‘OTA 패치’ 통하지 않는 자동차 시장..SW 기업, ‘장기 호흡’에 사활 - dailycar.co.kr</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBQYXpyU0UzZ1V1OUFEd1VQTV9HSEdkRGNsUTJFdjcxMDRxS01SVXpMbzJiYkJPQmZ4VmYtcVhJdGVZVkpwTmxINGF1NXFwZTNHc2dmakM0ODVuaDBMMnNmQTZxV0pSaDFwekw1ZjJfMHUwR1JoMXc?oc=5</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Fri, 22 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>DV PV 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>아주경제</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[단독] 삼성전자 HBM4, PVR 공정 통과… 선두 경쟁 본격화 - 아주경제</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFAwX0c4OXYyekY1RUxMVVhQUGkwdk0xVmFUQUtGS3R6RE5wM3ZDcDBBSzFyM0hlRllCRnB1ZTk2eGptNFFHcERoNHZWTS1MOFdoQW9MdThMWlpCZ9IBWEFVX3lxTE1xQWxYekNxVHdUTFNYc0EwMzRpYi1jY3pQWERUV29VanA1bld0SnZfRHItdDhIY2MyTTBPa285cEI0UlRPS2VHT3A2WFl4UUhMXzRQa2Z5dUc?oc=5</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Sun, 21 Sep 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>DV PV 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>brunch.co.kr</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>비우고 낮춰서 최적화하기 - brunch.co.kr</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE42Y2NSQ2JOYVNBcXdJZWpiVk9LR045clB6VmdzNmpuQmw4UTZ5TjdkcTNZWmxPXzBnbV9jeUxTQXdzQUtOUjVIeUhyQzNUSGFDSVE?oc=5</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Tue, 29 Nov 2022 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>필드클레임</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>뉴스클레임</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[식사합시다] 의평옥 - 뉴스클레임</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBBTlFJNGhXd01zOHRRbDRyZ2xyczNzY0pPZjFLc3Zfd2ZCcC13ejktdHdxREpoS0VxbTFBVk1KVGlaaDR0d0puYnpVbVhIUGlmMmk3R1V0eEY3UmRvSTlHV001NG45eUs0UzdaVzJlcE7SAXRBVV95cUxPbTEtSXdRTjZnYUpmaFR1cjI1ejJpcjZBVWhsZmlkX2Fvdmt6cjdaYUZIeUVyZk9yX2VFUEpmbUQtcFRtNzR3a0hfOEw4VzkwNk1wVVdaVTlXM1JqdEZKSnZheEE5NW1GMU9pYnVFZndMd21nZQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Sun, 07 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>필드클레임</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>전기신문</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>현대모비스, 설계에서 품질까지 AI기술 적용 - 전기신문</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5ZNWhsbGJqQmlqeVBBS2JYZklDYzJuUG50aVY4YS1BMlhYLTk5amNxVWlCZTJWdDA1Wnl1TGpsNGNyNVNpU1ZJdjhTNU03eDEzRHgtMjl3U0pGcDBud2Q0WXJIaGJ3RUdBTTdnc9IBcEFVX3lxTE5SSWRQbXdIT1pDdF9sY2xOT1B6TlYxYm4xcnQzR0k5Zm1uTUpmLTd0ajRxcmVPb09NRU5uWEZkN05vNFYyd3FNeUZzSmFSMVFHQUd1Y3Y0MUtOZHJkM2h6cElVX2ZDSUsySE9Qejg2eFA?oc=5</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Mon, 07 Jun 2021 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>필드클레임</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>동아사이언스</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>현대모비스, AI로 품질·효율성 높인다…40여개 기술 적용 - 동아사이언스</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTFBRM0NnY1VvZGZIRjdBdUItMWJreWZlblc0TTZSbFNWcmc1OG9zQUhPMzRuTXBDMjBwMTJOc09VMzFtR0JIUTkzY0xsZU9lWXM5LXFoTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Sun, 06 Jun 2021 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>필드클레임</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>EXCLUSIVE: China starts production of home-grown immersion DUV chipmaking tools, source says - Reuters</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxOR1Zubmoxd1FlV0N3dFpST2F0QUFhNS04Mlg5cmNUcndrWXlwYVFfSFZZODc5UzQxTWZiNzktWEZ6dlJfVm4xVXZWYUlSdndZUXFyNjNhLUZlWm9Zc3pSN001WmZFQWZRSjd3dFo0dmptM1VIbGg2aUhVYU9aNllfV3VkRFZGREJsczdOZThmQ2tidTJMc2dweFp3V1FWQ0hLOEIzaU9mMFRWWGhrUXoySUxST3VqekE4Rnp5Qg?oc=5</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>EUV Lithography</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>36Kr</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>All Eyes on EUV Lithography Machines: Key Trends, Industry Impact &amp; Global Technological Competition - 36Kr</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE5XY1BURlZ0X1RpaUplNldaV3hHWms2VU9xamVTYzBPYkhlTGxubk5QdmZpd3hXMTRfbU4xVzlCbG5aQkloQ0wzZDNiTXBNdGdiRm93?oc=5</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 04:04:18 GMT</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>EUV Lithography</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Tom's Hardware</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Chinese chipmaking tool roadmaps examined — Beijing's nascent lithography tools target DUV production at five machines a year, and an EUV prototype with no chips - Tom's Hardware</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOUExMQlZwd0hKSjZ4eVl6eEc1RmxjS0x6WDlrUjREMXRXa2E2X2pPS05KS0V1WjhPNzZlR0RlWmpROVhVT0d3a3hzcTh2NGZ3ZWtOaUlEbEJDY0dwVXFFNDNKeUc3TUlDai1PLTJxcUp1TWFETC1fZ2xRMU9ZcUtrNjhwazBSYXNacnZzbVh6dVp1UGg2R0dWZHltX3hrZTA?oc=5</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 13:15:00 GMT</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>EUV Lithography</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>The Korea Herald</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>aweXome Ray readies EUV pellicle material for commercial debut - The Korea Herald</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiV0FVX3lxTFA3QVMtSUtoSmJINGloNEFNMkJwRmJkNS0wSkR3X3FqYWpZdlhtNXNNRnlBcEpxMDVyYlNLSXZzMkhOOGRpSjRkQ1dvekVYb3Z5Nllka3ViZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 08:16:06 GMT</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>EUV Lithography</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>MarketsandMarkets</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Taiwan Extreme Ultraviolet (EUV) Lithography Market Size, Share,Trends, Growth Analysis Report, 2031 - MarketsandMarkets</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQREN5b3dsWTZ0N3B2RVZMUkRMbnpGeGl3ZHZrMkxJb0xBRDRDQTQ1X2k0Q3dxQWtzMjd5QXpWY0VNMHNrblRuTHpKSEVGY0F0YjhyOGpabXNISy03S3NHQzU5RUZrMDR6Wm54Zi1KZFJhbnduSjZlQi1fcW1DcHNxMzVQMTB3QkU4eWhvSXlhWlJ3eUtXeDN4S0YxbGtWeEhhaERvTmNiWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 17:05:06 GMT</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>EUV Lithography</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>AIP.ORG</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Harnessing sulfur hexafluoride for clearer and more efficient plasma etching - AIP.ORG</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQX1lHWWEtMkdJalJjMUJvWUF1TVlNdXNZX01ib3lPMjFxMDdEdUFURVo3cGRRenBxU0l0cmlIN21kb2VwQ1didFdISjQ4RDEyTW9RMGNybm1PTG5ja3dNalpKbXFtXzV2ZGV5UHZTUXZ5R3VoVDhUcDhCc3BVTXpwbHlKNzRidEZYMUVRUmJnMHdPaFZ1ZjAyUEV5a0VDZTNCbmNDVUhGZmszQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Fri, 06 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Dry Etching</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Wiley Online Library</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Impact of Ions and Radicals on Etch Selectivity and Fluorocarbon Polymerization in the Selective Dry Etching of Si - Wiley Online Library</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE45VlliYlVPMkJiQnh5Ry1zeklDM1J1ejNaQnBGNmxSQmt2TkNfNjV2X0R3dlgzWl9OZzJvWDlLM29FT011T2VNc1QwMjJ3d0p4REQxNlRUaEViVVV5QzdRbWV0VU5lM1c5dTdV?oc=5</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Dry Etching</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>thelec.net</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>ICD to Supply Dry Etching Equipment to China's Everdisplay - thelec.net</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBtcW9QM3lFel9MVC1TVWp5Tnl6LVUxcGVmNWFEZ0tUOEJ5OERRTDZiWUVLZXAxWS1fa3JaU09fbm1odEFBMFdqZmt6TWUyUG00X3dtQTZSVFZsdURKNmZoem9xeFhNQVU?oc=5</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Dry Etching</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Facile, etch-free atomic layer-coated resist templates for rapid prototyping of efficient visible metasurfaces - Nature</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE1GNDR6TWZwSFdVXzhJdmY1S3FReG5Pcl94eVRmYkU1TDdsUkpFb09lTmswTENNOENyQ1FmbXlXZW5KUlUtbC1mZG9XcFJUcWVEdzd1QzZlaERtZUMxM3hz?oc=5</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Mon, 13 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Dry Etching</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>EurekAlert!</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Ruthenium nano-TSV and all-dry SOI thinning advance backside power delivery - EurekAlert!</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE94OURudVp4T0dBTDhPZFhoUWxEWk5tb21KVC1yaGQ1T1NrWW40cElnQ253ZDlmX3gzX0pPWXByc1k2aExMdjhKVHc3MXJtc25yTU41M3ZkNnlhcVZz?oc=5</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Dry Etching</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Atomic layer deposition - Nature</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE8yU1BZM1hydWFIc1lLamo0WDY4emJRM3c2VE9YWG5zc1EyMGg4RjRqYVdEY0h2NzZWNlliME1XNElxYUV6SDZRTDBPMXptTUZyS2hDUzNCNVNiTFZSdU04?oc=5</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Thu, 16 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>ALD Deposition</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>publishing.aip.org</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Atomic Layer Deposition (ALD) and Atomic Layer Etching (ALE) - publishing.aip.org</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPbGwtd2YtblJPTXlpYUZZRWE0cHJ2MWRNM3pUWFhYRVhjSUEyN290X051RHl0eDAzS05vLWtzYVBsTVdYR3NFUHhRQW5JcFNwNkY5aWNJMUZZSndjT0lwcmZCZERpQmJfV0ZBdnFZTXBreDZMNFhtU3BKU19TOEpIbTF3SE1wYlNaZVF6MU13Q1NHd0NIT0Y1clluOGktOENaUjJPcjkwb0pWWTM1SGRabFFzdkRaaUpMUjh5YzBaUUxBWGhGd3c?oc=5</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>ALD Deposition</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Compound Semiconductor</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>KAIST-led team develops next gen ALD process - Compound Semiconductor</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPeC1ENklrcTd0eVVtQ195S1l0bUhHMWc0NG1BT3hHSng5SFNYN3djMUQ1Nm1SbzZNVm9KbGlGY21xUTdXTXNPU3RVRS1KZ2x2QVgzY3ViVGFIell1amZJSTNGbHZvTnFreGhoVDgyTFdUWGltRmRfODU1QUxrbjZFcVo5WHFFVndvdlVKLUZQbjhSbDdhV3NYZA?oc=5</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>ALD Deposition</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>AZoM</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Machine Learning Guides ALD to Predict Better Hafnium Oxide Film Quality - AZoM</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFB1MFN0WmE3dW9LWXQ3bFJmUXFMXzA3VGhwdHZuUWlWQnZTeGdkbWZVR0F5NTNzUU5aLTBGZWlPcm51TmN4UGNhaTJXWkl2UEJQcGR3RndR?oc=5</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>ALD Deposition</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Market Research Future</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Atomic Layer Deposition Market Size &amp; Share | Industry Report 2035 - Market Research Future</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQZzNfTkNvRWEtVERXYmJSNEF5am1kZGV3Wk5sc0pBMjlNVndmRGs4LTNCS3NoQ25tTmxFY3NGOTJnUVhTRGgwcUZRckhoUklkV3NxTy03M0RGc2VGbWtzWDVKX2VlaFQ5Uk1kSU1hRWd5ejg5VnU5QWRRWEdaODVpTEdtRkdqSWc?oc=5</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Wed, 22 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>ALD Deposition</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Fortune Business Insights</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>CMP Slurry Market Size, Share, Trends | Growth Report [2034] - Fortune Business Insights</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE05bUJKaGdaMmduazhfaWF5Y21EYzVvaDhnOUI4X2lMM1RmYkFib3FERWRxOWc0LXk4MExoa3RkbWVLakM1VWdibkpjZzVHTGJWRTNNNUJFSGxseEpURlBLeEJJWDRudzd5SzBXX0JPVVZyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Fri, 06 Feb 2026 11:58:52 GMT</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>CMP Slurry</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>AZoM</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Monitoring Particle Size and Large Particle Counts in CMP Slurries - AZoM</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBVTlRJYmNCelo3S1ZNV1lVOUJ0blplc2wtVWFZNGh0VVFucHBlREgzcUgyZzhDc0R5dm12aHFldXZhQ1B2UzlYZGY5elhpRWhCTVlVNzVmSFc0S1BTU2c?oc=5</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>CMP Slurry</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>A novel immersion chemical mechanical polishing device and tailored slurry for processing heavy duty gas turbine compressor blades - Nature</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE56NkpTc2UzZ2FYcjRNWW9SUWNWNF9kVHNUSnJLX2Y2alhDeU5uU3hrWFVsRXBibWx6cDFkQ2JJZndVV1dWVnJrbmFLUUYtRWsyNm5OY01NZHI3RUVBR0Vz?oc=5</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Sat, 23 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>CMP Slurry</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>DuPont</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Qnity and SK hynix Sign Long-Term CMP Pad Supply Agreement - DuPont</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOUWYyeDZtSHAtVlgtYjVXcV9xN0d0OXFtRURUV1haNTJzb1BQVWpIaUZORlhkQ3pmOWJFaDFDRndlY244M3lWWUdyQWcxMFl1dXlDdkV1cjJueF84UkNFV0gycHJuQ2RxZGxoeE9jbm15a2ZqaHRGUmZwU1lfYllVYkZGV09mMWV6V0g4bHlOV01qeHJuOUE?oc=5</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Thu, 16 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>CMP Slurry</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>thelec.net</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>KCTech Expands CMP Applications Into Advanced Packaging - thelec.net</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE5tVmJlS2hfVENjZFYyWmpvQ2l5ek5CU3Q0b2RtNlRWd1NoQjM4WGZuNkdubk5heVhQdEZ6ZVlSTDFkOGYtaVFjREFHY1hNNHNLck9pWVVPZWVGeU1ZUndTQXJfN25jWWc?oc=5</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>CMP Slurry</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>IndexBox</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Subsurface Defect Reference Blocks Market Growth to 2035 Driven by Semiconductor Sub-50µm Detection Thresholds - News and Statistics - IndexBox</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNQWYtelEwRHVwa09Pc1JwRXZDbTBuTjFFQU1Gck9qMVU3MndKZ2RCcjNFazk1ZWRhcGgtRzBTaXdRaDFLLWpFbjZDVml2UkdCUHpCQVJlTEpWS3dESDFiWWtqNHp2ejJXekkyTVdvYWxGTHdhQTY2UjZqMWNkTWpGejl4cUF6bWhtb2tNX2E1M3dNQThhLVgtdVhRX2VCQ3Bnczd0Tk5UREZxQUsyTGFWUWJDbGlSZUVwbDYxa0pBM1VLNWViM1NVZ3MzUnJXbzZ2TFp1czlLWVJOcDFnRllJZVd5aw?oc=5</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:46:11 GMT</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Semiconductor Defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NVIDIA Developer</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Optimizing Semiconductor Defect Classification with Generative AI and Vision Foundation Models - NVIDIA Developer</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPTVg1dGV0REp6VFczZUN3QXpoZS15dFliODhWTmFxX0xscWw5MnZYN05wMDRMRnlfSUxubjVIbWVoVW1aTTRGaVQ1YnluaGJYZHhsS3l5X05IaGQ4ejlPWVF4dmdERzd6RWxLZnZtLWprX2pUQ0RlM1VNYlNCZUhQWFIzYXh1UHpaUENlRWNFNmNTZWNWdlF6Tkx5WVdQakJDdm9NOThxbmpHYzBvTlpSNXNDUXg3OHFhZW9ZUE5zZGlwUHU2OEpPbQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Tue, 16 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Semiconductor Defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Cornell Chronicle</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Electron microscopy shows ‘mouse bite’ defects in semiconductors - Cornell Chronicle</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxQamZreFZ5dG5ZRkhaa0xET3ZERVZSaksxMlppeTZvU2Q3YnFyQ2pRb3EwWmFTVjIzeXl1ZGJGRml1Y2ZzeDh3Rjg1SHBRVHctSThkZWJCQzNTc1NCY1c5RTRHeUxBc09LLXhvcFdjYUtYQjU2WklUVUhTd0RmSGJnUXpoeVBySTRoOWhCY01GOUsyVy1LUFRoZl9abHd6Z2pya1E?oc=5</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Mon, 02 Mar 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Semiconductor Defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>thelec.net</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>iVisionWorks Begins Development of Semiconductor Wafer Inspection System - thelec.net</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1TN3Q1RlVPYU9YRnIwaUlNazdWSVl1OFBGMTA4VlpwbTA2LXlicEtaV0VzTlNDQUFpN3hVZUcxcmluNjBVRGdZd0VrQXUxdy11cFVzS0FtMVJoMENpaTBvR2Ewc21mUEk?oc=5</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Wed, 05 Aug 2026 22:40:09 GMT</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Semiconductor Defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Quantum Computing Report</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>SKKU Researchers Identify Room-Temperature “Spin Qubit” Defect in Zinc Oxide Semiconductors - Quantum Computing Report</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPYkJudm5YNUVXVGh5UG11aGpTSWl4cjRtVTJ2N3l4TGpRZlAxSzEyRHhUSzgtbXBhVXlNajV2dWl3S0p2VC1ZLVVMbGxhYzNURmJUMUpldzgtQzZrYU00a3IwNW1IOHZBbmVLRTU0X0J2TkxOVW11LXpJQW9WRXdLdWw4YW56cEg0NGtBbUEwR2otYjFzVHZqQ2JDNDd4QnRfUFN0SlN1ZndiNDZpa3RPb2RGdmlKOENaQjJIckhqdGpPZVXSAcgBQVVfeXFMTlFRaVhVbm5uSEZlTjB3ZnB4OFZYSmtUeDFrQ1pZQ1VjUFJmMW9iLW9JU29CVC05bG4zeXVxRF80RWZwVl9qcWt5Q182RktKR19LNVB4bUpDcjRBMWJRTUtVQnpKNWNVVDNpNUlKdXVuYU9IekpObmMybDVPbHNJY2FyY0NNejZ4bGlJeUdWQUdSZHZtQlNHM3I1U19pOUR5d00wMFBFTEJCR0NUQ3VIcDNsdGY0YnNLUGJXdGtleFdXMkNVdFViYkc?oc=5</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Sat, 25 Jul 2026 13:16:55 GMT</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Semiconductor Defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>BOJ may face pressure to ramp up bond-buying if yields spike, ex-central bank policymaker says - Reuters</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPOG0xd2F5WkRoZ0NtYlBoWnJmUDhXNmVSTUVFdEtKYUhZa1hLQVNaaFh2UXFsRVV2dWV1UHFsLXdUUjlFQ3JuWXY4RUZReDRUZDhGX01keFgyT2JZUzhvV0ZyRkdJUldpTElkN2lkMmlSbWVLYlhXSkdmMHd2ZzZJQXlHemRTYm5YWnJ2STh4SWNkeGN6LUJkNWdIcEFERUlzbXA4MVFNVERkODJobF9KVW50WGk4ZXI1b05MYmMzVENLai05eHhR?oc=5</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Yield Ramp Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Wccftech</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Intel Starts Paying Overtime Bonuses To Expedite Work On Its Ohio Fab, As EMIB-T Package Yield Approaches 90 Percent - Wccftech</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQVmxOdk53eVc4WVo1NVFXd3BFQ205UVZOWm5yUkJKT0cxVUdpSEdYM1JJOXRhTUFpWlNvMHM5ODAyLURZVXpkOS1weG83N21fdzVDM0Fpb21zejlsRVFuSVJHTFNzTTFWNkJJS3E2REpnRWNlXzdNLVJtQ0RqRXpFb05ua2t1amFKaVJqT25wcGFmQUQ5MFNneVpjR1VIRDF4V2NNRFVrUnk2Um9zNVc5MVR1YmJKOHNMdVU3dlcwTUh0SWd6RzBJYmVVX25UcWhSRzM00gHYAUFVX3lxTE82dFhJMUxwdW5VUk5teFFybU1DT1VCeDJ0ZzRHZ1NkYnpSbHJpVmMzVTFqSFl6X21Yc0JZN1NjODF2T1l4TXA4bG9tem80UHZZZ1F2aWhzaUEwa0RRMkczdDQ1YzIxdGlabXRzY1hPN0lzTmVvYmNZQmxKdDdXbHVVY1dxTzhwRnRpM1RfLThpSGlpV3VRYnNhSlVGOXlleW1xZXV5OW41eFIyazJUOHBwUDBIY3ZUV0FwbGpxdS1ibVJvU1Z6NWdxWnR5b2ZEaHAyMlUwc3Njcw?oc=5</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Sat, 01 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Yield Ramp Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>BOE rate hike bets ramp up as gilt yields surge higher - TradingView</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQUW9hWVdIbDR4ZkF3QWl6M2VTSFZXbTFfLUx4aW9pVmZCUmFKNzhxVlVVeEdxUkdTeUVQMFpnckJ2Q0VRTUxkTFdKeVROUlh4VGxlVm9lM2d4YVE3aU1jZS1EWmVKeWRQaVgtc2RKYi11X2hkZHBfQWE0aVZ6WGdaQ1JsczNnN1ZvdFRGb25oZ0wzaVVPaUY3aEZISks2X0paVDV5RTRtNE1PYjdBLXROaHpZa0U?oc=5</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 08:04:35 GMT</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Yield Ramp Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Bond Traders Ramp Up Wagers Hedging for 5% Yields as Oil Surges - Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQZ3daRU5KMDc0QWktRHVtMUpWYTJZbVNzbUtFb1EycTREbXh2MHpYb2loYVl3QThEanhvQTRIVHZuQnNqWVY5cnQ2S1ZTSENEUHRzN2VBWTBvWlBMMFFkeVNlU2FqWFlpWEJkdjJSS1dNNFJWZlUtMjRqSG1Qb1h2WVJ6ZUFkc2JYWll2cTBnTHktNE5KVVFUUlVkNkJYV21oeC1fcmo1dWVSc3ppZ2s3WFZkRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Yield Ramp Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Smithers</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>IATF 16949 News: 2025 Rules and 2026 Changes - Smithers</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOVm9QQkxSU2l3XzJwM1V2THZhd0N3U2JfRTllRU8xVkhfVHgzYVZfUlpId2RUQ3RCSy01N1B0VUtHQTlzVGpfaFByaE9nRmowVXBuWXBnQ2UtLTFuSEI1T2xhRjFlcUtYb1VYc3RuOGRlRi1rM1pWbFJoakFuNnlkaUhGRk5IYW5hLXJDVnBUdUNxVUU?oc=5</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 18:49:03 GMT</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>IATF 16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>EIN News</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>KSB: Setting the Standard as a Top Rated Paint Protection Film In the World with IATF16949 - EIN News</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPdVlqZnFucnE3UF9oTmw1RXZIWHFkUlV5RG1oSVczeDNmT2JTWHpJSFpkUWFmMC1vaWk1TFZBUFZRT2Zodnp6TUdFeFpvTGZmcDBsV05XTUIxLXFSdm9ELWdobTBjY2IzanhGV0t4dXcxemp4UFdlQk95RHctQ0NUamhvaDNPWGx5UklyaXg3clU5bEI4M3FTZGg5V0Nad09Cb29zWnFrSnhPbnZZMjVYWkhoZHRUcnd0WXItNUtRLTFfQ05BMUJya2ZHcw?oc=5</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Sat, 08 Aug 2026 19:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>IATF 16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Quality Magazine</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>ISO 9001 in 2026: What’s Changing—and How AS9100 (IA9100), IATF 16949, NIST &amp; CMMC Fit Together - Quality Magazine</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxNUDBBTkNhLUt1d2dqX3JSUndoUnJERkJjVmFCQUs1QW4teDJRZXAySTJFZE9ibUpsYVJMSWtZWlFpbldpdUZsN1cwZEpmWEE0WmtFQ0RNeEFMcFVlUWlwM2FkbGpLYjQyTHZQbjhDSFp6bEVIekxpSGNEa1Q3VkVnM2JTemllc1lZTlZwNnFuM3dNOXZLcnpMMU1CaDJmeF8yR19CXzBOcW4wRDBDVFdDWU1Ub3FTbWYzRlFDWnk3SW5NVkFBMGRaLVg1cDc?oc=5</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Thu, 08 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>IATF 16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CarNewsChina.com</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Rulemaker status: BYD joins elite IATF body to help shape international EV rules - CarNewsChina.com</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOY1pjbDJTRDBGSHFrbzFFbF90SUJMRkV6Rk53Y1VhazRRbWxEVUtWbTdGZGFrUjNvbktycXhEWmN0QlJCekVob0JUUmJOR2ptN2loQmFSa1RGSHh4QlFIMl9YNUluRS1rbGh3ZUptdGxuU2tNVER4Y0FoTndxTm8zMldYVHo3NzEwZHRpX3V3TDl0S2dkV1Ezd1JsR2FNNWF4eU95ZUxfalRTRGxNMG80RU9lX3NWMEE?oc=5</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Wed, 11 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>IATF 16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Australasian Fleet Management Association - AfMA</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>BYD joins auto standards body IATF as new member - Australasian Fleet Management Association - AfMA</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE1Xa3NzaEJvSnFhakRlaXUtLUVQblE5dnlUM2NCTmhJTlozdllRVVAzdjJCS2d4VUJPY2I3WUtEdWVaWTJyeHpiOTFEMzNDQ2lxVVFkS19HR1FnZEtkYVhZZFo0ZmJyeGhaV1FMenJhaDJrcXpLS05TOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Wed, 18 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>IATF 16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>businesswire.com</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Torex Introduces Automotive AEC-Q100 Grade 1-Compliant 36V/600mA Compact Step-Down DC/DC Converter XD9704/XD9705 Series - businesswire.com</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxPTzNSWm5xSFlqeUZYNHNVQmoyY3lWRllVa0k5cUVIQVRtbl8zRFRISTlwZHhlUW5HRUV6TUxJcXE0cFRTNG9makR2M0thRDd2aVQ4dVlxaHEzX0JqdVNhYjJGdmZTeXl1NTh0UWJBc3liT0N4eXd3SnpfTkY3YkVMNU03N2s0TlAyYkh3WDhseEZVRmFOaDBjVWNPUHhBdERHd3M2blNFT2VFeDVZb1l5X3RiTHFwZjZXZWF2OF93MTluR2lHNmFERFQxVnJPT2N3TElWYWctc2NWRS1URENnWDdTYjRhcnJYbVN0NXd0TEFTT2JPajZjYXJPdHZ6RFZHY2Nz?oc=5</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 02:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>The Joplin Globe</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Torex Introduces Automotive AEC-Q100 Grade 1-Compliant 36V/600mA Compact Step-Down DC/DC Converter XD9704/XD9705 Series - The Joplin Globe</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxNXzFUYWxONW5HbVM4LTZnMThhUTJUTE1zcThOMFRnb1dMTFJ2dVpYMk5JQmYxMWlJM3k5X2ZXZ0JFWTJBN3hBQ3BMeG83clo0VUxTaWRHN0phdVE3bE82Q181OXBVbDlQTW12MThuVjI2NmllempNanZvV09aWVZPcGNwUkw2N1JZLWFUVWdiY01pYVg4Nk00eE8zcXNHdDA2MHJNWUtYWHAyUVI4UEFZTnhmSW1iSS1OQXpnWERnNEJiVDFaUXNfX2dSS25lTGVSLUdIYVpGLVJuQ25sUVQ0Y0UzSGxDRkxSOHRDUmF4WTIxOVNiZUlTdGY1Z0hlcDZvNzFPSWwxU3FSaEUwc2tvRFlWR252bkswcGpN?oc=5</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 02:56:25 GMT</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Bisinfotech</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Torex Semiconductor unveils AEC-Q100 Grade 1 automotive - Bisinfotech</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNWXdtakx6Z0NDVWpzRkJvZmFISWlVSzFkV0ctaUZOeVh1UGhjNmt2VWdDSVcydHREWHp5aVRjb1JIazVEM05lY3hZWXhCN25SWGVwckNOQmh6M1o0cjlETm1lVFdWNGd0bl9fY29vWmdUM1kxRmVQUDRfZWZicEp5R1htSlRSdG8?oc=5</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:11:11 GMT</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>All About Circuits</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>What Designers Should Know About AEC-Q100 - All About Circuits</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOZ0NxLWZxVmpfWWtQQ2NFVUhRd0xkU1k4T3Q3OG5sWEJYWXZNQ3JMUm9KM2pOVjBoQmVmZzJoTElkMDRoTHlLd1c3RWVBWERyVlNoNjBGWWU4dzBPdzFzWlVvX05RUC1mZ29QdTg0ZS1vczM1aUlabloxWEZ5bWZoQmxkWDZHRnc?oc=5</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2020 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Microchip Technology</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>PolarFire® SoC FPGAs Achieve AEC-Q100 Qualification - Microchip Technology</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPR1JhTkl1VDgzejdjRk1qLUVmcjVqUmV4clhMZG5iTy1xY0Q4Qk52RDhxdDhyVXI2ZG1iTVdyMWhrUktmNVhSMzVMb01Ec2pQV3VBVFR5ZWItSkV0ZC1LQUxQRi12bHp6a1dYX01NOUdKdERlaWE0UnRiUXJBVVJGcHY4aDJYZmlLRmJjOTVmVC1jWnZSVjlIVnMwMmJ6UDd5aVB2OERNdEhPaDdJMDZJV2hQUFg?oc=5</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Mon, 24 Mar 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Silicon Motion (SIMO) Achieves ISO 26262 Certification for Automotive Applications - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQa3FQV0dobFZ2aVRyby1ETVJtLTcyMDQ4ZWF1T3pyR0QtTW44RlNuazhGaEtKeUo1S2lFd0h6WE9wQXhfOW50NmhTYnRoZ0ltSHVzQ0pFY2ROZ1VTWUZScTRkVjB6QXZBSFZ0N1V2UWNkVUk3NVZ2X1ZWU1FkeFprOWVTXzdXeXh6eUlUMjZuUlRjb0Jvb2ZHblgyZ0dEdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Mon, 25 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>ISO 26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>株式会社SUBARU</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Subaru Obtains ISO 26262 Certification in SoC Development for Next-Generation EyeSight - 株式会社SUBARU</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBtUWdnbGFoVHVsRHJyOHRNSTFtc05VZXZTWkhYREFyZW1EZUpyNDJBVXFIUU01cTFQWEJ6WWJPNWwzSjdCUlByMWNGdEx0b0pDUkxXRHpxbkhUQjZqZEU4Tw?oc=5</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Fri, 21 Nov 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>ISO 26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>businesswire.com</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Silicon Motion Achieves ISO 26262 Certification for Automotive Applications - businesswire.com</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPUzdfMkh0R2hzSC0tM2JzY3A2bUNCX2hlVTFzTGllaDNnNkJEN0FNNV9wNThsVGktZ3dqc2NuMjZENHEyNURranYtdmx0c0hzeHNUZWJONDZVX2lMX3U2OGdfcFI5Rl8zaTNyLVpPTWNfS0R5emNnUV9LSVAyblE3T1dYd1pQRmNyM3czRkFsTmY2dV9Ya01LUVhiNlpEMlZuTkwyZy01YXMwaGhiX3RENUtrcEtQTFlTU3dnTUVBWFhWRXVfaHZvNVdkLV8?oc=5</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>ISO 26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>embedded.com</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>ISO 26262: The Impact of ASIL Metrics on Embedded Software Design - embedded.com</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQWXAxU0dmZkZCbC03MmNyamxyR01KSHZ4MkJQclBUTWt0YXlfTFItN3p6RUpsVXdaM1k3UjhPWE8ybmJhSGs4X01xeDdRM2NBYXNILWV3ZXBkSlpBNVdnN09FczBnLVM5aWNQYkp5dy12TWFCS3JsZ1RBWGkyWkFIczRqY0NmLUtvLWxod1dCeVI5eGN3?oc=5</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Thu, 23 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>ISO 26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>The Auto Channel</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>NOVOSENSE Expands SafeNovo® Portfolio for Automotive Functional Safety Applications - The Auto Channel</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNUmoySHdzN2hxSlpkR0I0NDFzRDhUTWk2eWpDVmFsZVNDcnZOcEhSRnZfYkRKT3c1RW0waHdUcEpiczZoS0o5X1owaS1tRTcyUHlEQmU2V1hrVTVyOGZWbVZhWFhUbTloQUR3aUh1ekJNZFVCODh6bzVGUzQ0Q2hia25rRzVrZDNpSE5WYVVmUm5KdXZldXgxNTMwNzBNWlVrQ1dvZ0ZFZDZJdU1sVklDX3JvQTRHY3V2YTFvbVVDNG1ScGdLQmNzMGVKb19TQ0JTMFJJTHh4YWMzdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Thu, 14 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>ISO 26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Frontiers</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Implementation of an FMEA-guided quality-improvement workflow is associated with improved setup accuracy in lung stereotactic body radiotherapy - Frontiers</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNc19xaGZmZ3lENjN4aGZOcElQdWt5TWk4N2hoVEVfRFpGM084R1hiN3ZEN3Z6b1o0X1d6NEVrNmhvNWcwdFU3NlUwYS11YVJWNVpydDFuSkZaRUR6QTFweEZzVzlZeXZfc2FlRW9hemxUdDN1TUlkaWszWno1U3pQUWtwalMzTDk1c0tsRFpB?oc=5</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 17:09:32 GMT</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>FMEA Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>WKOW</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Excedify Launches Free AI-Powered FMEA Tool Integrated with EXC PLM - WKOW</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNeUtJd1YwaHJneFJOT0xacDAwcEdYSVdCc1JWWW5HUXcwaWJuY1h4U3JJRjhpSWNObUVEeG9lc3BlVUtrQllNTzdVSENOQnktazBpWlhVZjUwa1IzdGg5NndWNmdLQkJ2b2hVWDdjb19LaERZVVVlZ0I4eF9mQURGRl9UVkNhTllIVFloXzI5cDBqa250OHc3OFhfRFRkRVNfS1B3ZWZka0JQUm9JOTFDaEFfWnowQUgzekk0Z1NOMDhRQi1zMl9jRF9EWkpQR0dxNnZiZlkxUm10elBPYmRSUVN5WmtBTDZlWVJfb2tvbVp0aDdhSmx2VEVIVGRIUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 00:25:02 GMT</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>FMEA Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Transform Quality Management with Closed-Loop PLM: Boost Efficiency &amp; Reduce Defects with Autodesk Fusion - Autodesk</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOWFNkSmxhMjdYY0dKZDNHVF9xZmZndmF2a3pLbHdRcFNWZHp0SUhENE1xWjJERkNlTmZod1dWbHJSNk5HSkZKcEViVWxNLVZXdVh0Sk1tR0JuaWNuUFJhRE8zdFJZbkQyaFF2S1lJU29IcmZrZ3hMUndjeUpiWmhpRVhIODJ4bTI2T1pJRDI0WHdnbXE1NWxRUU91dWY?oc=5</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Thu, 04 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>FMEA Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Supply Chain Management Review</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Not-so-sweet spots: Diagnosing cocoa supply chain woes using FMEA - Supply Chain Management Review</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQRzA1aTZTbUVPcGt1aUpmcEVlNFhXdS1BQ1p5M3lOZk44UG9OWmtISEhILVVjOTk1Q0RadnlUYWluOFRKMndrVlRPX0RSMl9SdHd1U3c0Qmc4LUd5M05DUG5wdzFTSHZkMXA3RXN3ZkNYMlRMdmIwUzhkNHRWOVhsczJOOVRKLXkyblA3VU0tNFBaSWNSYUNINg?oc=5</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Wed, 07 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>FMEA Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:03</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Automotive World</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>VDA and AIAG harmonise SPC quality standard globally - Automotive World</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPZEQwbVFyckRHV1F2eWZOV0NNMExIRmZCMk1MYXFKVTlFaGU3V2dKdTk4MFVZNEpMZXQzTmo3bkpnR050a294Q2J6MndyS0d0VG03WUJlbU5KYVoyX3dIVkhVaUVLdW1sYl9Qak5IZDhYNnN1T09XaElOTnpoUGZlcFR2aU56eUNkUURjRDJHaXhxWXU5?oc=5</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Fri, 03 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>FMEA Quality</t>
         </is>
       </c>
     </row>

--- a/accumulated_news.xlsx
+++ b/accumulated_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J248"/>
+  <dimension ref="A1:J253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12336,6 +12336,246 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:07</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>platum.kr</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>어썸레이, 75억 원 유치하며 EUV 펠리클 사업화 단계로 - platum.kr</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE9rX0R1SDlkQVU5LTQwREJJMVRWcnU1eVZ6U1MzLTFsWmFIc09XX2k0Y1I0LUJlWGlGb1BsbFpGc1gwU0ZIMXoyRA?oc=5</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:21:05 GMT</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:07</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>ASML, 인텔과 하이NA EUV 첫 양산 성과…"차세대 공정 본격화" - v.daum.net</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTE5CSVRxTWVkdnhtV3lzOU5ZaTF0cHpsV0dNSW9NR3RvV3kyT2xLZ2Iyb1U5ZG14NDR2bi1ZVlp6VTNlVU96Rkp1ZFZoWUpuc0s0aFZLMA?oc=5</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>High-NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:07</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>강원랜드, ‘한국서비스품질 우수기업(SQ)’인증 획득 - 한국경제</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE45R1N5bzA3MU9EQmx5M1lzTU1ETGh1cnE1Q2I5QTZqcWsyMkpRZ3l2Zng5MlNpdXFXNDlRcUtMdUdjaVM3X1R5dDBSNEkxZFdZbTZnd19YN2Rxdw?oc=5</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Fri, 17 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:07</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>wccftech.com</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Intel Starts Paying Overtime Bonuses To Expedite Work On Its Ohio Fab, As EMIB-T Package Yield Approaches 90 Percent - wccftech.com</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQVmxOdk53eVc4WVo1NVFXd3BFQ205UVZOWm5yUkJKT0cxVUdpSEdYM1JJOXRhTUFpWlNvMHM5ODAyLURZVXpkOS1weG83N21fdzVDM0Fpb21zejlsRVFuSVJHTFNzTTFWNkJJS3E2REpnRWNlXzdNLVJtQ0RqRXpFb05ua2t1amFKaVJqT25wcGFmQUQ5MFNneVpjR1VIRDF4V2NNRFVrUnk2Um9zNVc5MVR1YmJKOHNMdVU3dlcwTUh0SWd6RzBJYmVVX25UcWhSRzM00gHYAUFVX3lxTE82dFhJMUxwdW5VUk5teFFybU1DT1VCeDJ0ZzRHZ1NkYnpSbHJpVmMzVTFqSFl6X21Yc0JZN1NjODF2T1l4TXA4bG9tem80UHZZZ1F2aWhzaUEwa0RRMkczdDQ1YzIxdGlabXRzY1hPN0lzTmVvYmNZQmxKdDdXbHVVY1dxTzhwRnRpM1RfLThpSGlpV3VRYnNhSlVGOXlleW1xZXV5OW41eFIyazJUOHBwUDBIY3ZUV0FwbGpxdS1ibVJvU1Z6NWdxWnR5b2ZEaHAyMlUwc3Njcw?oc=5</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Sat, 01 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Yield Ramp Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-08-11 03:07</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>bloomberg.com</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Bond Traders Ramp Up Wagers Hedging for 5% Yields as Oil Surges - bloomberg.com</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQZ3daRU5KMDc0QWktRHVtMUpWYTJZbVNzbUtFb1EycTREbXh2MHpYb2loYVl3QThEanhvQTRIVHZuQnNqWVY5cnQ2S1ZTSENEUHRzN2VBWTBvWlBMMFFkeVNlU2FqWFlpWEJkdjJSS1dNNFJWZlUtMjRqSG1Qb1h2WVJ6ZUFkc2JYWll2cTBnTHktNE5KVVFUUlVkNkJYV21oeC1fcmo1dWVSc3ppZ2s3WFZkRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Wed, 29 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Yield Ramp Up</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/accumulated_news.xlsx
+++ b/accumulated_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J253"/>
+  <dimension ref="A1:J282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12576,6 +12576,1398 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>자본시장뉴스</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>삼성 18나노 D램 유출 6년 4개월…SK하이닉스 4000장 출력 5년 - 자본시장뉴스</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1oU2d5bzJod01vN21RZURHMGRMYngwdTN5amhjbGxPX2Vrcjd2TGlGMVh6bEtHVDg0azJHM2FfWVNoRnZ5UUQ4OUNiLTBwU1NyQlFtakUwcnpCckxwRjZaclFWZVJpZ3c?oc=5</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>한국일보</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>SK하이닉스 8월 대규모 신규 채용..."학력 제한 없애고 반나절 심층 면접" - 한국일보</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5tWFpqU09FenNSOGR0eGJZbUVCdjZSNlBnWElpd0ZRRXNHWG1QRUp5WGhJN1pEQlppeGVzYzVlMWhjUVFLNFZZaTNOM0dTcTdzYmhWcC1NVTdudHN4R3haay1YQUVMbmZmdncyN2NR0gFzQVVfeXFMTmF3a2Rya0xhZDhXZFNxeGpPQVVjME9zNzNYY0xUVW5fYnQyeGVXR1pkSkVrdHFpSnYtQldTWVRNeFVXNzZBalpNUDZLWGhlX1Atei1sQ080MTNRTHJhUEk0QjdCZUgzZ2hDa3NGQXIwZFQtWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>SK하이닉스 양산기술</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>충청매일</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>하이닉스, 청주 M17 건설 확정 - 충청매일</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE90X0JRcjdMcWQtTWtDeE80Tm1JMEd6LVZ0ZGlNRzlGMmhZOXUyT2h6SzdHaVlOWlNtd1RleTdCbHNEOHRhUHpVNUIwcnRheGxHRDJ6bHprcDMxVmMxSm5oUUh5eE1pUVZpU2c?oc=5</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 04:30:00 GMT</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>서울이코노미뉴스</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 청주 M15X서 첨단 D램 생산 확대 - 서울이코노미뉴스</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5TMC1YWFgxWDBsUHNOM0RaZDZaRU9TSEN0S09tR2cwcDdVNjZPc0FxWkJYMVI5MFZwRk5aeXlDRGJoTXEzSFRoeVZtMVpNSDEySW5ZbktyNmRFOHIxVDBpVU81TjBkWkIzZmdWUXdR?oc=5</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Sun, 12 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>라인/투자/Fab</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>newsprime.co.kr</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>한미반도체, 'AI 병목 해결책' HBF 상용화 임박 '수혜'…"핵심 TC 본더 수율 검증 완료" - newsprime.co.kr</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1vYkZxUmJKN3dzNnRTcTFsVFRWZmNnQTllcHlaX2Y1TzAyVnZ1R1Q5aHFucVgyWFY3MFkzUy1wTzBJZ01kcWRsUVM5ZlE5U3NLU291SmZlbGlsSk02a0lKb2swbm0tRWVPN1Z6ZA?oc=5</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 23:14:49 GMT</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>financialpost.co.kr</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>[인사이드] 'HBM 성공 주역' 구자흠 부사장이 밝힌 '삼성 파운드리' 공정 경쟁력 - financialpost.co.kr</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE94UmdlUmxpcjdOdnFsTHRXSU1RTklsRHI5Nl9yR1FERXVrZEYtS3NpVlR0QlhnMG9sckF0SVZPVU5jZ051SWpaTGFfWUE2WmpWYmJ6cDlRdlhDTkM5cGpmNVR0R01NOTBUbTBUZWdCZHhpLXBZ?oc=5</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 02:43:35 GMT</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>thekoreancarblog.com</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>현대·기아, 독일에서 15년 ICCU 보증 발표 - thekoreancarblog.com</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNRTRpVG9MaXIwaEJwS2pIcjd1dnJIODJTZGxBbElCdWhuRTQtTGhoTzFlMDlpN3JFMUdnb2hrZ2FRUXdRYWNQQ3V1UHFXVTYzbVZ2blhSRUJ2UHZ0RnhFU20xdGVsdGtZS1NSbFNUNmtlWDRFRkE4VDRhU2VBbXRUYXNONThFeHItdmhuTk5SRkNHV3ZOQUVPa0JEVWNHMmM?oc=5</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>핀포인트뉴스</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>노광공정의 핵심 '오버레이 계측장비'… 오로스테크놀로지, 기술력 입증 부각 - 핀포인트뉴스</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE8tOGJiMmNETUU5UUJSeDM1T3JoZzJ2anozeF9RQzhZUHJZT3F3ZGRUV0QtcFQxRVVQYWtPcXB2QUJMNHBySEtYaFVwLTJZTWY5QThyVnQ3SjMyMXpORG4ycE5mV1JtOHhieDduRzZNYjlDX0HSAXdBVV95cUxNVFBRR0RWSmUwdUJBalVrSkxDdWdvbmRIU2RJWnl4S3lBUG15TmJFX0Z6QlpSMFJJY0hxdE5aRy16cmdmSkN0MlhPUEZuNnNuRzJGV3huLUFDNXJRaG5uSkVmM3JsdFUyVXJGMGJJV2puMGpWQW1rQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Mon, 04 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>dealsite.co.kr</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>삼성전자, HBM4 연말 수율 목표치 85%로 상향 - dealsite.co.kr</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1YOXJiM1lVZEc0RXlKeGhpOEJHQy1tVjlOS0xMbXI5cFE3R2FBLVNXV3Y0WTYzWnA4V2Q4OUJTcGp2NDdTZDhlSUg3dWlDa0E?oc=5</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>newsprime.co.kr</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>시노펙스, 베트남 사업장 '국제 공인 자동차 품질 인증' IATF16949 획득 - newsprime.co.kr</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE9jLVlPS2UyX0pHSnBVajEtdUQwVmd5QzlNcVdwUUQtWXBIZFh6cWRROE15SWI0MXZGbjQxd1Vfd29iUGJxdXYtYk95OExyR3Rwa0RpZjRMT3dsSHRva1B3XzJSQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Wed, 24 Apr 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>IATF16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>samsung.com</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>삼성전자, 차량용 반도체 기능안전 국제 표준 인증 - samsung.com</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxOWWxfWjhGOUI4YnE1VWphZkJlaXhuMlN6akNTV0tBb2RPTVRqcmRFVHVRUnpOazc2bXpfLTdYTWo4X0lVNFdiOFF1aElIb0pFRnNUNHJCS2wyTmpUQ1ZMMGNlQTNQMEFPcWNoSFJfY0R2Y2xTMmM1TDgzZW9wb05FN3hjMjU2ODRMVmFOMlBzV2dHYnJ3MlRnQS1mUWJQYll2Mk5FZGlBWTA4OGhVY2tOQTgtVFlYaVIwUV9lb0dDS1lYblJIVHM0c3pFTnk0MG83d2k3REJWOXAzUXlCenZTbHZpcl9hTkNkMnJzVHlBOFRXVU5BRzViTXAyVUpYSmJvSzRUWkpGTENhYVUxNUEyZWctLVB4TmpMQkxMSEgtRHRzck54QXNHcHNheWItUDI4NHdRN2k1QWIxQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Mon, 13 May 2019 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>IATF16949</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>헬로티</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>ST, 자동차 배터리 효율 높이는 선형 전압 레귤레이터 출시 - 헬로티</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5YRWlyOFNkSi10RnpGaVFvdkNpR0FGNWs4OGZHclNRZmVMTFhFbkZPVUtBOFBGQTJnUnhPQjBTR0pOS0ZQdnVpbkdteU9CZ0RhbkxCU3QtLXF4bTZX?oc=5</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Wed, 01 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>kipost.net</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>TÜV SÜD Korea, 하우엔지니어링웍스와 자동차 ISO 26262 기능안전 및 A-SPICE 분야 업무협약 체결 - kipost.net</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9xMUFlQnNHUXE4X3g1ZTZPNXJ0ZERWc21kNmdZaWxtUV82WlBsYnM2Mm9hcVY1NWhVOW0zLWgyNjFkM0RLX2ljRzk1U1JBeDhMeEhJUGR2M1ZDT0llcEZGUUh1VEstSFpr0gFsQVVfeXFMTXFqUWtnS2NOb3VxLVFFZ1R2M25KNmxxMS1MZWxSczdMaWV2QU9zM2V3S215T3FHVGFrU1ZKZ3RWMjZFVTlWam16SnFibkNmQUFHMGh1UG5zdmhvSlRORTdKSzdCbmlDNm1OTHZf?oc=5</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>techsuda.com</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>이엠포커스 ‘스마트 FMEA’, ‘FMEA 360’으로 제품명 변경 - techsuda.com</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQaWR3TmJPUjRLeDBaZEMxQ05meXZ4aXd0VnFzUnQwTmdKQnJlcTZRVjhfdmJCVXU4cU5lTWpaaXc1ZXBPMTlvcHV0LVdhZEI1d2x6cktOYlpxd25rOGhNSEtWcnlyYkw1Y2NiSEl5ellLUlcxY0JmY2Q4YVlob3VWVElWbmpFTHU4clFUV2JmUENpd9IBlwFBVV95cUxPREVZc0FjRVJodDBiZDVabVNkcGx6UW9nbUwtaVZXMmU5RnlmbWNXUGZad3E5OTFzVzlsTVZkRDhrWkpVOU5QNXVaSXB3Y1MwRTRuRnE5Z2RIM1pBXzQ4V05COTlrSHR1dGF3Q08zSVNINDB1bFhvcnI0YWp1Q2UxQmFxeUlqOEUwUy0ybDdKdEVobEZ2R1RJ?oc=5</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Wed, 14 Feb 2024 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>newswire.co.kr</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>이엠포커스, LG마그나에 FMEA 솔루션 공급 계약 체결 - newswire.co.kr</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBXTE5xN3QxUmtBVnM5UmhxXzRmU3FudkJYUjFmbUNVRVhrMHR0ZHhVZDRzVVo5Z0oxYlVrWnc1X3M4bkFwc1h4TmhTVTB4bWtkWlQ4SldBWFozaVN4WVE?oc=5</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Tue, 11 Jul 2023 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>테크월드</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>세윤씨앤에스, APQP 프로세스 관리 솔루션 ‘와이저오토 포털’ 신버전 개발 완료 - 테크월드</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBkRTFOV093MXF2Z3QyLUtRWGlFTmVGOE1lTUVCNkkwLVJwNGp5RWNqdi1jSWxPclNxakhlZ1NnaV9FZEk5WGtDZl9WSG5DMTVkWWtoQXlBLWRQUnNGcGQxSXJXTkFkM1k?oc=5</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2015 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>APQP</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>로컬세계</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>강원랜드, ‘한국서비스품질 우수기업(SQ)’ 인증 획득 - 로컬세계</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE94Sk5kRVJEUzdXRkRJcG93djQtUGlLOVBKdktfWmtRSEVXV0ZIS1N5UG5tdl81a3ROaFFJcUtybE1HYXFUWjhNYkg3UmpPQ09lMW91VDZqT0FqRnNOTFBSNNIBWEFVX3lxTE5Jb3V6c0RCNm5XajZST21WQ1otQ1RBRTJLWlZvekZmekdLcTVWU1dsLXEyQ3lCOXRTQXkwbVV1ejAxT3VZYjM0di1sWVZNMk5wUTk2SU10OGc?oc=5</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Fri, 17 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>finance-scope.com</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>아모텍, 전장용 MLCC 성장세 지속… 고신뢰성 라인업으로 시장 공략 가속 - finance-scope.com</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9HcTJwLWYycVpqR01iOHh5aHZRREY1UUtmNUFWa1V2UzBla2FucTlDbWdxSy1hLUdYMnBiVHJKRFRWaU9HSnI0dXdyRWZpblM2ZDFWejJPSVZza2RwU1R0V2Z4RHlibHlyRnc?oc=5</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 23:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>네이트</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>링크드, 글로벌 완성차 부품 공급처 확대…전동모터 본격 양산 - 네이트</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE9vYVZCUUNtZ3ZlT0ZWa3A4ckRBUFhNUDJybDRsbVJ6bEVNWlNZMFhBZXJqWFFhS1FMWVZvWGRXZDBCdC1GZWJqc0luQXFwSE5WbEVj?oc=5</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Tue, 07 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>DV PV 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>국내</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>브런치</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>비우고 낮춰서 최적화하기 - 브런치</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE42Y2NSQ2JOYVNBcXdJZWpiVk9LR045clB6VmdzNmpuQmw4UTZ5TjdkcTNZWmxPXzBnbV9jeUxTQXdzQUtOUjVIeUhyQzNUSGFDSVE?oc=5</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Tue, 29 Nov 2022 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>필드클레임</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>eu.36kr.com</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>All Eyes on EUV Lithography Machines: Key Trends, Industry Impact &amp; Global Technological Competition - eu.36kr.com</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE5XY1BURlZ0X1RpaUplNldaV3hHWms2VU9xamVTYzBPYkhlTGxubk5QdmZpd3hXMTRfbU4xVzlCbG5aQkloQ0wzZDNiTXBNdGdiRm93?oc=5</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 04:04:18 GMT</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>EUV Lithography</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>AIP Publishing LLC</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Atomic Layer Deposition (ALD) and Atomic Layer Etching (ALE) - AIP Publishing LLC</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxPbGwtd2YtblJPTXlpYUZZRWE0cHJ2MWRNM3pUWFhYRVhjSUEyN290X051RHl0eDAzS05vLWtzYVBsTVdYR3NFUHhRQW5JcFNwNkY5aWNJMUZZSndjT0lwcmZCZERpQmJfV0ZBdnFZTXBreDZMNFhtU3BKU19TOEpIbTF3SE1wYlNaZVF6MU13Q1NHd0NIT0Y1clluOGktOENaUjJPcjkwb0pWWTM1SGRabFFzdkRaaUpMUjh5YzBaUUxBWGhGd3c?oc=5</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>ALD Deposition</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>fortunebusinessinsights.com</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>CMP Slurry Market Size, Share, Trends | Growth Report [2034] - fortunebusinessinsights.com</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE05bUJKaGdaMmduazhfaWF5Y21EYzVvaDhnOUI4X2lMM1RmYkFib3FERWRxOWc0LXk4MExoa3RkbWVLakM1VWdibkpjZzVHTGJWRTNNNUJFSGxseEpURlBLeEJJWDRudzd5SzBXX0JPVVZyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Fri, 06 Feb 2026 11:58:52 GMT</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>CMP Slurry</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Korean AI Startup AiBiz Cuts Semiconductor Defects with GPU-Free AI, Powered by AMD EPYC CPUs - Business Wire</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPWUtybUwyWXhxMEMwVUZaenV4M1BnWU5GdkZaellQVWF0d2FWdVAwdmZVWVRwLTdFbUFjbl9zYnJFOERvMlRJaTBCNkw3UjJfYlJkQk5QcEJ2TzJaVmo4QmtLc0VsUkNGbDAwM1RjV2dqempmMDJfY1F0eG9PcHo1YWZUWEZzYVplMVUtQl9BbmlzaU5ZcmdFQWV3UFJydWF0Vzd2NlpxMWswMVdQWkpZSUFFNU1iRUpaXzFNRHZsOEFlak5zZVhmaVJiWVVsdmZkZVdHdWFLWC0wdnBFTWx6SjBhWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Semiconductor Defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>trendforce.com</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>[News] Samsung’s HBM4 Yield Reportedly Hits 80% as HBM Race Heats Up, SK hynix Labor Talks Add a Twist - trendforce.com</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQQVNwX0F2ZVdNRW5nb0tGdG9WblBSZVltNE5TMEt2NHdOU2NDd1NMbmE0ZGlXY0tha04xeXduSHNqSFVzdFpEMmtPWVhiTExOcnJqZU9uNU9GWDVicHZ1SHVsd1ZZSFlwR2poOUd0cHdYM3k0cWo5MW1YU3NiMzJ3dVNDdl9VU1FDRW1DbVpLbVY4MG5kWFVqcFNhNjVDaFpla2lQeFhwcGw3Q1dDTTFsQmQ3RmdDXzh2SHJfQnVtaG02eDF0Z2Zra0pYU19YUzNUYkR2cGRDSXpQbnc4SFBHYlpTNTZqWDFGMGxKMEpHRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 03:27:21 GMT</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Yield Ramp Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Lam Research Newsroom</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Virtualization and AI in Fabtex™ Yield Optimizer Ramp Up Yield in Semiconductor Manufacturing - Lam Research Newsroom</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxNbU5mR2ptRExOb3JOQnNCeGZGSUVqTk9DS1ZoR0hvYjh1dlNGQmcxMGRNUW1kNUVjZWxYWVU0NF9IVVQyYTY5ZHdSWVFjUlJLaVZrWnNFa3pJUTNfTWU1bTBoOWdxS1A5YjEyZ3V1cThwT2I3ekU3RzV6bEtRRW9UUkl2eS1saWM5RGZWSnFzOEhtUkhxYmtidE44a09JYlM5Q29VRWhPeGdCQm41WGtqWjBwaXpVVzR3S2NVYW96NlBuQ21rTzhiX1FicUh4QnM?oc=5</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Tue, 21 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Yield Ramp Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>TechPowerUp</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Intel 14A Yields Hit Impressive Milestone Before Trial Production - TechPowerUp</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOTjhBWF8ybGZsaHVUejh0U01hZTRfc1c2Vk9WQW5vckpBLTRoSXRkMTF0WElMalNibVNDVlpLNW1XekJLSkh1UHBqQVJPZDdNZTRuZk5sY0lkWTZzSnk0emsycXRXeHkwMExzNUFtUWFLRVRtMkRxUklBWUpGWWY1dXVVUDIwZTRxdFFnLUNrMm85YXRKc0pXUUlOOHI0V2s2MUHSAacBQVVfeXFMUE50dGt1Z05HMGdNb1lydmVyRFNqckJMQmMxZ1J3RzN3SkJaTHN0TGhXclNKenl2LVhTN0lBaUpoSWwxcHF5Z1ZTSlJQenc1WHloc3lVX25JUkxxX3RiUWRMOWdhUWl6Y01nUDVVbVB4dEFvakVQbFJoekV5cWFWQUlhb1FRNkVIR1pHS2Uwd1ByOFZCay1Cbi1KTWNzbFlqNVd1NE5ZVms?oc=5</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Tue, 16 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Yield Ramp Up</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Torex Introduces Automotive AEC-Q100 Grade 1-Compliant 36V/600mA Compact Step-Down DC/DC Converter XD9704/XD9705 Series - Business Wire</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwJBVV95cUxPTzNSWm5xSFlqeUZYNHNVQmoyY3lWRllVa0k5cUVIQVRtbl8zRFRISTlwZHhlUW5HRUV6TUxJcXE0cFRTNG9makR2M0thRDd2aVQ4dVlxaHEzX0JqdVNhYjJGdmZTeXl1NTh0UWJBc3liT0N4eXd3SnpfTkY3YkVMNU03N2s0TlAyYkh3WDhseEZVRmFOaDBjVWNPUHhBdERHd3M2blNFT2VFeDVZb1l5X3RiTHFwZjZXZWF2OF93MTluR2lHNmFERFQxVnJPT2N3TElWYWctc2NWRS1URENnWDdTYjRhcnJYbVN0NXd0TEFTT2JPajZjYXJPdHZ6RFZHY2Nz?oc=5</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 02:55:00 GMT</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:37</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>해외</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Business Wire</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Silicon Motion Achieves ISO 26262 Certification for Automotive Applications - Business Wire</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPUzdfMkh0R2hzSC0tM2JzY3A2bUNCX2hlVTFzTGllaDNnNkJEN0FNNV9wNThsVGktZ3dqc2NuMjZENHEyNURranYtdmx0c0hzeHNUZWJONDZVX2lMX3U2OGdfcFI5Rl8zaTNyLVpPTWNfS0R5emNnUV9LSVAyblE3T1dYd1pQRmNyM3czRkFsTmY2dV9Ya01LUVhiNlpEMlZuTkwyZy01YXMwaGhiX3RENUtrcEtQTFlTU3dnTUVBWFhWRXVfaHZvNVdkLV8?oc=5</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Wed, 20 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>ISO 26262</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/accumulated_news.xlsx
+++ b/accumulated_news.xlsx
@@ -45487,9 +45487,5050 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>수집일시</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>면접활용도</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>분류태그</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>검색키워드</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>언론사</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>뉴스제목</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>링크</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>발행일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>자본시장뉴스</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>삼성 18나노 D램 유출 6년 4개월…SK하이닉스 4000장 출력 5년 - 자본시장뉴스</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE1oU2d5bzJod01vN21RZURHMGRMYngwdTN5amhjbGxPX2Vrcjd2TGlGMVh6bEtHVDg0azJHM2FfWVNoRnZ5UUQ4OUNiLTBwU1NyQlFtakUwcnpCckxwRjZaclFWZVJpZ3c?oc=5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>잡플래닛</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>삼성전자 반도체 엔지니어 이직, 협력사 경력 도움될까? - 잡플래닛</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wJBVV95cUxNUHhlY3dNVE5ja3BJb1FLRFN2a0xiNWhVVDhrOGk5U0duUlNKM05XOVJWN3AxV3dwNDhXMS11dWFycWxYVmdUOGY2M25ibkZLQ01XaVBWTkZmWVdwMER3aTBLUnRoNmVNZ0VtMnUtOVpPVWU0MGlVQVNQOU5CNVZNeHAzbWxVS3RiOUIwUm0xVWZvUjhUYWE1MFdfdmEtMUdBSXdydU8wdW5LWTFhLUdleDg2NmhyVDZ4WU9DQ0FuYmxySlFQM3J5clRRODlNaklSQzdHUjVLX2cydWFOMVdfamJHVWhiYThaZHhTYThfcXBsX1owck9LU1luNXQyUy1yckNVT1Nld09xS0MtZW1wRnFkRE82M3N0S1Z0bS1JX1FoX1hpVW1qZEJ2QTRyYy0yUHZBYUFXekdXcGlac1pLNGFSWEdUcWU4M1RqSUI4a2RIY0E2eVBKOEdsTDNFWUxGdWtlRm1DelYzb0U?oc=5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>삼성 ‘HBM4 성공’ 숨은 주역 최정민 “4나노 초저전력 공정 기술로 HBM4 양산화” - v.daum.net</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9MOWNpNHJXdFpwNFJMSTctNkk2WE5FRWNtbEJ5NkhuMnRrdGIwSGhCQlZpcUpna1JwU2Nmc1FHZlNldk8xb18zOUltRGFJNGc?oc=5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>munhwa.com</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>“AI시대 견인 핵심엔 반도체 공정 기술” - munhwa.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE9fMUpERmRteE1wb1VNNVBfelFyaDFjemJGRjlNQjBNbHBaNDdLRVRmZEdndXNLMzYtNEg2cE1udU50THVjSWRwdnBUSFF3eTRj?oc=5</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>삼성전자 공정기술</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>dt.co.kr</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>‘4나노 파운드리’로 HBM 양산 큰 몫… 삼성전자, 개발 스토리 소개 - dt.co.kr</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE51cEpBdDdTelpkSnYxaVNwM2h4YU9FQnRYSlpfR05BRzNlNEU4Tmx6LVJ1Qm5RRDIwZ1ZGM3JTVld1UXAyUGRWS0xrOXhaZw?oc=5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SK하이닉스 양산기술</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>한국일보</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SK하이닉스 8월 대규모 신규 채용..."학력 제한 없애고 반나절 심층 면접" - 한국일보</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5tWFpqU09FenNSOGR0eGJZbUVCdjZSNlBnWElpd0ZRRXNHWG1QRUp5WGhJN1pEQlppeGVzYzVlMWhjUVFLNFZZaTNOM0dTcTdzYmhWcC1NVTdudHN4R3haay1YQUVMbmZmdncyN2NR0gFzQVVfeXFMTmF3a2Rya0xhZDhXZFNxeGpPQVVjME9zNzNYY0xUVW5fYnQyeGVXR1pkSkVrdHFpSnYtQldTWVRNeFVXNzZBalpNUDZLWGhlX1Atei1sQ080MTNRTHJhUEk0QjdCZUgzZ2hDa3NGQXIwZFQtWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SK하이닉스 양산기술</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SK하닉 '억대 성과급' 그냥 주는 거 아니었네…취준생 '발칵' - 한국경제</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBKTGJycGExaUdoV2lpUjI1ZzZEdmRGeDF1enRrc2lEZjJITXBZdHRfdFFQd2JHbFJLUW1xdktaOGJ6Sk00SzBXMWZKWFhMZDFUWTdmaVEtZTFzZw?oc=5</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Thu, 30 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SK하이닉스 양산기술</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>뉴시스</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 반도체 인재 대규모 채용 돌입…"세 자릿수 규모" - 뉴시스</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE1LLVM2VlJjMmR4VE82RER0TVlJSDB5dm10WFhHcGVLbnY2WFM0UXFXd2VJWEE0dzRodlJCTUU3X2gyVjdySFhyYUVJdkwycG9QUU5DZnNnOFA3YzlweDZaZdIBeEFVX3lxTFB6MTVYTV82LU5MeS1fMVdkZ1lvaXptcm1jYWxPelpGaVNBbklKejQxWnU2YnF1b0tIZ192cWFkN1hKOEhtUHgzR255UVJCRmZGSXZLQU51QlJyc0xyWHhoMzRKVmRRRzNONUdWek9PclZoRWQwekx2ag?oc=5</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SK하이닉스 양산기술</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>삼성전자·SK하이닉스, HBM4 수율 격차 1.5배…엔비디아 물량 배분 좌우 - 글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOMnZtX2ZuS2JkLWw1NE84UDI1MnV2TVQzMDZoeENPeGpQOGhXMmh0RmlIZzgxVVAyTmhQeFRTNjgwRVktYnV3dEt1cDZ5eFVoRnZlMUtEM2RnaHJtZzJpaDhCMzNFNTYxMVVWNndEc3dJY2pxVHhubTJsWXo2cjhUeWZSc1RMd1dr?oc=5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>현대차 개발품질</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hyundai Motor Group</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>남양기술연구소 디지털 측정 센터, 데이터 기반 측정 혁신으로 품질 기준을 재정의하다 | 저널 | 현대자동차그룹 - Hyundai Motor Group</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOeTVKeGJZOG9LSW9iU1RqNG9jcHI3em9jLTNTZUZQT1RsQkEzSVdZZm1WZktrMWhDUUJVZFZTSXBGVi10YjBwOFRUdjhUMFphRUlHaDdWQTVHZWxBTFp1cFJ2ejFzWHZ3SkNqWHV3ZWFjRXVIU2c0UlRZaFpqZEE2RDlmZGpfMVRBaFBhblB3RnYtcnZybVdZVUdXUDhVZw?oc=5</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>현대차 개발품질</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>현대차·기아, 딥엑스와 AI칩 공동개발…"품질 검증 완료" [CES 2026] - 한국경제</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5tbTFpeVVYcmxpeXMwdU1mWHRwRWVkbzdGQ3htYy1Kbm1vdV9kSE5PZzdjRDJ4OVExSHo4VWZDWG5KeG5YaWFiak9IWDB1eENGdjZHLUFkVzlPdw?oc=5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>현대차 개발품질</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>정조대왕, 즉위 직후 "내 아버지는 사도세자"… 정몽구 회장은? - 조선일보</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPdjlUU2FaMGVCNzZCOUFhN3FZY2g0cXlFUzY2bzhrTVFfeDVueEg3dFNkazhyME9fZGllOWdla0U0dVo2V3NZd012OGs3a2NvLVNoZEJEbjRaY2pvN1hFUV82Y3E3X25reVViWUxaalp6M2JxRDJNa1ZWcGlZSWlodlhveFhJVmVzZFNHTG5ZTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Mon, 15 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>현대차 개발품질</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>비즈니스포스트</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[현장] 현대차그룹 남양기술연구소를 가다, 정의선 '세계적 품질' 자신감의 비밀 - 비즈니스포스트</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBDUUZxUDg5UlNtb2VmRXdGQVpWVm5OaDF2OWhtVTM3c2VLRF90VV9fa09hOXRJMEFpR0RKdnBDSjlzZE9tVWlqWjJQUmNxZV9URF9DREJ6N3QyemJJRm5TZ2wwSFhTVmpCY1FucE1OMy1ELVk?oc=5</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>현대차 개발품질</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>월요신문</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>현대차·기아, 딥엑스와 AI 칩 공동 개발...품질 검증 완료 - 월요신문</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1wV2taeHY0NnlnODJGdVZpS2tzOV8zdlcxelFyN0oyNlZyeDJLVTVQa0YxczRxRnIyck43bkxEaTlBRzJOOGQ1eEo2YkFBSl9YQjBUbkxZdERDUWdjZ0FQTFQ3VWFXazdaNEE?oc=5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fri, 09 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>현대모비스 품질</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>매일경제</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>현대모비스, 생성형 AI ‘MoAI’ R&amp;D·품질·영업 업무에 도입 - 매일경제</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE16cmVMNFhKblNrS2N6YVFVUjE5Qk0tNEdZdVFvVG1FdVpvMW1QanUxN0NzVFNIaVJDSGZIN3FrWXZELVJFMzRrMmdFNENuX0JOTXRyb2RR?oc=5</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Tue, 21 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>현대모비스 품질</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>뉴스퀘스트</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>로봇 부품 시장 진출하는 현대모비스, 아틀라스 양산 맞춰 원가·품질 두 마리 토끼 잡는다 - 뉴스퀘스트</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1fWk1wMWRzcTgtVFlDUm5oR1dqUkZMZENEZ0UyU0pWZE5pNW5CYVM5d29naFZMekxoNmtxdTFER0oyS2U4STROV0ZBNVJ4cjNEdldLMGluSi1QOW5XUHhKb2tWMC05bVRpQ05oNVFtY9IBc0FVX3lxTE1CbGhxVTFCVkY1YktFeEVwckVpUndjREZvN0MyUDdITzNFRmtTbHBlb0l6OHRPUTRiT3dfTEJXVERkZ3U4U210TDRxU0hXeHo3RUt2NFNWbFVZd2t1UDZib3BsRVFDMG01UUk1NzJrZTF5ZUU?oc=5</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Wed, 24 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>현대모비스 품질</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>데일리e뉴스</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[ESG 포커스] 현대모비스 "품질보증 체제 확립...최고 경쟁력 유지 총력" - 데일리e뉴스</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE5xdUgwRUZvbVI3bXZ1WGpoUUo5SWxCOTRoemFSRWxvSVF4UFB1MHdlbmRrX2pZVVcyam1hUzUwbmlINXUzV1lOVm9neWlxNzdVYUlqY1BkQnp0OFFwWU0tUTd6ZkxxbTF1YUYwODZrZw?oc=5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Wed, 01 May 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>현대모비스 품질</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>뉴스1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>현대모비스, 車 반도체 설계부터 품질 검증 등 전 과정 인증 완료 - 뉴스1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFB2NUVnemtiN0pKd1VwOVlyLUFqLWs4QS1YMEFwUGlCeVo4dVp3Zy15UW5vcVhOVDVIaTZyb3QzbDVVY0NzVXktanlfLS1jUDktVXF6OHhPMloxazhhcWJMcg?oc=5</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Thu, 21 Aug 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>충청매일</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>하이닉스, 청주 M17 건설 확정 - 충청매일</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE90X0JRcjdMcWQtTWtDeE80Tm1JMEd6LVZ0ZGlNRzlGMmhZOXUyT2h6SzdHaVlOWlNtd1RleTdCbHNEOHRhUHpVNUIwcnRheGxHRDJ6bHprcDMxVmMxSm5oUUh5eE1pUVZpU2c?oc=5</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 04:30:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>아주경제</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 中 충칭 털고 용인·청주 54조 폭풍 투자…AI 메모리 선택과 집중 - 아주경제</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1ZZ1JyelV3UzMwWXgzV0ltZ3BwaEk3WHc1T19BMzdyT3RDY1otUGczT203TElfX1NJcU9kY01NRWVvN3FMYXMybEhxNE9tSzZFWkIxclNuRDFuQdIBWEFVX3lxTFBRWHpTQVhhM3dTM2VrUUdobjY3UU1aVF91N0x2UDB6d2VBdXhaLUxVdTJaY0pYaDVjSW5icTlrTVQzOVNkZXJGSWdVS1ZHNDhqNlJIQWhSM00?oc=5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>낸드, 2027년 물량 완판 초읽기…SK하이닉스, 청주 M17 건설 19조 투자 - 글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPOEJ3a3ZsbVFmN0Exd1dBUm1LeWtTVVZzdldpWmJnQUp4MlRlWTVNalg4cjFiM1htaHRGZWdOS0lyc0c4a3VBRmU3c0VUc1o2OW1HSFlJdEl1T2dqMXJONTJxUUI3T3FFNmJsc0lqR3pPVUF0WllTN0dBdDdoNzg3dHhjb0ctNlow?oc=5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sat, 08 Aug 2026 19:15:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>"용인과 청주에 54조 투자" SK하이닉스, 中 충칭 공장 지분 매각 검토 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE11N0swb3hTLVEzYmFjRmFGV2RuYmozNUlVb05VR3gwTXFYX2FmcmIzVGZMWlNRTXo2cXFOa052dmJMT05HOENuY0FNQU1ic0k?oc=5</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sat, 08 Aug 2026 11:21:28 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>오늘경제</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[이슈] SK하이닉스, 용인·청주에 54조 원 투자 확정…"공급력이 곧 경쟁력" - 오늘경제</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE0wWEluOFMxOHFJQThIYUdBRzAxal9oMXFEaDlYSmUzSnI3LXl1a05MbkF1LXF1WWk1aFBMRFMtbkJPOHZXSlp1ODdBdng2OXlYVU5yRjd1MU1QaHRBWndLV0FvOUpxUGZSZllDZl90N2MxcUk?oc=5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>경향신문</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>청주 SK하이닉스 공장서 불···유독 가스 누출돼 직원 3600명 대피 소동 - 경향신문</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE4xTFg0MmhKMVNBMnFNd1JMR09sRHZ2N1lwR1ltSzdabWpURHR6b2R5eTJtaTZKWF9ybElxaTRWV05ZRUZhZzJ2eUlYelpmQjYzYnJMQlBNVE1fd9IBX0FVX3lxTE5hRHRDanZmS3FrUWVnYjltMUdqcTJXa216MnM1VzRhODN3N19TbHhzSk40Qk5tdkFjYmIyd05zSVd3eFZ3M0V3emZySEJCczlyN1NydGR1YU5TWUtCMU80?oc=5</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 이달부터 M15X 신공장서 HBM4용 D램 생산 본격화 - 조선비즈 - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPRElnN2tWX3ppM3gxcnhOZzlqVHpXUUxUV0NxRmJJSHd0cFVfeWwtb05CencweUxBR3Y2SXZTeldOcEpCQUpWclptaDlJczNjQnFyV3ZFLTE2elFXZzl2em9oQldwU3czX25rSldrbjhub2ZseWtMbVlvd0xDcDUwQURB0gGWAUFVX3lxTE1aa1V1SFBCYmtxeG5ubm40Z1I5eEZ4LTBMTlNWUVFBVHZ1dDRhaDVKYVd3dXFDb1YtcVlNWThRZnBER0lkcHdXYTUzMVd1YUxZU2paUC1NcnBBc3RfNUhQaW8ycXZjY1oxLUIwcGhpQlZ0VnptTHpLRDhPQjNYMkpISXU2QmRheEoxR1BYalhHRW95Y3BZQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Fri, 10 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>에너지경제신문</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주공장서 불…3600여명 대피 소동 - 에너지경제신문</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFAzZjBNSG90RDNrc1NpajlsOHlpU2thalQ0QWQyR2FWTXNFLWF3dVJ1bGJxVHlxY1NEbEhtMjdUd0VtX1ZnejltMEc1RjhKTy12Wl9nbmJSRmhxZHc?oc=5</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Mon, 01 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>서울이코노미뉴스</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 청주 M15X서 첨단 D램 생산 확대 - 서울이코노미뉴스</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5TMC1YWFgxWDBsUHNOM0RaZDZaRU9TSEN0S09tR2cwcDdVNjZPc0FxWkJYMVI5MFZwRk5aeXlDRGJoTXEzSFRoeVZtMVpNSDEySW5ZbktyNmRFOHIxVDBpVU81TjBkWkIzZmdWUXdR?oc=5</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sun, 12 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SK하이닉스 M15</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>충청타임즈</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SK하이닉스 청주사업장 반도체특별법 포함 유력(?) - 충청타임즈</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1VaXBPRVdvV2hySUZRLXVMTDkyMEh6c1pBUWlmeFZKMkZrZHRGdlZHVm44RldVWXNBMzlaalZMZDFTTEMtaHhpck45elltMnNJbWNBd1pKTDl5QmdodXc2cHJxR3hvV2NL?oc=5</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 10:32:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>HBM 12단서 8단 후퇴 검토…삼성·SK하이닉스 수율이 판 가른다 - 글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQU25KdjJ5UjdodEJ1NU5nUjhIMmg4SnZMMS1mNzVLZkJoWV8tMThtNjc3WGNnZWdLZHR3REc1VVI3bS1yTHdvZkJPUkU1T0xBcm1CbEdpejc4cTEtYTE3N08yUlktZnE2Qmt0dWdwcC1oSlcxRVo0UWg2U3FXZFhqa3ROVzAyZkJW?oc=5</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 18:35:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>블록체인투데이</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>드디어 승부 뒤집나?… 삼성 HBM4 수율 80% 육박, SK하이닉스 맹추격 - 블록체인투데이</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBGcnp5M2dnNVBSd1pBTGJsb25LUWduek5ERGs0aEdnbzcwX1QtbHhPRVBCcjFQQ2l6YW56eG1GMTl4V2xSYVhncTRqWXYweDZIeGs1WTB0am01amg5VXpqbjJKSVRuZk8ydmlqdFNvc1Y?oc=5</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 13:49:03 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>전자신문</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>[반도체 라이징 스타]퓨리언스, HBM 공정 수율 높이는 포스트 CMP 세정 솔루션 고도화 - 전자신문</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE5LTWE2OHJCOFhrTHBlR003R0ZzQU1RblJ2OTVWMHlhdlprMEdRek0zeEI3b3o4TUxmbXRLRUtDVWNrTWFTN3FZd1diOGxaQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 05:14:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>서울경제</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>삼성 HBM4 ‘황금 수율’ 달성…공급 늘린다 - 서울경제</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9kU0ZBOTF2WWpnUm5XeXZIUVZndGwxdUs4V0thTUxBOWczek1sMFRadF9zd2t6UTNYbWlYSTVfMENzLWYtZXRvVmozZnBKcHByMWfSAVNBVV95cUxQVUkwSlQ4ejBQa2dXdklEMlpoWGRxMzZEVG5UQl9jaVpCeVNIUFN5cW11NUN0RXphQndEWG5ZWmhoYnZpMDN2X2VuMXl5eTBoQTRUSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 09:12:48 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>HBM 수율</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>프라임경제</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>한미반도체, 'AI 병목 해결책' HBF 상용화 임박 '수혜'…"핵심 TC 본더 수율 검증 완료" - 프라임경제</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE9wUFhZTXZ2OXJsNzVVVnN2cDN1aXp6R21MOHFUaTB2dTIwUkY0WUZsZzNSLW5FQi1WQTFobGQ1TGYzMGtlXzhtaWZLZE5BSWRtcENLOXNnbWdVYWFjckVTUjQtX29jSTNsMXBqdGF6blQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sun, 09 Aug 2026 23:14:49 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>파이낸셜포스트</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>[인사이드] 'HBM 성공 주역' 구자흠 부사장이 밝힌 '삼성 파운드리' 공정 경쟁력 - 파이낸셜포스트</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE94UmdlUmxpcjdOdnFsTHRXSU1RTklsRHI5Nl9yR1FERXVrZEYtS3NpVlR0QlhnMG9sckF0SVZPVU5jZ051SWpaTGFfWUE2WmpWYmJ6cDlRdlhDTkM5cGpmNVR0R01NOTBUbTBUZWdCZHhpLXBZ?oc=5</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 02:43:35 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>뉴스투데이</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>[취준생을 위하여] (55)반도체 후공정 담당하는 삼성전자 DS부문 ‘TSP총괄’은 어떤 일을 할까 - 뉴스투데이</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE9NX3dGTlBDUVZkMEpVeWtKT2V0Wkd6VjVMNlRyb2xFSWNyUXh3WXpBN1F5dnhWM2pXNnlqTTBLalJKeC1uSUdETQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Thu, 05 Sep 2019 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>아시아투데이</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>파운드리는 패키지가 3할…삼성전자가 조용히 키우는 TSP총괄 - 아시아투데이</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5TeHpUMHlFcjJtVTdQLUZBYmw2aGxxRWpsOEM3QWZ6aXRfekhCZnI2RDZjU0k5UURqOEdOUkFScmdDWm5pX3BsTWo0RUxKS1dMRVo2UERuLW1DSWNvYU5XRDZOMWNiZ3YyZC1VTHRB?oc=5</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Wed, 05 May 2021 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>녹색경제신문</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>삼성전자, “반도체 후공정 라인 무인화율 30% 달성” - 녹색경제신문</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE5Zal8tc1dsQ2c4cndLWVNacmxSUnlQWkVrUWwzTHAwbVRfcE8yUHlaWjNFeFYxdjJmSzh2amhiS3djUWxvRWpiZWdwNmJSVFBYVk5hTHNTa3RxeGFlY09XNzB6LVprbV9l?oc=5</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Thu, 29 Aug 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TSP 공정</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>전자신문</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>뉴로테크, G2셀 방식 TSP공정 장비 중국에 수출 - 전자신문</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE9XVU9iM0xmVjNvSzllNWZWTzhTd2p5Q3V3VUM1N0J5eEY2Qm12U2VJTU0zX1FwRW5ORmlDd3dNVjFUeXBVcDFzRzdXOA?oc=5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Wed, 05 Dec 2012 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>어썸레이, EUV 펠리클 멤브레인에 75억원 규모 투자 유치 - 디일렉</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9fVW9sT0d0d0hhWkxjdXZVWDAtVzFkQ1hydl9DaGZLNnNVRWVSa0FFTHdkRXpodk55R0R4OFhxUS0za2ZDX3pwTkpuVjhFb2h3U1dVeG1PUG5admVBaVYzNXhfMW5Sdw?oc=5</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:40:45 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>삼성전자, 1나노부터 고개구율 EUV 기술 적용 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9PakF0dkoxUE9Jdk1Gd01raS10NUpzUmdaOVVjV3R5SmZRM0NOQmozVlZpU0xjZWRhOHRjY2ItYjVQcnNmcnpBZWZ4TzBIU0U?oc=5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:17:36 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>지디넷코리아</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SK하이닉스, EUV 공정 고도화…신소재 'PSM' 도입 시작 - 지디넷코리아</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5udkV1Sm5VbjNVcHBhMnNpWEQ0RWFEWGl5Y1ZfYm1pcHBFQmVUMjBTTDAtQ2FFVWpobmxHNTlnRGlhU2lyb1JERlAtX0tNeW9uUVNEZlBR?oc=5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 06:50:33 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>시사저널e</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>SK하이닉스, ‘EUV 멀티’·‘하이NA 싱글’ 차세대 패터닝 전략 다각화 - 시사저널e</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9wZmJlM2pINExCSWIwMlktdXRmNnZVLXdPZmhhR01INzZEMm02YkplX2lUZ1ZtMDZYSWRZYk02Z1RadGlGVTQtVEtxbDRRakcxTnFpOWlnN2F5eGtCdGNtN09UT3VrVzJYNTdVcjdYMHBnOGpna3fSAXZBVV95cUxPcGZiZTNqSDRMQkliMDJZLXV0ZjZ2VS13T2ZoYUdNSDc2RDJtNmJKZV9pVGdWbTA2WElkWWJNNmdUWnRpRlU0LVRLcWw0UWpHMU5xaTlpZzdheXhrQnRjbTdPVE91a1cyWDU3VXI3WDBwZzhqZ2t3?oc=5</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:19:47 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>EUV</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>플래텀(Platum)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>어썸레이, 75억 원 유치하며 EUV 펠리클 사업화 단계로 - 플래텀(Platum)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE9rX0R1SDlkQVU5LTQwREJJMVRWcnU1eVZ6U1MzLTFsWmFIc09XX2k0Y1I0LUJlWGlGb1BsbFpGc1gwU0ZIMXoyRA?oc=5</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 05:21:05 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>High-NA</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>지디넷코리아</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>삼성전자, 1나노부터 고개구율 EUV 기술 적용 - 지디넷코리아</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFBvdDZLbGFCQjZHRDk4VFdKTHA1TU5ZX3BIZDdlOXhJSE9TUkZaX2M4bFdQZE56dXE5TzZWLXdrOUFjTjhzd3UwNFhpOVRETGZXUTFIdXhn?oc=5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Tue, 11 Aug 2026 05:16:23 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>High-NA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Chosunbiz</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>인텔, ‘하이NA’ EUV 실전 배치하며 차세대 파운드리 ‘속도전’… 삼성전자는 신중 - 조선비즈 - Chosunbiz</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQb3R5cERDWGFnYmh6T2wzTExKRVpZSzVkdFBEWXdXTTZ1R056Rm12cUpQdVBHZE5jVHhJQW11Mlp6WDRNTHdwZ1B0d054dGJqY25ZMHIzbDlyQzRKOXVIZDI5enZXZzRsNDVtNW5sLWhncm1VNHdjV3hVaW14RmRNLUVn0gGWAUFVX3lxTFAtOV9INlRKUHl0VmI3aXd4SHpMTXRKRGpGcXRiUWJnTjlJdWs5c1VZWjFHUEFZQnBQc2hDVE4zTzRKWnZlOTJHUEs5VlR6OXdSUlVoZ3BnQlFqdlF6dlE5ZW5wNEFYYlp2cW14M2kzTlFhcTRvQ3BrcENkVmFsVjZmOXoxY3hLa0FKN3Y3OEZNMzBRdHQyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>High-NA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>수천억 하이-NA 도입하고도 속도 조절… 삼성, 2나노 수율 잡고도 양산 늦춘 속사정 - 글로벌이코노믹</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPMDZhMW9DVWpJdFBaX0N4ajFaTDFIMTZPNklLeWpnZWVXTlBWc2dxdkE1TzgzOE1vNkZiamtveU5xWmhxMnV1T3U0eEgxMTVLOWJCemFsdHdqcDJIUHZUMHR6Z2FiWl80RU85YUI1UlVJemJCN2ZWREhMT1ItVHIydkJRQUQwSkJW?oc=5</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sun, 19 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Dry Etch</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Spherical Insights</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>반도체 Etch 장비 시장 크기, 공유 및 예측 - Spherical Insights</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQbm9iMmNjd3VSUEZNWWl3NmFBLVFxbFVsTERCUUZTVUpwdGlaVG92TGZ3eVR2MHp6OUdaZVlOMEFhQ0ctUlg3VkFjOVEydEVhcVVFQmFjOTMtMmZma1kzb1dYNkJvczRrcWFwUFk4ektKWlhNMTdBbjNGc2RydHBPcGo5c0NtVXN4cFlYcGp3?oc=5</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sun, 26 Jul 2026 01:26:35 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Dry Etch</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>잡플래닛</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>식각 공정을 지원하는 쿠어스텍의 첨단 세라믹 솔루션 | 쿠어스텍코리아(유)의 비즈니스 뉴스 | 쿠어스텍코리아(유) - 잡플래닛</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wJBVV95cUxPMGtDX1ZWMXgySkh6R1RUd3RrbG9lOU9iM1pJcTdVNUg2WTJYQi1uVUdWWkxXY29GR2k3VmNrRDNJc2JzeTI3QW5nOUtWYTVSbXdqc09tOVh6bG1zcXc4MXUwTHYxQkk2NGhFWTJoenVsRnVzeXJ3djdRck1RT0IySnUxcmxzc3otSmFDMlZZaXZHVldCQTdxVHUzNnRFc3Y2QTExNTc4YTFXQjRhY0tzQ1JXRWpMc044Q3o1UVZIeUxnR2hzaTNQa1U0a1hVMmQzSldQTDhMQ3pMQlhiX0RUU3ZwTEZheFVWY2IyazhZLVN0Zll2cGNleVFhLU1IaUszMkwydWpBVWhhR2VhSWVvRGpUWENWVkV4a3RKazhfbU5OY2tPSWFfb2xrZUhaNXIwMzJRRmRxX2xfSVU0X0h5VnpVQkVDaVUxbUNtX1htYXhVSmxhV21mRWpKbEJvSW5rRjZmN1hIaHhkWWM?oc=5</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Wed, 22 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Dry Etch</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>elec4.co.kr</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>[연재 기고] 반도체 및 디스플레이 공정에서의 친환경 건식 식각 기술 동향 - elec4.co.kr</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBPaEVKc1Z2QVlsNERfb00zLVRac2ltanRBQ1pGWmpZMHNzNHNMQnUyRFVhSi1hOWhYUm53Yk1oTFRVTmtrNUg3Q2t1LTBqVzJpbDJKR3BDNjBadmR0d19OUi12X1VHTldwdXhJN2FR?oc=5</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Mon, 18 May 2026 02:14:47 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Dry Etch</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ppss.kr</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>미세공정의 열쇠 '플라즈마', 반도체 식각의 한계를 깨다 - ppss.kr</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTFBubjJlUVBtTnhLRXZubVFQa1JFckJZMGxqaktMUS1WWWpaY2JSdE1zSnhmaEJsWXFGUjFhS2RYd0RYX0xWZVlVRy02WmhKQW5rUnJ3ZnVjT0w5VURjcEpwMURKVk0?oc=5</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Fri, 05 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Dry Etch</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한경매거진&amp;북</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>반도체 '쌓는'시대, 칩메이커 뒤에서 조용히 폭등…식각이 뭐길래[반도체 8대공정] - 한경매거진&amp;북</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE43MlBUYTM4aHB5OVRhT1JOQ3F0cjJWa3NOeVNDbEhBNkNsck94RnJjS294V2hETHpWcnR1SHZpNV9kejkxTU1LRGNjYW8zb0FXVVpzR0dxTk04VERpd21waGJjdThoRFVWbzA1dg?oc=5</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Tue, 02 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ALD 증착</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>시사저널e</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>삼성전자·SK하이닉스 증착 공정 ALD 비중 늘자 주성엔지니어링 '방긋' - 시사저널e</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE1zQlh2Q09LVjZtenJ6YV9lcWtWRDBaNlJXWUs4OE9MbGhjZGtjN256QjFtZkR5ZklVLXI1X2c3V2JkTmt0d2JIbUVTYkloR0dTdndUMnktVktvdk80X2l4MzFvZTRWeUxpS1ZTZHJVWUVpZ9IBdkFVX3lxTE1uQ0xXM3FYVEMyazJIV2swU2prcU90Sm5KNFc2MFJudHY1UDQ5U1BEdURCazF0bUY1UExVNlhTek80T1hUSFB1akNZRHRZZUlyVDhEWjd1NUlFbWpBMWVZUnA3aVNJbVRlWmNaX21lQTZyUmJtcUE?oc=5</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Tue, 14 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ALD 증착</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>조세일보</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>“원자 단위의 한계 돌파”…3나노·300단 시대, ALD 장비가 뜬다 - 조세일보</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTE92N3NYWnJGZVpwVWVsaXRuWHVFb1BvSE5tdDBGTDViN1Z6S2Y2M3FuLUM1cm5oNlM2OURrMjVwb1RQTmpVaFZRTnh2XzZnYS1PcWZPSzhjU1BYQmpqMnJn?oc=5</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Fri, 15 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ALD 증착</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>어플라이드, 2나노 GAA 공정용 증착 시스템 2종 발표 - 디일렉</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5vakhtQ1ZRcndRNHMxMlRXNFZKa2RkM3NKenhtd1VQMmg2Ylk2SF94WTYtRUFneDJQbVBMXzUydl9JZTJoSU9td2Ftckd5NS0zUWN6cGsxYktfdEJ6R1d6RUFXcnFOZw?oc=5</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Wed, 15 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ALD 증착</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>대학지성 In&amp;Out</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>한양대 박진성 교수, 원자층증착 분야 세계적 학술상 ‘ALD Innovator Award’ 수상 - 대학지성 In&amp;Out</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9zTHh1ZmxiOVRuX0tBSHRydXdGMjFHMmpnWTAxQXFpOUJDdWVHR0gzQ3F2NWp4R1JrQmJBc2lObUYtUXlOZHBvNlo5U2hab1FTOXRScFBKWGFJOHp4Nm1RZ2dvNHUybVN1cGl0TQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Thu, 02 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ALD 증착</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>녹색경제신문</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>[세미콘코리아2026] 원익IPS, "낸드·로직향 ALD 수요 증가 체감" - 녹색경제신문</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9kTWpGRjlUUkhKZ2dQY2ZsMXVHRkZscVhqNmVEeVpOaTlLcFdtc2ZQVEU5UllsM0swd1p6Y3dFRXlFdjVzdUpMXzhLR1k4NnRZT2tlQVVQUDRGQXFnMW9ZVjBoRmtFa1lO?oc=5</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Fri, 13 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CMP 슬러리</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>케이씨텍, CMP 공정으로 패키징 영토 확장 - 디일렉</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFB6OGhXeThrSkdCWU1veENFQ2drcW13dzNsTlJZdTRJMm9Xc3VMZWhCMGxMNk5GOTVuWmduTFNvS2dsdkxHTlJ4QW1lRlRLb3l4UmhZNTZTMWR1S1hRUzlZRlItU3NDQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Tue, 28 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CMP 슬러리</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>마켓인</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>와이씨켐, SK엔펄스 CMP 슬러리 사업부 인수…반도체 소재 사업 확대 - 마켓인</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE0yRWpKRmVIR0hDb25nUmR1RF9CMjFBbmR0eU1lcXA4SEZCc1RxWXdISmE3djFkLWs1bVY0S2s4UHZjQm1pTWNpVnlHTjB2dmo3c0ozVElTbEZUVHlJQ2xVZW5lZjhvbmZHR1BOSkVCVVR6SXc?oc=5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Fri, 24 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CMP 슬러리</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>연합인포맥스</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SK엔펄스, CMP슬러리 사업 110억에 매각…사업 총정리 - 연합인포맥스</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5vRWxETU1fMnFoNVpYdlNHVDdVNEhGN2Q3cFMxZ0hvY0FxMU1QT1JOUXRBVHFHNm1jZ3laX0p3UGFnMFhMd04wVlkwbXAzOFoxcXFoUUprdTV1blo2NXRTejNQWWNfRkQ0bEVpVUtnXzQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Wed, 22 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CMP 슬러리</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Straits Research</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CMP 슬러리 시장 규모, 점유율, 성장률, 분석 (2034년) - Straits Research</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE5pS0NuazBaRzdXNEV1ZVB6V3dZa0g5RzA5eTAwcW5vVmpaT0dVR2pTV1hQSDV2d25MMjlvVUl2YXQ2ajBvMGZ3Z0l2ekRzX1dfbGFSbEFscXZ5dG1hdHFZc2pSdkFZdw?oc=5</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Mon, 13 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CMP 슬러리</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>케이씨텍, CMP 기술로 日 독점 반도체 핵심소재 국산화 추진 - 디일렉</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBJWjBOTndxQy1NRmh2RHNGejRmeHkxNHJJNjN5Y0Q5SW1pUXEwcnlleEVMTVpBYUdLZzlFUFhMNk9MWDk4WTc1YXA1MzJScHA4cUZrY2w1a1VtalZ4eEtHenFYYmJnQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Thu, 07 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>교수신문</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>한국외대 임주원 교수 연구팀, 이종접합 반도체 광전극 개발로 차세대 광전화학 전지 성능 획기적 향상 - 교수신문</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTE9QVjBlQnkwdjBqbU96NzU1dU9HbVpWRUg5OWQ3TVlEanJDSUxUM1lGakhlZ1k0SXpkd0hWeW9zZmc3ZzdTdUNaWmwwVklNNW53ZEtKeEdPbzNoU1V4bzk2Y2tEWGRnX1k?oc=5</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Tue, 18 Nov 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>뉴스H</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>한양대 ERICA 이승현 교수팀, 차세대 그린수소 촉매 설계 전략 제시 - 뉴스H</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE1BM1FLUk5rX3NEcDczZ25xdjBsN0lTVUtNZnBVQnphaEZ5MDVpNFJMMlZBN2doN21WMFhvTTBuLXZ3S1hJYzRvMTV6Z056M1NNZFJLUGNtVUxEZnpXN2ZFdTRKM1hvRnlWQW9F?oc=5</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Mon, 08 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>토픽트리</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>“주행 중 갑자기 멈춘다?”... 현대차·기아 차주들 10명 중 1명은 겪는다는 '이 결함' - 토픽트리</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQQnBDcVVxU2Fxa3c3ekx3NTJoTEtQNWlCZFJHdWlFRHZ6R2NXRHFzVDRVQk5nLTVoUWZwS1pGSHBzZmZnQ2RSQk5UUk5nVWkzdTU1Q0ZrVGg2WXVMbkF3WUl0RjV2VEpIVV9GUEpEYUNpVnAwOUNNdXhqT2g0ajRVMtIBiAFBVV95cUxQQnJ4MXJYNEZ1cVo2ZnZjZ29IRXBsT1l3WVNMSVhLOHg1QlJFcVI1dGZUbDd4LXdzNGpjOHNmcEtHNGt4dTVKRVkta2tKaE5hQk54OUJGZGJPUzhkSHJ2b2F2bWhyb3Q1c25sODlPRVR4bUNyMmhlMTg3RGJYeURkdjNQZVZVdm51?oc=5</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Sun, 22 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Korean Car Blog</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>현대·기아, 독일에서 15년 ICCU 보증 발표 - Korean Car Blog</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNRTRpVG9MaXIwaEJwS2pIcjd1dnJIODJTZGxBbElCdWhuRTQtTGhoTzFlMDlpN3JFMUdnb2hrZ2FRUXdRYWNQQ3V1UHFXVTYzbVZ2blhSRUJ2UHZ0RnhFU20xdGVsdGtZS1NSbFNUNmtlWDRFRkE4VDRhU2VBbXRUYXNONThFeHItdmhuTk5SRkNHV3ZOQUVPa0JEVWNHMmM?oc=5</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Defect 제어</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>뉴스프리존</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>한양대 에리카, 차세대 그린수소 촉매 설계 전략 제시 - 뉴스프리존</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE44eEtsRzZtNmNEQkl1NWhnbkZORUEtM0dJM3B6UHFxemdBMWdaNUFvT05mY1ZYNXdhc1Q3MHdLRGkzamVSMzFMeHJvcjZibFJLVlNTaTloUEwtV0xpbGtaR3VtaFExdnBTZEJOVjVsUWdoZGPSAXdBVV95cUxOYVFVdFJHZm5sYl9tZEV2d05pSGhyTm5RdFVNTmFFQzBRRWQxbVNfb2tTWDJndWlpcXZWa1lhQzhxWVBZVlZtb1lucWx6dVpHcE9oOWpJNWRZamNKbi01Ym5SZXlnUFlrRjk5S3ZEdXRZZ2FhcE40SQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Wed, 26 Nov 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>챔버 파티클</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>마켓잉크</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>티로보틱스, 진공로봇 하나로 여러 챔버 연결…평행링크로 팹 공간 줄인다 - 마켓잉크</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1FQm5jZEdzampnNVgtRlAxYVRacFl1WnJFZmRXaDRyTDd1T201YUE4cEVMWkVRR1VySWg5TVJlc25zOHRSQ0RGR0tackVuSzRobnduQ2RiQ29ySzNnWXJVOHc1WUVMRFZQemdOQU1R?oc=5</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Mon, 27 Jul 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>챔버 파티클</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>라온로보틱스, DD 모터 로봇 앞세워 신규 반도체 고객사 진입 - 디일렉</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBRVndaMmowV2l0SEhqSXYyQWFOTzZVVVNTRmJPT1RKZGdpaTJRMTZfdEcxeHdOQ2pQSFA2SzdzeFpSUGdMNzBPX2JsbHQzTXVHSnYzdkdLbGdwVUFZNG5fLVFrSHBWQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>챔버 파티클</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>칸(KHARN)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>신성이엔지, 차세대 반도체 인프라 신기술 공개 - 칸(KHARN)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5TR2llQTlZMXZqRkhjUG5acHo3dG9uRzZZa1FvMjI3STBYMDctcXN0OW9qUUhIRVFnRW1kdzBJQVBQR0thcnRqem50NzNBUXJXdkNCV3VJMU56bDA?oc=5</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>챔버 파티클</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>경기일보</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>“HBM 공정 수율 잡는다”...신성이엔지, 정전기·습도 동시 제어 ‘일체형 EFEM’ 특허 공개 - 경기일보</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE1VZmtJQ1RYdTh2TExVVFVUY2tYUmpIVkRtQ3l3ZDA4ZktZb19nX0xQVTRYalcteGh0d0lic0xiazhCbG9RT3ZLYjZrdzlEUTNCNWJ0MjB6cnEwNTQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sun, 18 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>플라즈마 제어</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>헬로디디</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ITER, 핵심 제어기술 첫 실증 무대로 KSTAR 선택세계 표준 검증 플랫폼 입증···韓 핵융합 기술 경쟁력 재확인 - 헬로디디</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9mbHRlQlU4amdZTXlxQ1VJLWRrSmY0anFHTnh6ejhxMXNJZmtKV2k4RU9ONGFiandSWDJPMDRfdExLa0ZZR2p4WDdFY2pfQTFaM0xBX1FnWXVmeXpHckZNVGx6MVhOU2Y3UWc?oc=5</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>플라즈마 제어</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>시사프리즘</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>[심층] ‘태양을 지상에’… AI가 가속하는 핵융합 경쟁, 한국의 선도 기술은 어디까지 왔나 - 시사프리즘</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBiZExPYzNpdnVIeUxMTXI3Y3RUWUlwRWF0czE3Q05yNXFRLVBxeDhnRVg4cTJucWZPb1JfTFM1VVBJTG1rTjZlNG1GZElUcXowR2tPbFBDTmpOOVdrSG5MODNkYVVqRU93?oc=5</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Fri, 06 Mar 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>플라즈마 제어</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>조선일보</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>AI로 ‘플라스마’ 통제 쉬워져… 핵융합 발전에 한발 더 가까이 - 조선일보</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPUFJCWXB6cWs5cFZDNXFkMElJcE9vNkNTRHJqV0lobmNHQW5Nems3SGR0T3M5bE9WZUtORnI3SWhyLUNXUFZGQWstNlFfS1lROUV2Si1oZzdaSnVTd2tiRWZSLUxSZ1pMbEw1YVgxU2p3TFJNMDl0SXRHa0tHMnVLVTFhZw?oc=5</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Thu, 23 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>플라즈마 제어</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>동아사이언스</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>태양의 원리를 지구에서... KSTAR, 텅스텐 환경 핵융합 실험 본격화 - 동아사이언스</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVEFVX3lxTFA1VkpKMzhvUkVUTkxOT09EcXNjdVVpLXZUZHV3TXE2czVnRUlFVkh0bFFjYjFoRUJ3Uk05TDF2cWJod0xjV1hIZmJILWJJSDFUeVN3Rg?oc=5</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Mon, 27 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>지티티코리아</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>스위치·오버레이 구조가 만든 SDN 병목, PON 기반 전환이 해답이다 - 지티티코리아</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE90MkU0QXN2SzhqUmh5YXhCNXJpZWRUVkowRE5TX1VZNDFZbjVibTZ1UE5NcS15SWRKUEJYYlZqRmFjUVQ0d0R1M0ZEdzExX2NoRmNiNF9GM2c4N0NMdEZhS3d5RHhEVmczeEE?oc=5</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Thu, 05 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>핀포인트뉴스</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>노광공정의 핵심 '오버레이 계측장비'… 오로스테크놀로지, 기술력 입증 부각 - 핀포인트뉴스</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE8tOGJiMmNETUU5UUJSeDM1T3JoZzJ2anozeF9RQzhZUHJZT3F3ZGRUV0QtcFQxRVVQYWtPcXB2QUJMNHBySEtYaFVwLTJZTWY5QThyVnQ3SjMyMXpORG4ycE5mV1JtOHhieDduRzZNYjlDX0HSAXdBVV95cUxNVFBRR0RWSmUwdUJBalVrSkxDdWdvbmRIU2RJWnl4S3lBUG15TmJFX0Z6QlpSMFJJY0hxdE5aRy16cmdmSkN0MlhPUEZuNnNuRzJGV3huLUFDNXJRaG5uSkVmM3JsdFUyVXJGMGJJV2puMGpWQW1rQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Mon, 04 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>elec4.co.kr</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>[연재 기고] 디스플레이 공정에 반도체 노광 기술을 어떻게 접목하는가 - elec4.co.kr</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9ZYUNoUkhPOWFvUXdiUzl5TWNoUmNvT3FCSGNKbjJ3VklzaTRGaTRyTFFLaDBLTTAzbFcxQV9sX2RBSkVKdUcxZjZDZkJueGc4QzlHVF92N3JGX0xpRVUwcGpiYVpEbGt3ZU0xQVJ3?oc=5</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Tue, 14 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>보드나라</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>엔비디아, 초고성능 측정과 오버레이 커스텀 추가된 프레임뷰 1.7 배포 - 보드나라</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE1JMnA0aU9OXzNwQm1oZEJjTWxjSmdnRndWSGFIUVpQX2swWHBuOHhjalU3UjFpRkF3dGN1UnVZeWJCeld3UXlIM1pCVUkwc1p4UEN2dEJuWVlrZTBod0FxU3VPRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Fri, 30 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>반도체 8대공정</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Overlay 제어</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>비즈월드</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>프랙틸리아, EUV 패턴 제어와 수율 향상 위해 스토캐스틱 제어 솔루션에 '오버레이 분석 기능' 추가 - 비즈월드</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE51UUM1MjdmSGw5NEpvbmlOam1KTUhoVWRxTEwtcnhJQmZvYXVIaDNUMm1tZ3h4QzFIaUF2aU0xMk9VQjUtZGs1UGdZZEk3TmY0RlpNRnk1SjFOYjNUNEo4S1IyT0tNbm56ZWc?oc=5</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Tue, 27 Jun 2023 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PRESS9</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>롯데에너지머티리얼즈, 판가 인상·수율 개선에 실적 반등 기대-NH투자증권 - PRESS9</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE84b0o3blZFUjV3b1o1TVBhZDYtUHo2QTlodXpzMTNTSlV0czNjc0RvZmhhRDZVY2cwZlp5cVl0MUFVRzNCV3JkR1JDcHMyVThId0hyZVZSYTVIS2U4ektQd1ljTm5LZw?oc=5</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Thu, 06 Aug 2026 23:50:13 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>dealsite.co.kr</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>삼성전자, HBM4 연말 수율 목표치 85%로 상향 - dealsite.co.kr</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1YOXJiM1lVZEc0RXlKeGhpOEJHQy1tVjlOS0xMbXI5cFE3R2FBLVNXV3Y0WTYzWnA4V2Q4OUJTcGp2NDdTZDhlSUg3dWlDa0E?oc=5</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Fri, 13 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>아세안익스프레스</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>마이크론, HBM4 램프업 순항 ‘2027년 HBM4E 양산’ - 아세안익스프레스</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTFBJY0hYWTgyaUt5enkxVmZJRWVwZDVEcW5rb2ZnNkExaHRDRHItMklpOUJhTTlZcXFyYzVzakw3RlhKb1UwX2hYUWpsLVVGQW9IMWpuNC1zV0NZYy1jNFN2QklINmYzQV9Y?oc=5</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Wed, 27 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>아시아투데이</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>[컨콜] SK하이닉스 “HBM4E 샘플 공급 완료…27년 본격 양산 목표” - 아시아투데이</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE4yLU9UZncybXpsTDRfQ2VjUnRfdWVDdGthdnEyei13cVE5N1JOWVVVejE3WTlPRU1xNDAyMHliVEZqa093UVpFM3VmYV9KYU9DUG5vS1RybW1kdzQ1TXJOcDFWREJHQ24xc19yU3ZB?oc=5</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Wed, 29 Jul 2026 00:49:39 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>수율 램프업</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>IT조선</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>[단독] “손익분기점 넘겼다”… 삼성전자 ‘1c D램’ 수율 60%까지 개선 - IT조선</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE5WXzhWU1d3OHg1ckluMzRkU3N6OGpnbm1ZbzFfWGJlNXI4enV2aXBFbGpWTUJDTTBlQ0xuemVOSTRWNHFiQW8xY1dOdk1OWFlhRlR5S3pmVmZmZmFVZGZFZy1sLWdwQmRGczFMRy0yWWvSAXRBVV95cUxPYXd3WW95MnRramRUelBZWGcycTM5cXU3SlJ0Vm1LbG9wd3M4cGFvUEJVQlRIdDdPR0I5SWpGOVJDbUtSMFBDbDhxdmlVMjdCU205U1JwUlBUbFNELUE4UEltZF8yUHZwZ2drYmlCWFRybHU1Sw?oc=5</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Fri, 16 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>IATF16949</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>한국경제</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>알엔투테크놀로지, 전력반도체용 세라믹 방열기판의 IATF16949 인증 획득 - 한국경제</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBPYm5SVjc2Vnk3bW5PWnZkdmQzQk00Q0VpUjNGY3ViNTkwV2wxY05nUHIxTnpoUENDYlAyQTlTR1hhOUtiT0NQbjdhQllYQXl4d1g0U2R6MG9tZw?oc=5</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Wed, 27 Nov 2024 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>IATF16949</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>프라임경제</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>시노펙스, 베트남 사업장 '국제 공인 자동차 품질 인증' IATF16949 획득 - 프라임경제</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTE9jLVlPS2UyX0pHSnBVajEtdUQwVmd5QzlNcVdwUUQtWXBIZFh6cWRROE15SWI0MXZGbjQxd1Vfd29iUGJxdXYtYk95OExyR3Rwa0RpZjRMT3dsSHRva1B3XzJSQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Wed, 24 Apr 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>IATF16949</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>에너지신문</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>시노펙스, 옌퐁사업장 자동차품질경영시스템 인증 획득 - 에너지신문</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFBZOTVkY0NxTlJ0MmV4X1RnckppbEd4NW94Q3c4ajZZU2R1b2pSb3lzVnhoaEhTMXJqNlp5VnY4VGl5TmQyLVQ3Z2dQaHFJWmxjWWphUk1oX2xoLXBscW8xZUhpelBzNzVLSGxlazRXeVBtdw?oc=5</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Wed, 24 Apr 2024 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>IATF16949</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>samsung.com</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>삼성전자, 차량용 반도체 기능안전 국제 표준 인증 - samsung.com</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugJBVV95cUxOWWxfWjhGOUI4YnE1VWphZkJlaXhuMlN6akNTV0tBb2RPTVRqcmRFVHVRUnpOazc2bXpfLTdYTWo4X0lVNFdiOFF1aElIb0pFRnNUNHJCS2wyTmpUQ1ZMMGNlQTNQMEFPcWNoSFJfY0R2Y2xTMmM1TDgzZW9wb05FN3hjMjU2ODRMVmFOMlBzV2dHYnJ3MlRnQS1mUWJQYll2Mk5FZGlBWTA4OGhVY2tOQTgtVFlYaVIwUV9lb0dDS1lYblJIVHM0c3pFTnk0MG83d2k3REJWOXAzUXlCenZTbHZpcl9hTkNkMnJzVHlBOFRXVU5BRzViTXAyVUpYSmJvSzRUWkpGTENhYVUxNUEyZWctLVB4TmpMQkxMSEgtRHRzck54QXNHcHNheWItUDI4NHdRN2k1QWIxQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Mon, 13 May 2019 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>센시리온, 전기차 배터리 열폭주 감지용 수소센서 공급 - 디일렉</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE0yYk1IeEZqQXdiYUtyNUFfV1JTM25LcHBYVjh3TVY0R3h0SmRHWUZIOXByeXMzWlRCdXMwY0IyMlJLRlE5ckhSTkxuSmRjQUZNMi1XNGZabm5IQXRJX1hZZk1pSGV4dw?oc=5</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>지티티코리아</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>전력 효율·AI 인지·기능 안전을 결합한 차세대 ADAS SoC 전략 - 지티티코리아</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFA3V0c2QXcxQjk4OWppeEthNUlNMzhIVlBoaF9DdzRNNDhibVpPOHFMTmQ4d1NlTlJTVXBkcXdjZU1tMEx3NXpNRm5tcFhkajFzNFpoOHBLbG8yNGg5Ny1CdlhNWS1OSFBYVmc?oc=5</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Wed, 31 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>elec4.co.kr</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>전체 애플리케이션 영역을 지원하는 차량용 게이트 드라이버 - elec4.co.kr</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9XdHV5a3JjaFVEYTRZVHNaREVEcWpfemFXVzdmN2djMV9DTWRpSENsR0sxZllGLVk3Q1BsUllCOGktZnB4dEZrZnJWNFljZnpJWGNYa3RHUnIyRFMzczhieDZLMS1KYl8wVHRGZQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Tue, 30 Dec 2025 05:06:09 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>헬로티</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ST, 자동차 배터리 효율 높이는 선형 전압 레귤레이터 출시 - 헬로티</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5YRWlyOFNkSi10RnpGaVFvdkNpR0FGNWs4OGZHclNRZmVMTFhFbkZPVUtBOFBGQTJnUnhPQjBTR0pOS0ZQdnVpbkdteU9CZ0RhbkxCU3QtLXF4bTZX?oc=5</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Wed, 01 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>수율/양산/PEDTC</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AEC-Q100</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>퀄리타스반도체, 자율주행 ADAS용 MIPI 서브시스템 IP 첫 공급 - 디일렉</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBMNy1NeXRPRTVRQXh0UXVjQVhMR1BVS2xHbXllQzhmTzN4bHkxck1Rb3JiSG1GWkdoeFhIU0QtUndsbUowcXJWQlRNaFpXQnRxRkJKLWp6aU4yekdaQy1oZk1UYjdMdw?oc=5</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Tue, 16 Dec 2025 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>mt.co.kr</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>'칩 설계 솔루션' 잇다반도체, ISO26262인증…"고객도 인증 효과" - 머니투데이 - mt.co.kr</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBYTUREcWJHZFk2aTdhSkw2VW5wek1ndllIRnl2QmpKeERTSjFkZzFXSDQwTmo5SHp1WmNBNzV2OWN3MFV1X1RpZ2E5RG9IRW95RWFtR2V2WnZhNmR1YXZNSzJFZVhCV1NPS1HSAW9BVV95cUxOMnZJeUNSRThYSlZkYTRnTjhUaFl1Rjgzb1k0ZktKbS1ISWRhN29rX09sSTJ4ckJ6NDJuZ2FGcEhDQXRBY2RrWUxDTW9ORnlkV3VSRjhOTVlUTGlNN01pa0NIMkd4TzVrZm10Sl9xd3c?oc=5</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Thu, 28 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 차량용 D램 'ISO 26262' 최고 등급 획득 - 디일렉</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE0xSV9lUWFSeE0tdE15c1VEM05qQzVDc2hxUUsyZ3RqSHFfM3BrS01PTFBWdUxnZV96eHNwdWg4VzlMNTdqbE9VdDlyeDgxSUZhUmtWNENhb0g5UWM4LWxsMWdUbEdlUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Mon, 19 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>TÜV SÜD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>TÜV SÜD Korea, 하우엔지니어링웍스와 자동차 ISO 26262 기능안전 및 A-SPICE 분야 업무협약 체결 - TÜV SÜD</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOWEJiLU91RTJFemEyZGNPNEpTdFR2d3VTdGZYU3VZM1hKdXI0OGVyU3Z6aVQ4bzhpRE91c3pMYWE5TVhucEFXY2xQYi1WaEh5MFhfcFhJck9yRzEwTl9DVUFndkFuSnJDeDVwRmZKZnByaGxsc25LaFhCS2RpalNWaGhTVnU2TUpEbUU0b3VKTmxSUVhaRWwzQk5ZQ0VZSUdaV0VXeS1fdjhJU2g4Z1lB?oc=5</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Wed, 04 Mar 2026 06:53:16 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>IT비즈뉴스</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>현대오토에버, 전장SW 검증자동화 툴 ‘ISO26262’ 획득 - IT비즈뉴스</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1FOTFRMVdNWi1HQk9WLTdTUDhvR25wazhiZXdzcHRpNFh1ZnBKeGJtMXB3UzlIbmFCaUxWS3pwaXRGWUU0UGRhaEdvRHRUTGJWeTRUSXAxa29jUTZ6NUxGUXozS25WVFFQc0Vpeg?oc=5</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Mon, 26 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>ISO26262</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>KIPOST</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>TÜV SÜD Korea, 하우엔지니어링웍스와 자동차 ISO 26262 기능안전 및 A-SPICE 분야 업무협약 체결 - KIPOST</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE9xMUFlQnNHUXE4X3g1ZTZPNXJ0ZERWc21kNmdZaWxtUV82WlBsYnM2Mm9hcVY1NWhVOW0zLWgyNjFkM0RLX2ljRzk1U1JBeDhMeEhJUGR2M1ZDT0llcEZGUUh1VEstSFpr0gFsQVVfeXFMTXFqUWtnS2NOb3VxLVFFZ1R2M25KNmxxMS1MZWxSczdMaWV2QU9zM2V3S215T3FHVGFrU1ZKZ3RWMjZFVTlWam16SnFibkNmQUFHMGh1UG5zdmhvSlRORTdKSzdCbmlDNm1OTHZf?oc=5</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Fri, 27 Feb 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>autoelectronics.co.kr</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>[구태완 테크 칼럼] Safety Analysis: 귀납적 vs. 연역적 안전분석 - autoelectronics.co.kr</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE1KN1FSaWdHRGk0YUlSMjZkbjdLemtBemNuLUpUMnJIa3FJS05OMVdGeFhKRTdWZk5zcUh4SlYxR3hvcUNfbkQ0Z2JUVzV4VmYyV29CQkp6OFZmUThUNm1faFRLdHVoWkhzOEJfMExRcUNUTHhY?oc=5</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Mon, 02 Feb 2026 01:10:17 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>한국식품의약신문</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>의료기관평가인증원, ‘2026년 환자안전 현장지원 활성화’ 사업 시행 - 한국식품의약신문</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBCZ3JBYnFsSWJLT1BzOHNFbGQ3amtDOXdrTW1hTmdIOGxyaDBNdXBpUVIxME9MXzB5ak5JOHJMZ3QxRzNkRXZuekdRYjhkTnlHRVByU193cHJEOElQX2ZZeDllVWxyWXM?oc=5</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Tue, 10 Mar 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>techsuda.com</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>이엠포커스 ‘스마트 FMEA’, ‘FMEA 360’으로 제품명 변경 - techsuda.com</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQaWR3TmJPUjRLeDBaZEMxQ05meXZ4aXd0VnFzUnQwTmdKQnJlcTZRVjhfdmJCVXU4cU5lTWpaaXc1ZXBPMTlvcHV0LVdhZEI1d2x6cktOYlpxd25rOGhNSEtWcnlyYkw1Y2NiSEl5ellLUlcxY0JmY2Q4YVlob3VWVElWbmpFTHU4clFUV2JmUENpd9IBlwFBVV95cUxPREVZc0FjRVJodDBiZDVabVNkcGx6UW9nbUwtaVZXMmU5RnlmbWNXUGZad3E5OTFzVzlsTVZkRDhrWkpVOU5QNXVaSXB3Y1MwRTRuRnE5Z2RIM1pBXzQ4V05COTlrSHR1dGF3Q08zSVNINDB1bFhvcnI0YWp1Q2UxQmFxeUlqOEUwUy0ybDdKdEVobEZ2R1RJ?oc=5</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Wed, 14 Feb 2024 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>뉴스와이어</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>이엠포커스, LG마그나에 FMEA 솔루션 공급 계약 체결 - 뉴스와이어</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTFBXTE5xN3QxUmtBVnM5UmhxXzRmU3FudkJYUjFmbUNVRVhrMHR0ZHhVZDRzVVo5Z0oxYlVrWnc1X3M4bkFwc1h4TmhTVTB4bWtkWlQ4SldBWFozaVN4WVE?oc=5</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Tue, 11 Jul 2023 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>FMEA</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>동아일보</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>AIAG-VDA에 최적화된 ‘스마트-FMEA’ 솔루션 - 동아일보</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBwb3hnTmVBTEszXzBFMGhKZTdTV3FfSDB2dWh2TjVtaVpHU0NPX09TZTN5M2g1Z1A5Qk5CY3g5N1ZFUGtSVHBDSEx3R2REZEROc2JZZEltZHMyT2YzMUlqYmJieTRIY2hjOGF3X3k4VVhLM1M1LXfSAWZBVV95cUxObUJjU1NjUldKNkFJNTJZenVmSUFMRUhIV1p2OGRYVjdaNE53VFdfdDl2WGE4RmtQVEZJako4R3hWb3lhRmw2em9aNkZDaExwY0h2Y2gtMUVvd0NLY0VnSFJrOTdDeEE?oc=5</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Mon, 31 Oct 2022 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>APQP</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>테크월드</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>세윤씨앤에스, APQP 프로세스 관리 솔루션 ‘와이저오토 포털’ 신버전 개발 완료 - 테크월드</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZ0FVX3lxTFBkRTFOV093MXF2Z3QyLUtRWGlFTmVGOE1lTUVCNkkwLVJwNGp5RWNqdi1jSWxPclNxakhlZ1NnaV9FZEk5WGtDZl9WSG5DMTVkWWtoQXlBLWRQUnNGcGQxSXJXTkFkM1k?oc=5</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Fri, 24 Jul 2015 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>PPAP</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>v.daum.net</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>'PPAP' 피코타로, 15세 연하 모델과 결혼 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE5UT1F5ZmFwM2RNUnpkY29aMFdiZE56eHJQTllyaGJjQ2Fna21oS0Eta0h2Qkt3cW9CUk4xMXJtRUdrOUcwQXc?oc=5</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Fri, 04 Aug 2017 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>PPAP</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>yna.co.kr</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>'의외의 조합?'…日 기시다 외무상 만난 PPAP 아저씨 - yna.co.kr</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9wY1hZdEs0U3E3N042OGJBTWVLX05JOWcxSnRta3FPTzlOazFRSkpnYTRBTEZNZUNvY2RDb243T0xDWkNMYnVLZ1o2eXFqbjl5NDlwU05qS3M1bjQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Thu, 13 Jul 2017 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>PPAP</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>중앙일보</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>'PPAP' 아저씨, 유튜브 스타로 만들어준 저스틴 비버와 만났다 - 중앙일보</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTFA5MkNndW1lRzhEOHlHSTlzVDU1MVhxWXVnQXFjMlNiN2R2dXM3ekI0eThfdmw5VUNrdUdyVm51Zld4c0Y3cmstRS1SMlRIWFpZS1ZHWEtR?oc=5</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Tue, 07 Feb 2017 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PPAP</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>munhwa.com</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>제2의 강남스타일 ‘PPAP’ 아시나요? - munhwa.com</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTE1sS2hXYjBkaHZCX3BXaDc3cDZIODRLR0NiYTNWNFcwMFMxRXRidm55TmVIdVFNaUVKMFBMQkh2dzNKY1FfdEZVVnVfSlpGTkxl?oc=5</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Mon, 24 Oct 2016 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>PPAP</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>경향신문</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>트럼프와 피코 타로의 첫 만남은..."PPAP 부르려고 하자 트럼프가 '스톱'" - 경향신문</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5pMXNOc25OSFZRUG9vaS1JcVo1UUx2RkY5S05hb3NCMDRBb2YxY0JBMkppOGdQLW9fZWhJX3RGc052M2ozbGhSVjdLcm95ZXE4RUVVUGd3amZWQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Tue, 07 Nov 2017 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>시흥타임즈</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>시흥도시공사, ‘ISO10002’ 및 ‘SQ인증’ 연속 획득 - 시흥타임즈</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBFd3JRUHlpMC1iYnBZdG9VZnBhY3dzNzhVY3o0VUFsSjJWbXE4QUNzTjB4QTZaQjd2ZjlLTHgtZWtXckV4aExlMks4QUhXMXZYV0IwYVk4UV8tRGVKRUNybw?oc=5</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Wed, 10 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>성동저널</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>‘고객중심 서비스 혁신’... 성동공단, ‘한국서비스품질 우수기업’ 인증 - 성동저널</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTE1DeUhnU09ka1JudDhqb2ZHZlgyb0RnOFNYTHA5NWVjYVRGRmJNeFVNeVRKa29TVEhmQk9OeU9tS1YySnpMNzY5aTN5Mk16Ml83dGFsU0U1eDNKNlVyQTVkUkFjMDdwbDdYUEFEMk4wTGY?oc=5</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Thu, 11 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>디일렉</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>페스카로, JS오토모티브 인수 "SDV 수직계열화 완성" - 디일렉</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE9sVm9KV09WRlZHaHc0TTI0U1Raa0FxSU9TeGxnUEtsWWZTVWVqQUhSQmZ1LWJERDVXZDFJUFhEUmlWcC1NOTJDVzNHOHRyMVlIZlRNNHVabERwYm9pSU00VUw0eDNTdw?oc=5</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Fri, 08 May 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>로컬세계</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>강원랜드, ‘한국서비스품질 우수기업(SQ)’ 인증 획득 - 로컬세계</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE94Sk5kRVJEUzdXRkRJcG93djQtUGlLOVBKdktfWmtRSEVXV0ZIS1N5UG5tdl81a3ROaFFJcUtybE1HYXFUWjhNYkg3UmpPQ09lMW91VDZqT0FqRnNOTFBSNNIBWEFVX3lxTE5Jb3V6c0RCNm5XajZST21WQ1otQ1RBRTJLWlZvekZmekdLcTVWU1dsLXEyQ3lCOXRTQXkwbVV1ejAxT3VZYjM0di1sWVZNMk5wUTk2SU10OGc?oc=5</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Fri, 17 Oct 2025 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SQ인증</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>내외경제TV</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>부산시설공단, 한국서비스품질 우수기업(SQ) 인증 취득 - 내외경제TV</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE9Td3d0MzdVTndmM2FIUmQtajl3QjZxV0pHTXltaW9mVmctRjVLbEd1Ni1qekQtTXRULXFBY016eXBKTjlySTZRbFVCU1ozMThfYkRDNWRteUxJQmM1MnlCbEVNZlp3LWQwRzZv?oc=5</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Tue, 13 Jan 2026 08:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>기업일반/동향</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>더스탁(The Stock)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>디케이티, 휴머노이드 초단기 진입…'비결' 본업에 있다 - 더스탁(The Stock)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5NODRjZzdNX3FVaW15WjlBWm9hcUtFUldocmttendMZzhtMGR4bVJVdHFFZW5aQk9sX3liWktTOVEzVURMaWh4SFlIdlMwZVkxeXJVS0poWEdoMHA1ODk2QkJwX1h5b3NESUE?oc=5</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Mon, 10 Aug 2026 01:01:11 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>파이낸스스코프</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>아모텍, 전장용 MLCC 성장세 지속… 고신뢰성 라인업으로 시장 공략 가속 - 파이낸스스코프</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9HcTJwLWYycVpqR01iOHh5aHZRREY1UUtmNUFWa1V2UzBla2FucTlDbWdxSy1hLUdYMnBiVHJKRFRWaU9HSnI0dXdyRWZpblM2ZDFWejJPSVZza2RwU1R0V2Z4RHlibHlyRnc?oc=5</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Mon, 03 Aug 2026 23:56:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>데이터넷</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>아모텍, 전장용 MLCC 공급 확대 추진 ··· 고신뢰성 제품 경쟁력 강화 - 데이터넷</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5uQVlKWHQ5SmROZ3BnRzFYbll1NW9ac2wxN1dZeGxjUHJ6alVTUFVrZ3MxNnhsRXN5clE4eWJ1NExvMENrUTJzV2ZScmZFT20wS0dtVmtXbWVrODRtc3owQ3N2VFZiSlJyc1psMQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Tue, 04 Aug 2026 04:41:19 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>전자신문</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>FITI시험연구원, '소재부터 배터리 팩까지'…미래 모빌리티 신뢰성 혁신 이끈다 - 전자신문</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE90VmFscmVXVnU3WHF0MWV4WEEzU1VCQWJVSTFsTWFQNVNRZHdFR2c3bkVKNDd4eld6d2toWlFqa2VmWDJKN0pCTzJCM0UyUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Fri, 12 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:44</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>자동차/전장 품질</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>전장 신뢰성</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>IT비즈뉴스</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SK키파운드리, 전장반도체 신뢰성 극대화 ‘온칩 EMC 보호 기술’ 개발 - IT비즈뉴스</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9HU3ZXQjJQY2l1RzRtamVJN1QzSV9FdnQ0a0w3b0RSNDdfYmJ0dF9KeGJaYUlIUVR3VzRLZUNUcHI4ODlTQzFLTkxUMWV3SkhWUHZ4R3YwTUxJSEFwZFFfZWR5UkZXX3hHZHozbA?oc=5</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 07:00:00 GMT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>